--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B466"/>
+  <dimension ref="A1:B478"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3427,154 +3427,154 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>REPORT</v>
+        <v>HDR</v>
       </c>
       <c r="B378" t="str">
-        <v>RAPPORTO</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>FAIL</v>
+        <v>Code points</v>
       </c>
       <c r="B379" t="str">
-        <v>NON SUPERATO</v>
+        <v>Punti di codice</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>checks</v>
+        <v>Gain curve</v>
       </c>
       <c r="B380" t="str">
-        <v>controlli</v>
+        <v>Curva di guadagno</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B381" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>Primari di colore</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B382" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Caratteristiche di trasferimento</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B383" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Coefficienti di matrice</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Powered by {lib}</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B384" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Flag intervallo video completo</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Subscribe</v>
+        <v>Full range</v>
       </c>
       <c r="B385" t="str">
-        <v>Iscriviti</v>
+        <v>Intervallo completo</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Narrow range</v>
       </c>
       <c r="B386" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Intervallo ridotto</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Get notified about new releases</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B387" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>non assegnato da ITU-T H.273</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Close</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B388" t="str">
-        <v>Chiudi</v>
+        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B389" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Email address</v>
+        <v>REPORT</v>
       </c>
       <c r="B390" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>you@example.com</v>
+        <v>FAIL</v>
       </c>
       <c r="B391" t="str">
-        <v>tu@esempio.com</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>How will you use profiletool?</v>
+        <v>checks</v>
       </c>
       <c r="B392" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>(optional)</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B393" t="str">
-        <v>(opzionale)</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B394" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B395" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Cancel</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B396" t="str">
-        <v>Annulla</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="397">
@@ -3587,18 +3587,18 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B398" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B399" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="400">
@@ -3611,535 +3611,631 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Privacy notice</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B401" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Email address</v>
       </c>
       <c r="B402" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B403" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Please check the form and try again.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B404" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B405" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Network error. Please try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B406" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Error:</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B407" t="str">
-        <v>Errore:</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Convert to XML</v>
+        <v>Cancel</v>
       </c>
       <c r="B408" t="str">
-        <v>Converti in XML</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Convert to JSON</v>
+        <v>Subscribe</v>
       </c>
       <c r="B409" t="str">
-        <v>Converti in JSON</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Convert to ICC</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B410" t="str">
-        <v>Converti in ICC</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Converting to XML…</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B411" t="str">
-        <v>Conversione in XML…</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Converting to JSON…</v>
+        <v>Close</v>
       </c>
       <c r="B412" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Converting to ICC…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B413" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Load ICC profile</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B414" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B415" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile ID</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B416" t="str">
-        <v>ID profilo</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>No tags found.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B417" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Tag Name</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B418" t="str">
-        <v>Nome tag</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ID</v>
+        <v>Error:</v>
       </c>
       <c r="B419" t="str">
-        <v>ID</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Offset</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B420" t="str">
-        <v>Offset</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Size</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B421" t="str">
-        <v>Dimensione</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Pad</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B422" t="str">
-        <v>Riempimento</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B423" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Type</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B424" t="str">
-        <v>Tipo</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Array of {type}</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B425" t="str">
-        <v>Array di {type}</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>(No content)</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B426" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>bytes</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B427" t="str">
-        <v>byte</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Loading full description…</v>
+        <v>Profile ID</v>
       </c>
       <c r="B428" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not load full description:</v>
+        <v>No tags found.</v>
       </c>
       <c r="B429" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B430" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>ID</v>
       </c>
       <c r="B431" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No validation output</v>
+        <v>Offset</v>
       </c>
       <c r="B432" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Profile is valid</v>
+        <v>Size</v>
       </c>
       <c r="B433" t="str">
-        <v>Il profilo è valido</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Pad</v>
       </c>
       <c r="B434" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B435" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Critical validation error</v>
+        <v>Type</v>
       </c>
       <c r="B436" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Unknown validation status</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B437" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>(No content)</v>
       </c>
       <c r="B438" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>No warnings or errors found.</v>
+        <v>bytes</v>
       </c>
       <c r="B439" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Valid</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B440" t="str">
-        <v>Valido</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Warning</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B441" t="str">
-        <v>Avviso</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Error</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B442" t="str">
-        <v>Errore</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Unknown</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B443" t="str">
-        <v>Sconosciuto</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Pass</v>
+        <v>No validation output</v>
       </c>
       <c r="B444" t="str">
-        <v>Superato</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Fail</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B445" t="str">
-        <v>Non superato</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>View in context</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B446" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Validation detail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B447" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Triggered by</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B448" t="str">
-        <v>Attivato da</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Field</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B449" t="str">
-        <v>Campo</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Current value</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B450" t="str">
-        <v>Valore attuale</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Required: 0</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B451" t="str">
-        <v>Richiesto: 0</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Expected: {value}</v>
+        <v>Valid</v>
       </c>
       <c r="B452" t="str">
-        <v>Atteso: {value}</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Invalid</v>
+        <v>Warning</v>
       </c>
       <c r="B453" t="str">
-        <v>Non valido</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Error</v>
       </c>
       <c r="B454" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Close</v>
+        <v>Unknown</v>
       </c>
       <c r="B455" t="str">
-        <v>Chiudi</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Loading XML editor…</v>
+        <v>Pass</v>
       </c>
       <c r="B456" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Fail</v>
       </c>
       <c r="B457" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>View in context</v>
       </c>
       <c r="B458" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B459" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Triggered by</v>
       </c>
       <c r="B460" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Field</v>
       </c>
       <c r="B461" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Current value</v>
       </c>
       <c r="B462" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B463" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>indent</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B464" t="str">
-        <v>rientro</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>sort keys</v>
+        <v>Invalid</v>
       </c>
       <c r="B465" t="str">
-        <v>ordina chiavi</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B466" t="str">
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B467" t="str">
+        <v>Chiudi</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B468" t="str">
+        <v>Caricamento editor XML…</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B469" t="str">
+        <v>Caricamento editor JSON…</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B470" t="str">
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B471" t="str">
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B472" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B473" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B474" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B475" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B476" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B477" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B466" t="str">
+      <c r="B478" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B466"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B478"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B478"/>
+  <dimension ref="A1:B498"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3451,791 +3451,951 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Colour primaries</v>
+        <v>Environment</v>
       </c>
       <c r="B381" t="str">
-        <v>Primari di colore</v>
+        <v>Ambiente</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Transfer characteristics</v>
+        <v>Detecting…</v>
       </c>
       <c r="B382" t="str">
-        <v>Caratteristiche di trasferimento</v>
+        <v>Rilevamento…</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Matrix coefficients</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B383" t="str">
-        <v>Coefficienti di matrice</v>
+        <v>Impossibile rilevare l’ambiente.</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Video full-range flag</v>
+        <v>HDR display</v>
       </c>
       <c r="B384" t="str">
-        <v>Flag intervallo video completo</v>
+        <v>Display HDR</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Full range</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B385" t="str">
-        <v>Intervallo completo</v>
+        <v>Gamut esteso</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Narrow range</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B386" t="str">
-        <v>Intervallo ridotto</v>
+        <v>Percorso canvas HDR</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>sRGB</v>
       </c>
       <c r="B387" t="str">
-        <v>non assegnato da ITU-T H.273</v>
+        <v>sRGB</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>none</v>
       </c>
       <c r="B388" t="str">
-        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
+        <v>nessuno</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>yes</v>
       </c>
       <c r="B389" t="str">
-        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
+        <v>sì</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>REPORT</v>
+        <v>no</v>
       </c>
       <c r="B390" t="str">
-        <v>RAPPORTO</v>
+        <v>no</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>FAIL</v>
+        <v>not reported</v>
       </c>
       <c r="B391" t="str">
-        <v>NON SUPERATO</v>
+        <v>non riportato</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>checks</v>
+        <v>Format</v>
       </c>
       <c r="B392" t="str">
-        <v>controlli</v>
+        <v>Formato</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Inspect</v>
       </c>
       <c r="B393" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>Ispeziona</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Display</v>
       </c>
       <c r="B394" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Visualizza</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR</v>
       </c>
       <c r="B395" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Powered by {lib}</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B396" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Legge il profilo ICC incorporato — nessun codec richiesto</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Subscribe</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B397" t="str">
-        <v>Iscriviti</v>
+        <v>Mostra i pixel</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B398" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Resa più luminosa del bianco</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Get notified about new releases</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B399" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Decodificato da profiletool, quindi indipendente dal browser</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
       </c>
       <c r="B400" t="str">
-        <v>Chiudi</v>
+        <v>I browser non possono indicare quanto margine HDR abbia un display, solo se esiste un percorso HDR.</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B401" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Primari di colore</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Email address</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B402" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>Caratteristiche di trasferimento</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>you@example.com</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B403" t="str">
-        <v>tu@esempio.com</v>
+        <v>Coefficienti di matrice</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B404" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>Flag intervallo video completo</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>(optional)</v>
+        <v>Full range</v>
       </c>
       <c r="B405" t="str">
-        <v>(opzionale)</v>
+        <v>Intervallo completo</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Narrow range</v>
       </c>
       <c r="B406" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>Intervallo ridotto</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B407" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>non assegnato da ITU-T H.273</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Cancel</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B408" t="str">
-        <v>Annulla</v>
+        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Subscribe</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B409" t="str">
-        <v>Iscriviti</v>
+        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>REPORT</v>
       </c>
       <c r="B410" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>FAIL</v>
       </c>
       <c r="B411" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Close</v>
+        <v>checks</v>
       </c>
       <c r="B412" t="str">
-        <v>Chiudi</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Privacy notice</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B413" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B414" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B415" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B416" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B417" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B418" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Error:</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B419" t="str">
-        <v>Errore:</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Convert to XML</v>
+        <v>Close</v>
       </c>
       <c r="B420" t="str">
-        <v>Converti in XML</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Convert to JSON</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B421" t="str">
-        <v>Converti in JSON</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Convert to ICC</v>
+        <v>Email address</v>
       </c>
       <c r="B422" t="str">
-        <v>Converti in ICC</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Converting to XML…</v>
+        <v>you@example.com</v>
       </c>
       <c r="B423" t="str">
-        <v>Conversione in XML…</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Converting to JSON…</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B424" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Converting to ICC…</v>
+        <v>(optional)</v>
       </c>
       <c r="B425" t="str">
-        <v>Conversione in ICC…</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Load ICC profile</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B426" t="str">
-        <v>Carica profilo ICC</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B427" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Profile ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B428" t="str">
-        <v>ID profilo</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>No tags found.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B429" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Tag Name</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B430" t="str">
-        <v>Nome tag</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B431" t="str">
-        <v>ID</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Offset</v>
+        <v>Close</v>
       </c>
       <c r="B432" t="str">
-        <v>Offset</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Size</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B433" t="str">
-        <v>Dimensione</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Pad</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B434" t="str">
-        <v>Riempimento</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Bytes changed since load</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B435" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Type</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B436" t="str">
-        <v>Tipo</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Array of {type}</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B437" t="str">
-        <v>Array di {type}</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>(No content)</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B438" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>bytes</v>
+        <v>Error:</v>
       </c>
       <c r="B439" t="str">
-        <v>byte</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Loading full description…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B440" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Could not load full description:</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B441" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B442" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B443" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>No validation output</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B444" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Profile is valid</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B445" t="str">
-        <v>Il profilo è valido</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B446" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B447" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Critical validation error</v>
+        <v>Profile ID</v>
       </c>
       <c r="B448" t="str">
-        <v>Errore di convalida critico</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Unknown validation status</v>
+        <v>No tags found.</v>
       </c>
       <c r="B449" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Tag Name</v>
       </c>
       <c r="B450" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>No warnings or errors found.</v>
+        <v>ID</v>
       </c>
       <c r="B451" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Valid</v>
+        <v>Offset</v>
       </c>
       <c r="B452" t="str">
-        <v>Valido</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Warning</v>
+        <v>Size</v>
       </c>
       <c r="B453" t="str">
-        <v>Avviso</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Error</v>
+        <v>Pad</v>
       </c>
       <c r="B454" t="str">
-        <v>Errore</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Unknown</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B455" t="str">
-        <v>Sconosciuto</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Pass</v>
+        <v>Type</v>
       </c>
       <c r="B456" t="str">
-        <v>Superato</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Fail</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B457" t="str">
-        <v>Non superato</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>View in context</v>
+        <v>(No content)</v>
       </c>
       <c r="B458" t="str">
-        <v>Mostra nel contesto</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Validation detail</v>
+        <v>bytes</v>
       </c>
       <c r="B459" t="str">
-        <v>Dettaglio convalida</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Triggered by</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B460" t="str">
-        <v>Attivato da</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Field</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B461" t="str">
-        <v>Campo</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Current value</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B462" t="str">
-        <v>Valore attuale</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Required: 0</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B463" t="str">
-        <v>Richiesto: 0</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Expected: {value}</v>
+        <v>No validation output</v>
       </c>
       <c r="B464" t="str">
-        <v>Atteso: {value}</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Invalid</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B465" t="str">
-        <v>Non valido</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B466" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Close</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B467" t="str">
-        <v>Chiudi</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Loading XML editor…</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B468" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B469" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B470" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B471" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Valid</v>
       </c>
       <c r="B472" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Warning</v>
       </c>
       <c r="B473" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Error</v>
       </c>
       <c r="B474" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Unknown</v>
       </c>
       <c r="B475" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>indent</v>
+        <v>Pass</v>
       </c>
       <c r="B476" t="str">
-        <v>rientro</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>sort keys</v>
+        <v>Fail</v>
       </c>
       <c r="B477" t="str">
-        <v>ordina chiavi</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B478" t="str">
+        <v>Mostra nel contesto</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B479" t="str">
+        <v>Dettaglio convalida</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B480" t="str">
+        <v>Attivato da</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B481" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B482" t="str">
+        <v>Valore attuale</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B483" t="str">
+        <v>Richiesto: 0</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B484" t="str">
+        <v>Atteso: {value}</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B485" t="str">
+        <v>Non valido</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B486" t="str">
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B487" t="str">
+        <v>Chiudi</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B488" t="str">
+        <v>Caricamento editor XML…</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B489" t="str">
+        <v>Caricamento editor JSON…</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B490" t="str">
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B491" t="str">
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B492" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B493" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B494" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B495" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B496" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B497" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B478" t="str">
+      <c r="B498" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B478"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B498"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B498"/>
+  <dimension ref="A1:B502"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3459,943 +3459,975 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Detecting…</v>
+        <v>Showing the SDR fallback</v>
       </c>
       <c r="B382" t="str">
-        <v>Rilevamento…</v>
+        <v>Visualizzazione del ripiego SDR</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Could not detect environment.</v>
+        <v>HDR Profile in the chain</v>
       </c>
       <c r="B383" t="str">
-        <v>Impossibile rilevare l’ambiente.</v>
+        <v>Profilo HDR nella catena</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>HDR display</v>
+        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B384" t="str">
-        <v>Display HDR</v>
+        <v>Le trasformazioni attraverso un profilo HDR usano il suo AToB0Tag — il rendering SDR fissato richiesto dalla clausola 8.10.6 — perché la clausola 8.10.1 non gli lascia tag TRC. Il risultato è quel ripiego, non comportamento HDR.</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Wide gamut</v>
+        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B385" t="str">
-        <v>Gamut esteso</v>
+        <v>Sono profili HDR, privi di tag TRC: il gamut è quindi costruito dall’AToB0Tag, il rendering SDR fissato che la clausola 8.10.6 richiede per i consumatori senza elaborazione HDR. Non è il gamut HDR del profilo, che non può essere tracciato in un PCS limitato.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>HDR canvas path</v>
+        <v>Detecting…</v>
       </c>
       <c r="B386" t="str">
-        <v>Percorso canvas HDR</v>
+        <v>Rilevamento…</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>sRGB</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B387" t="str">
-        <v>sRGB</v>
+        <v>Impossibile rilevare l’ambiente.</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>none</v>
+        <v>HDR display</v>
       </c>
       <c r="B388" t="str">
-        <v>nessuno</v>
+        <v>Display HDR</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>yes</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B389" t="str">
-        <v>sì</v>
+        <v>Gamut esteso</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>no</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B390" t="str">
-        <v>no</v>
+        <v>Percorso canvas HDR</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>not reported</v>
+        <v>sRGB</v>
       </c>
       <c r="B391" t="str">
-        <v>non riportato</v>
+        <v>sRGB</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Format</v>
+        <v>none</v>
       </c>
       <c r="B392" t="str">
-        <v>Formato</v>
+        <v>nessuno</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Inspect</v>
+        <v>yes</v>
       </c>
       <c r="B393" t="str">
-        <v>Ispeziona</v>
+        <v>sì</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Display</v>
+        <v>no</v>
       </c>
       <c r="B394" t="str">
-        <v>Visualizza</v>
+        <v>no</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>HDR</v>
+        <v>not reported</v>
       </c>
       <c r="B395" t="str">
-        <v>HDR</v>
+        <v>non riportato</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Read the embedded ICC profile — needs no codec</v>
+        <v>Format</v>
       </c>
       <c r="B396" t="str">
-        <v>Legge il profilo ICC incorporato — nessun codec richiesto</v>
+        <v>Formato</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Show the pixels</v>
+        <v>Inspect</v>
       </c>
       <c r="B397" t="str">
-        <v>Mostra i pixel</v>
+        <v>Ispeziona</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Render brighter-than-white</v>
+        <v>Display</v>
       </c>
       <c r="B398" t="str">
-        <v>Resa più luminosa del bianco</v>
+        <v>Visualizza</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Decoded by profiletool itself, so browser-independent</v>
+        <v>HDR</v>
       </c>
       <c r="B399" t="str">
-        <v>Decodificato da profiletool, quindi indipendente dal browser</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B400" t="str">
-        <v>I browser non possono indicare quanto margine HDR abbia un display, solo se esiste un percorso HDR.</v>
+        <v>Legge il profilo ICC incorporato — nessun codec richiesto</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Colour primaries</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B401" t="str">
-        <v>Primari di colore</v>
+        <v>Mostra i pixel</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Transfer characteristics</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B402" t="str">
-        <v>Caratteristiche di trasferimento</v>
+        <v>Resa più luminosa del bianco</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Matrix coefficients</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B403" t="str">
-        <v>Coefficienti di matrice</v>
+        <v>Decodificato da profiletool, quindi indipendente dal browser</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Video full-range flag</v>
+        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
       </c>
       <c r="B404" t="str">
-        <v>Flag intervallo video completo</v>
+        <v>I browser non possono indicare quanto margine HDR abbia un display, solo se esiste un percorso HDR.</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Full range</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B405" t="str">
-        <v>Intervallo completo</v>
+        <v>Primari di colore</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Narrow range</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B406" t="str">
-        <v>Intervallo ridotto</v>
+        <v>Caratteristiche di trasferimento</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B407" t="str">
-        <v>non assegnato da ITU-T H.273</v>
+        <v>Coefficienti di matrice</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B408" t="str">
-        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
+        <v>Flag intervallo video completo</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Full range</v>
       </c>
       <c r="B409" t="str">
-        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
+        <v>Intervallo completo</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>REPORT</v>
+        <v>Narrow range</v>
       </c>
       <c r="B410" t="str">
-        <v>RAPPORTO</v>
+        <v>Intervallo ridotto</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>FAIL</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B411" t="str">
-        <v>NON SUPERATO</v>
+        <v>non assegnato da ITU-T H.273</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>checks</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B412" t="str">
-        <v>controlli</v>
+        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B413" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>REPORT</v>
       </c>
       <c r="B414" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>ICC Profile Tool</v>
+        <v>FAIL</v>
       </c>
       <c r="B415" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Powered by {lib}</v>
+        <v>checks</v>
       </c>
       <c r="B416" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Subscribe</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B417" t="str">
-        <v>Iscriviti</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B418" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B419" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Close</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B420" t="str">
-        <v>Chiudi</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B421" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Email address</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B422" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B423" t="str">
-        <v>tu@esempio.com</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Close</v>
       </c>
       <c r="B424" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>(optional)</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B425" t="str">
-        <v>(opzionale)</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Email address</v>
       </c>
       <c r="B426" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B427" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Cancel</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B428" t="str">
-        <v>Annulla</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Subscribe</v>
+        <v>(optional)</v>
       </c>
       <c r="B429" t="str">
-        <v>Iscriviti</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B430" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B431" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B432" t="str">
-        <v>Chiudi</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Privacy notice</v>
+        <v>Subscribe</v>
       </c>
       <c r="B433" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B434" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B435" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Close</v>
       </c>
       <c r="B436" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B437" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B438" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Error:</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B439" t="str">
-        <v>Errore:</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Convert to XML</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B440" t="str">
-        <v>Converti in XML</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Convert to JSON</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B441" t="str">
-        <v>Converti in JSON</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Convert to ICC</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B442" t="str">
-        <v>Converti in ICC</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Converting to XML…</v>
+        <v>Error:</v>
       </c>
       <c r="B443" t="str">
-        <v>Conversione in XML…</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B444" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B445" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B446" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B447" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Profile ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B448" t="str">
-        <v>ID profilo</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>No tags found.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B449" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Tag Name</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B450" t="str">
-        <v>Nome tag</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B451" t="str">
-        <v>ID</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Offset</v>
+        <v>Profile ID</v>
       </c>
       <c r="B452" t="str">
-        <v>Offset</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Size</v>
+        <v>No tags found.</v>
       </c>
       <c r="B453" t="str">
-        <v>Dimensione</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Pad</v>
+        <v>Tag Name</v>
       </c>
       <c r="B454" t="str">
-        <v>Riempimento</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Bytes changed since load</v>
+        <v>ID</v>
       </c>
       <c r="B455" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Type</v>
+        <v>Offset</v>
       </c>
       <c r="B456" t="str">
-        <v>Tipo</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Array of {type}</v>
+        <v>Size</v>
       </c>
       <c r="B457" t="str">
-        <v>Array di {type}</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>(No content)</v>
+        <v>Pad</v>
       </c>
       <c r="B458" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>bytes</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B459" t="str">
-        <v>byte</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Loading full description…</v>
+        <v>Type</v>
       </c>
       <c r="B460" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Could not load full description:</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B461" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>(No content)</v>
       </c>
       <c r="B462" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>bytes</v>
       </c>
       <c r="B463" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>No validation output</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B464" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Profile is valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B465" t="str">
-        <v>Il profilo è valido</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Profile has warning(s)</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B466" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B467" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Critical validation error</v>
+        <v>No validation output</v>
       </c>
       <c r="B468" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B469" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B470" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B471" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B472" t="str">
-        <v>Valido</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Warning</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B473" t="str">
-        <v>Avviso</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Error</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B474" t="str">
-        <v>Errore</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Unknown</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B475" t="str">
-        <v>Sconosciuto</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Pass</v>
+        <v>Valid</v>
       </c>
       <c r="B476" t="str">
-        <v>Superato</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Fail</v>
+        <v>Warning</v>
       </c>
       <c r="B477" t="str">
-        <v>Non superato</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B478" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B479" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Triggered by</v>
+        <v>Pass</v>
       </c>
       <c r="B480" t="str">
-        <v>Attivato da</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Field</v>
+        <v>Fail</v>
       </c>
       <c r="B481" t="str">
-        <v>Campo</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Current value</v>
+        <v>View in context</v>
       </c>
       <c r="B482" t="str">
-        <v>Valore attuale</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Required: 0</v>
+        <v>Validation detail</v>
       </c>
       <c r="B483" t="str">
-        <v>Richiesto: 0</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Expected: {value}</v>
+        <v>Triggered by</v>
       </c>
       <c r="B484" t="str">
-        <v>Atteso: {value}</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Invalid</v>
+        <v>Field</v>
       </c>
       <c r="B485" t="str">
-        <v>Non valido</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Current value</v>
       </c>
       <c r="B486" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Close</v>
+        <v>Required: 0</v>
       </c>
       <c r="B487" t="str">
-        <v>Chiudi</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Loading XML editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B488" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B489" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B490" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B491" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B492" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Caricamento editor XML…</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B493" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Caricamento editor JSON…</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B494" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B495" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>indent</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B496" t="str">
-        <v>rientro</v>
+        <v>● modifiche XML non salvate</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>sort keys</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B497" t="str">
-        <v>ordina chiavi</v>
+        <v>● modifiche JSON non salvate</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B498" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B499" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B500" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B501" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B498" t="str">
+      <c r="B502" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B498"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B502"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B502"/>
+  <dimension ref="A1:B512"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3643,791 +3643,871 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Colour primaries</v>
+        <v>Browser flags</v>
       </c>
       <c r="B405" t="str">
-        <v>Primari di colore</v>
+        <v>Flag del browser</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Transfer characteristics</v>
+        <v>on</v>
       </c>
       <c r="B406" t="str">
-        <v>Caratteristiche di trasferimento</v>
+        <v>attivo</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Matrix coefficients</v>
+        <v>not enabled</v>
       </c>
       <c r="B407" t="str">
-        <v>Coefficienti di matrice</v>
+        <v>non attivo</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Video full-range flag</v>
+        <v>cannot be detected here</v>
       </c>
       <c r="B408" t="str">
-        <v>Flag intervallo video completo</v>
+        <v>non rilevabile qui</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Full range</v>
+        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
       </c>
       <c r="B409" t="str">
-        <v>Intervallo completo</v>
+        <v>Necessario per il rendering HDR in questo browser: senza WebGPU il canvas HDR è l’unica via. L’ispezione dei profili funziona anche senza.</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Narrow range</v>
+        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
       </c>
       <c r="B410" t="str">
-        <v>Intervallo ridotto</v>
+        <v>Facoltativo: l’HDR può passare da WebGPU, ma questo aggiunge il percorso canvas HDR e permette a profiletool di leggere il vero margine HDR dello schermo.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
       </c>
       <c r="B411" t="str">
-        <v>non assegnato da ITU-T H.273</v>
+        <v>Le pagine web non possono aprire le pagine dei flag. Incolla questo nella barra degli indirizzi, imposta Enabled e riavvia il browser.</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Copy</v>
       </c>
       <c r="B412" t="str">
-        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
+        <v>Copia</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Copied</v>
       </c>
       <c r="B413" t="str">
-        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
+        <v>Copiato</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>REPORT</v>
+        <v>Copy failed — select the address and copy it.</v>
       </c>
       <c r="B414" t="str">
-        <v>RAPPORTO</v>
+        <v>Copia non riuscita — seleziona l’indirizzo e copialo.</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>FAIL</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B415" t="str">
-        <v>NON SUPERATO</v>
+        <v>Primari di colore</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>checks</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B416" t="str">
-        <v>controlli</v>
+        <v>Caratteristiche di trasferimento</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B417" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>Coefficienti di matrice</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B418" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Flag intervallo video completo</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Full range</v>
       </c>
       <c r="B419" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Intervallo completo</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Powered by {lib}</v>
+        <v>Narrow range</v>
       </c>
       <c r="B420" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Intervallo ridotto</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Subscribe</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B421" t="str">
-        <v>Iscriviti</v>
+        <v>non assegnato da ITU-T H.273</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B422" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Get notified about new releases</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B423" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Close</v>
+        <v>REPORT</v>
       </c>
       <c r="B424" t="str">
-        <v>Chiudi</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>FAIL</v>
       </c>
       <c r="B425" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Email address</v>
+        <v>checks</v>
       </c>
       <c r="B426" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>you@example.com</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B427" t="str">
-        <v>tu@esempio.com</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B428" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B429" t="str">
-        <v>(opzionale)</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B430" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B431" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B432" t="str">
-        <v>Annulla</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B433" t="str">
-        <v>Iscriviti</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Close</v>
       </c>
       <c r="B434" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B435" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B436" t="str">
-        <v>Chiudi</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Privacy notice</v>
+        <v>you@example.com</v>
       </c>
       <c r="B437" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B438" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>(optional)</v>
       </c>
       <c r="B439" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Please check the form and try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B440" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B441" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B442" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Error:</v>
+        <v>Subscribe</v>
       </c>
       <c r="B443" t="str">
-        <v>Errore:</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Convert to XML</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B444" t="str">
-        <v>Converti in XML</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Convert to JSON</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B445" t="str">
-        <v>Converti in JSON</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Convert to ICC</v>
+        <v>Close</v>
       </c>
       <c r="B446" t="str">
-        <v>Converti in ICC</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Converting to XML…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B447" t="str">
-        <v>Conversione in XML…</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B448" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Converting to ICC…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B449" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Load ICC profile</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B450" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B451" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Profile ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B452" t="str">
-        <v>ID profilo</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>No tags found.</v>
+        <v>Error:</v>
       </c>
       <c r="B453" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Tag Name</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B454" t="str">
-        <v>Nome tag</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B455" t="str">
-        <v>ID</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Offset</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B456" t="str">
-        <v>Offset</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Size</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B457" t="str">
-        <v>Dimensione</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Pad</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B458" t="str">
-        <v>Riempimento</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B459" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Type</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B460" t="str">
-        <v>Tipo</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Array of {type}</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B461" t="str">
-        <v>Array di {type}</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>(No content)</v>
+        <v>Profile ID</v>
       </c>
       <c r="B462" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>bytes</v>
+        <v>No tags found.</v>
       </c>
       <c r="B463" t="str">
-        <v>byte</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Loading full description…</v>
+        <v>Tag Name</v>
       </c>
       <c r="B464" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Could not load full description:</v>
+        <v>ID</v>
       </c>
       <c r="B465" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Offset</v>
       </c>
       <c r="B466" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Size</v>
       </c>
       <c r="B467" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>No validation output</v>
+        <v>Pad</v>
       </c>
       <c r="B468" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Profile is valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B469" t="str">
-        <v>Il profilo è valido</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Type</v>
       </c>
       <c r="B470" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B471" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Critical validation error</v>
+        <v>(No content)</v>
       </c>
       <c r="B472" t="str">
-        <v>Errore di convalida critico</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Unknown validation status</v>
+        <v>bytes</v>
       </c>
       <c r="B473" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B474" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B475" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B476" t="str">
-        <v>Valido</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Warning</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B477" t="str">
-        <v>Avviso</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Error</v>
+        <v>No validation output</v>
       </c>
       <c r="B478" t="str">
-        <v>Errore</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Unknown</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B479" t="str">
-        <v>Sconosciuto</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Pass</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B480" t="str">
-        <v>Superato</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Fail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B481" t="str">
-        <v>Non superato</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>View in context</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B482" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Validation detail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B483" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Triggered by</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B484" t="str">
-        <v>Attivato da</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Field</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B485" t="str">
-        <v>Campo</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Current value</v>
+        <v>Valid</v>
       </c>
       <c r="B486" t="str">
-        <v>Valore attuale</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Required: 0</v>
+        <v>Warning</v>
       </c>
       <c r="B487" t="str">
-        <v>Richiesto: 0</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Expected: {value}</v>
+        <v>Error</v>
       </c>
       <c r="B488" t="str">
-        <v>Atteso: {value}</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Invalid</v>
+        <v>Unknown</v>
       </c>
       <c r="B489" t="str">
-        <v>Non valido</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Pass</v>
       </c>
       <c r="B490" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Close</v>
+        <v>Fail</v>
       </c>
       <c r="B491" t="str">
-        <v>Chiudi</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B492" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B493" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B494" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B495" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B496" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B497" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B498" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B499" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B500" t="str">
-        <v>rientro</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B501" t="str">
-        <v>ordina chiavi</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B502" t="str">
+        <v>Caricamento editor XML…</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B503" t="str">
+        <v>Caricamento editor JSON…</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B504" t="str">
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B505" t="str">
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B506" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B507" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B508" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B509" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B510" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B511" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B502" t="str">
+      <c r="B512" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B502"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B512"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B512"/>
+  <dimension ref="A1:B529"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3635,10 +3635,10 @@
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Browsers cannot report how much HDR headroom a display has, only whether an HDR path exists.</v>
+        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
       </c>
       <c r="B404" t="str">
-        <v>I browser non possono indicare quanto margine HDR abbia un display, solo se esiste un percorso HDR.</v>
+        <v>Questo browser non ha indicato il margine HDR del display, solo se esiste un percorso HDR.</v>
       </c>
     </row>
     <row r="405">
@@ -3723,791 +3723,927 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Colour primaries</v>
+        <v>Pixel ratio</v>
       </c>
       <c r="B415" t="str">
-        <v>Primari di colore</v>
+        <v>Rapporto pixel</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Transfer characteristics</v>
+        <v>Current monitor</v>
       </c>
       <c r="B416" t="str">
-        <v>Caratteristiche di trasferimento</v>
+        <v>Monitor attuale</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Matrix coefficients</v>
+        <v>unnamed</v>
       </c>
       <c r="B417" t="str">
-        <v>Coefficienti di matrice</v>
+        <v>senza nome</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Video full-range flag</v>
+        <v>primary</v>
       </c>
       <c r="B418" t="str">
-        <v>Flag intervallo video completo</v>
+        <v>principale</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Full range</v>
+        <v>built-in</v>
       </c>
       <c r="B419" t="str">
-        <v>Intervallo completo</v>
+        <v>integrato</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Narrow range</v>
+        <v>HDR headroom</v>
       </c>
       <c r="B420" t="str">
-        <v>Intervallo ridotto</v>
+        <v>Margine HDR</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>not exposed by this browser</v>
       </c>
       <c r="B421" t="str">
-        <v>non assegnato da ITU-T H.273</v>
+        <v>non esposto da questo browser</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Shown exactly as the browser reports it. The unit is not standardised yet; an SDR screen has been observed to report 0.</v>
       </c>
       <c r="B422" t="str">
-        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
+        <v>Mostrato esattamente come lo riporta il browser. L’unità non è ancora standardizzata; uno schermo SDR ha riportato 0.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B423" t="str">
-        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
+        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>REPORT</v>
+        <v>Identify displays</v>
       </c>
       <c r="B424" t="str">
-        <v>RAPPORTO</v>
+        <v>Identifica i display</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>FAIL</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B425" t="str">
-        <v>NON SUPERATO</v>
+        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>checks</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B426" t="str">
-        <v>controlli</v>
+        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B427" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B428" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B429" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Impossibile identificare i display.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Powered by {lib}</v>
+        <v>Display events</v>
       </c>
       <c r="B430" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Eventi del display</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Subscribe</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B431" t="str">
-        <v>Iscriviti</v>
+        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B432" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Primari di colore</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Get notified about new releases</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B433" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Caratteristiche di trasferimento</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Close</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B434" t="str">
-        <v>Chiudi</v>
+        <v>Coefficienti di matrice</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B435" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Flag intervallo video completo</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Email address</v>
+        <v>Full range</v>
       </c>
       <c r="B436" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>Intervallo completo</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>you@example.com</v>
+        <v>Narrow range</v>
       </c>
       <c r="B437" t="str">
-        <v>tu@esempio.com</v>
+        <v>Intervallo ridotto</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>How will you use profiletool?</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B438" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>non assegnato da ITU-T H.273</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>(optional)</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B439" t="str">
-        <v>(opzionale)</v>
+        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B440" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B441" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B442" t="str">
-        <v>Annulla</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B443" t="str">
-        <v>Iscriviti</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B444" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B445" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B446" t="str">
-        <v>Chiudi</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B447" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B448" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B449" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B450" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B451" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B452" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B453" t="str">
-        <v>Errore:</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B454" t="str">
-        <v>Converti in XML</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B455" t="str">
-        <v>Converti in JSON</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B456" t="str">
-        <v>Converti in ICC</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B457" t="str">
-        <v>Conversione in XML…</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B458" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B459" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B460" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B461" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B462" t="str">
-        <v>ID profilo</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B463" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B464" t="str">
-        <v>Nome tag</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B465" t="str">
-        <v>ID</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B466" t="str">
-        <v>Offset</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B467" t="str">
-        <v>Dimensione</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B468" t="str">
-        <v>Riempimento</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B469" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B470" t="str">
-        <v>Tipo</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B471" t="str">
-        <v>Array di {type}</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B472" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B473" t="str">
-        <v>byte</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B474" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B475" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B476" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B477" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B478" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B479" t="str">
-        <v>Il profilo è valido</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B480" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B481" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B482" t="str">
-        <v>Errore di convalida critico</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B483" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B484" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B485" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B486" t="str">
-        <v>Valido</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B487" t="str">
-        <v>Avviso</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B488" t="str">
-        <v>Errore</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B489" t="str">
-        <v>Sconosciuto</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B490" t="str">
-        <v>Superato</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B491" t="str">
-        <v>Non superato</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B492" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B493" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B494" t="str">
-        <v>Attivato da</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B495" t="str">
-        <v>Campo</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B496" t="str">
-        <v>Valore attuale</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B497" t="str">
-        <v>Richiesto: 0</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B498" t="str">
-        <v>Atteso: {value}</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B499" t="str">
-        <v>Non valido</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B500" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B501" t="str">
-        <v>Chiudi</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B502" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B503" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B504" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B505" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B506" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B507" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B508" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B509" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B510" t="str">
-        <v>rientro</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B511" t="str">
-        <v>ordina chiavi</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B512" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B513" t="str">
+        <v>Valore attuale</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B514" t="str">
+        <v>Richiesto: 0</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B515" t="str">
+        <v>Atteso: {value}</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B516" t="str">
+        <v>Non valido</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B517" t="str">
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B518" t="str">
+        <v>Chiudi</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B519" t="str">
+        <v>Caricamento editor XML…</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B520" t="str">
+        <v>Caricamento editor JSON…</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B521" t="str">
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B522" t="str">
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B523" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B524" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B525" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B526" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B527" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B528" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B512" t="str">
+      <c r="B529" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B512"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B529"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B529"/>
+  <dimension ref="A1:B530"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3779,871 +3779,879 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Shown exactly as the browser reports it. The unit is not standardised yet; an SDR screen has been observed to report 0.</v>
+        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
       </c>
       <c r="B422" t="str">
-        <v>Mostrato esattamente come lo riporta il browser. L’unità non è ancora standardizzata; uno schermo SDR ha riportato 0.</v>
+        <v>Chromium lo riporta in stop: log₂ della luminanza di picco del display ÷ il livello di bianco SDR. Su Windows si aggiorna solo quando Chrome rilegge il display — finestra spostata su un altro schermo o Chrome riattivato — non quando cambia la luminosità.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>{stops} stops (≈{ratio}× SDR white)</v>
       </c>
       <c r="B423" t="str">
-        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
+        <v>{stops} stop (≈{ratio}× il bianco SDR)</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B424" t="str">
-        <v>Identifica i display</v>
+        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B425" t="str">
-        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
+        <v>Identifica i display</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B426" t="str">
-        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
+        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B427" t="str">
-        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
+        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B428" t="str">
-        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
+        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B429" t="str">
-        <v>Impossibile identificare i display.</v>
+        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B430" t="str">
-        <v>Eventi del display</v>
+        <v>Impossibile identificare i display.</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B431" t="str">
-        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
+        <v>Eventi del display</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B432" t="str">
-        <v>Primari di colore</v>
+        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B433" t="str">
-        <v>Caratteristiche di trasferimento</v>
+        <v>Primari di colore</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B434" t="str">
-        <v>Coefficienti di matrice</v>
+        <v>Caratteristiche di trasferimento</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B435" t="str">
-        <v>Flag intervallo video completo</v>
+        <v>Coefficienti di matrice</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B436" t="str">
-        <v>Intervallo completo</v>
+        <v>Flag intervallo video completo</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B437" t="str">
-        <v>Intervallo ridotto</v>
+        <v>Intervallo completo</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B438" t="str">
-        <v>non assegnato da ITU-T H.273</v>
+        <v>Intervallo ridotto</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B439" t="str">
-        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
+        <v>non assegnato da ITU-T H.273</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B440" t="str">
-        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
+        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B441" t="str">
-        <v>RAPPORTO</v>
+        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B442" t="str">
-        <v>NON SUPERATO</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B443" t="str">
-        <v>controlli</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B444" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B445" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B446" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B447" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B448" t="str">
-        <v>Iscriviti</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B449" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B450" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B451" t="str">
-        <v>Chiudi</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B452" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B453" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B454" t="str">
-        <v>tu@esempio.com</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B455" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B456" t="str">
-        <v>(opzionale)</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B457" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B458" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B459" t="str">
-        <v>Annulla</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B460" t="str">
-        <v>Iscriviti</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B461" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B462" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B463" t="str">
-        <v>Chiudi</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B464" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B465" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B466" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B467" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B468" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B469" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B470" t="str">
-        <v>Errore:</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B471" t="str">
-        <v>Converti in XML</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B472" t="str">
-        <v>Converti in JSON</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B473" t="str">
-        <v>Converti in ICC</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B474" t="str">
-        <v>Conversione in XML…</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B475" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B476" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B477" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B478" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B479" t="str">
-        <v>ID profilo</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B480" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B481" t="str">
-        <v>Nome tag</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B482" t="str">
-        <v>ID</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B483" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B484" t="str">
-        <v>Dimensione</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B485" t="str">
-        <v>Riempimento</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B486" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B487" t="str">
-        <v>Tipo</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B488" t="str">
-        <v>Array di {type}</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B489" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B490" t="str">
-        <v>byte</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B491" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B492" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B493" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B494" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B495" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B496" t="str">
-        <v>Il profilo è valido</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B497" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B498" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B499" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B500" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B501" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B502" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B503" t="str">
-        <v>Valido</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B504" t="str">
-        <v>Avviso</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B505" t="str">
-        <v>Errore</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B506" t="str">
-        <v>Sconosciuto</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B507" t="str">
-        <v>Superato</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B508" t="str">
-        <v>Non superato</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B509" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B510" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B511" t="str">
-        <v>Attivato da</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B512" t="str">
-        <v>Campo</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B513" t="str">
-        <v>Valore attuale</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B514" t="str">
-        <v>Richiesto: 0</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B515" t="str">
-        <v>Atteso: {value}</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B516" t="str">
-        <v>Non valido</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B517" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B518" t="str">
-        <v>Chiudi</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B519" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B520" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Caricamento editor XML…</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B521" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Caricamento editor JSON…</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B522" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B523" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B524" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>● modifiche XML non salvate</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B525" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● modifiche JSON non salvate</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B526" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B527" t="str">
-        <v>rientro</v>
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B528" t="str">
-        <v>ordina chiavi</v>
+        <v>rientro</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B529" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B529" t="str">
+      <c r="B530" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B529"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B530"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B530"/>
+  <dimension ref="A1:B595"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3795,863 +3795,1383 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>HDR</v>
       </c>
       <c r="B424" t="str">
-        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Identify displays</v>
+        <v>Gain at a display headroom</v>
       </c>
       <c r="B425" t="str">
-        <v>Identifica i display</v>
+        <v>Guadagno a un margine del display</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR is decoded and rendered by profiletool.</v>
       </c>
       <c r="B426" t="str">
-        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
+        <v>Visualizza un’immagine HDR su questo display. I file che il browser sa decodificare sono mostrati dal browser stesso; OpenEXR è decodificato e reso da profiletool.</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Drop an HDR image here, or click to choose one</v>
       </c>
       <c r="B427" t="str">
-        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
+        <v>Trascina qui un’immagine HDR o fai clic per sceglierne una</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>OpenEXR, AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
+        <v>OpenEXR, AVIF, JPEG (anche JPEG con gain map), PNG — e HEIC su Safari.</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Choose another</v>
       </c>
       <c r="B429" t="str">
-        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
+        <v>Scegli un’altra</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Could not identify displays.</v>
+        <v>Clear</v>
       </c>
       <c r="B430" t="str">
-        <v>Impossibile identificare i display.</v>
+        <v>Svuota</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Display events</v>
+        <v>Embedded ICC profile</v>
       </c>
       <c r="B431" t="str">
-        <v>Eventi del display</v>
+        <v>Profilo ICC incorporato</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>none — OpenEXR states colour through chromaticities</v>
       </c>
       <c r="B432" t="str">
-        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
+        <v>nessuno — OpenEXR indica il colore tramite le cromaticità</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Colour primaries</v>
+        <v>checking…</v>
       </c>
       <c r="B433" t="str">
-        <v>Primari di colore</v>
+        <v>verifica…</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Transfer characteristics</v>
+        <v>none</v>
       </c>
       <c r="B434" t="str">
-        <v>Caratteristiche di trasferimento</v>
+        <v>nessuno</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Matrix coefficients</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B435" t="str">
-        <v>Coefficienti di matrice</v>
+        <v>Apri nella scheda Profilo</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Video full-range flag</v>
+        <v>Gain map</v>
       </c>
       <c r="B436" t="str">
-        <v>Flag intervallo video completo</v>
+        <v>Gain map</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Full range</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B437" t="str">
-        <v>Intervallo completo</v>
+        <v>rilevata, non decodificata</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Narrow range</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B438" t="str">
-        <v>Intervallo ridotto</v>
+        <v>Non è un’immagine. Carica i profili dal pannello Profili.</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B439" t="str">
-        <v>non assegnato da ITU-T H.273</v>
+        <v>Formato immagine non riconosciuto da profiletool.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B440" t="str">
-        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
+        <v>I pixel TIFF non sono ancora mostrati qui: i browser non decodificano il TIFF e la codifica HDR in un TIFF a 16 bit non è ancora decisa (fase 4.3). Il profilo incorporato può essere esaminato.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B441" t="str">
-        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
+        <v>Impossibile mostrare questa immagine qui:</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>REPORT</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B442" t="str">
-        <v>RAPPORTO</v>
+        <v>Il profilo incorporato può comunque essere esaminato.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>FAIL</v>
+        <v>Shown by</v>
       </c>
       <c r="B443" t="str">
-        <v>NON SUPERATO</v>
+        <v>Mostrato da</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>checks</v>
+        <v>the browser</v>
       </c>
       <c r="B444" t="str">
-        <v>controlli</v>
+        <v>il browser</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>profiletool</v>
       </c>
       <c r="B445" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>HDR display</v>
       </c>
       <c r="B446" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Display HDR</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B447" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>I browser ignorano l’HDR indicato solo da un profilo ICC incorporato, quindi questa immagine può apparire spenta e piatta.</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Powered by {lib}</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B448" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Questo browser non può passare un’immagine tra SDR e HDR; è mostrata come il browser la rende.</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Subscribe</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B449" t="str">
-        <v>Iscriviti</v>
+        <v>Il browser non è riuscito a decodificare questa immagine.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Output</v>
       </c>
       <c r="B450" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Uscita</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Get notified about new releases</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B451" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Canvas HDR (float16)</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Close</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B452" t="str">
-        <v>Chiudi</v>
+        <v>WebGPU (gamma estesa)</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B453" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Canvas SDR (tone mapping)</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Email address</v>
+        <v>Size</v>
       </c>
       <c r="B454" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>Dimensioni</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>you@example.com</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B455" t="str">
-        <v>tu@esempio.com</v>
+        <v>Pixel più luminoso</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>How will you use profiletool?</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B456" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>{n}× il bianco SDR</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>(optional)</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B457" t="str">
-        <v>(opzionale)</v>
+        <v>Cromaticità</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B458" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>non indicate — si assume Rec. 709</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B459" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>{from} non è disponibile qui ({why}); si usa l’uscita successiva.</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>Cancel</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B460" t="str">
-        <v>Annulla</v>
+        <v>Questa uscita non può trasportare valori più luminosi del bianco; è mostrata la resa SDR con tone mapping.</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Subscribe</v>
+        <v>Exposure</v>
       </c>
       <c r="B461" t="str">
-        <v>Iscriviti</v>
+        <v>Esposizione</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>{n} stops</v>
       </c>
       <c r="B462" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>{n} stop</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B463" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Decodifica non riuscita:</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Close</v>
+        <v>Decoding…</v>
       </c>
       <c r="B464" t="str">
-        <v>Chiudi</v>
+        <v>Decodifica…</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Privacy notice</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B465" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Gamma dinamica</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B466" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Questo browser offre solo i due estremi, non una miscela.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B467" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>IccProfLib non applica questa curva di guadagno: {why}. Un CMM passa al descrittore di tone mapping successivo (clausola 8.10.3).</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B468" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Margine del display</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B469" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>{n} stop (≈{r}× il bianco di riferimento)</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Baseline</v>
       </c>
       <c r="B470" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Error:</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B471" t="str">
-        <v>Errore:</v>
+        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>Convert to XML</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B472" t="str">
-        <v>Converti in XML</v>
+        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Convert to JSON</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B473" t="str">
-        <v>Converti in JSON</v>
+        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>Convert to ICC</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B474" t="str">
-        <v>Converti in ICC</v>
+        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Converting to XML…</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B475" t="str">
-        <v>Conversione in XML…</v>
+        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Converting to JSON…</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B476" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Converting to ICC…</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B477" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Curva a {h} stop (nessun guadagno)</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Load ICC profile</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B478" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Curva a {h} stop</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B479" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Applicato a {h} stop</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Profile ID</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B480" t="str">
-        <v>ID profilo</v>
+        <v>Guadagno applicato a questo margine</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>No tags found.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B481" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Tag Name</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B482" t="str">
-        <v>Nome tag</v>
+        <v>Guadagno (stop log2)</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>ID</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B483" t="str">
-        <v>ID</v>
+        <v>Curva tonale dei grigi a questo margine</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Offset</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B484" t="str">
-        <v>Offset</v>
+        <v>Ingresso (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Size</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B485" t="str">
-        <v>Dimensione</v>
+        <v>Uscita (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>Pad</v>
+        <v>No change</v>
       </c>
       <c r="B486" t="str">
-        <v>Riempimento</v>
+        <v>Nessuna modifica</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Bytes changed since load</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B487" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Picco del display a {h} stop</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Type</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B488" t="str">
-        <v>Tipo</v>
+        <v>Uscita a {h} stop</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>Array of {type}</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B489" t="str">
-        <v>Array di {type}</v>
+        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>(No content)</v>
+        <v>Identify displays</v>
       </c>
       <c r="B490" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Identifica i display</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>bytes</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B491" t="str">
-        <v>byte</v>
+        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Loading full description…</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B492" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Could not load full description:</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B493" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B494" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B495" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Impossibile identificare i display.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>No validation output</v>
+        <v>Display events</v>
       </c>
       <c r="B496" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Eventi del display</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Profile is valid</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B497" t="str">
-        <v>Il profilo è valido</v>
+        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B498" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Primari di colore</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B499" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Caratteristiche di trasferimento</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Critical validation error</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B500" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Coefficienti di matrice</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Unknown validation status</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B501" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Flag intervallo video completo</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Full range</v>
       </c>
       <c r="B502" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Intervallo completo</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B503" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Intervallo ridotto</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Valid</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B504" t="str">
-        <v>Valido</v>
+        <v>non assegnato da ITU-T H.273</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Warning</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B505" t="str">
-        <v>Avviso</v>
+        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Error</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B506" t="str">
-        <v>Errore</v>
+        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Unknown</v>
+        <v>REPORT</v>
       </c>
       <c r="B507" t="str">
-        <v>Sconosciuto</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Pass</v>
+        <v>FAIL</v>
       </c>
       <c r="B508" t="str">
-        <v>Superato</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Fail</v>
+        <v>checks</v>
       </c>
       <c r="B509" t="str">
-        <v>Non superato</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>View in context</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B510" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Validation detail</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B511" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Triggered by</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B512" t="str">
-        <v>Attivato da</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Field</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B513" t="str">
-        <v>Campo</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Current value</v>
+        <v>Subscribe</v>
       </c>
       <c r="B514" t="str">
-        <v>Valore attuale</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Required: 0</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B515" t="str">
-        <v>Richiesto: 0</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Expected: {value}</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B516" t="str">
-        <v>Atteso: {value}</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Invalid</v>
+        <v>Close</v>
       </c>
       <c r="B517" t="str">
-        <v>Non valido</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B518" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B519" t="str">
-        <v>Chiudi</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Loading XML editor…</v>
+        <v>you@example.com</v>
       </c>
       <c r="B520" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Loading JSON editor…</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B521" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>(optional)</v>
       </c>
       <c r="B522" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B523" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>● unsaved XML edits</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B524" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Cancel</v>
       </c>
       <c r="B525" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B526" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B527" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>indent</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B528" t="str">
-        <v>rientro</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B529" t="str">
-        <v>ordina chiavi</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B530" t="str">
+        <v>Informativa sulla privacy</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B531" t="str">
+        <v>Inserisci un indirizzo e-mail valido.</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B532" t="str">
+        <v>Troppe richieste. Riprova più tardi.</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B533" t="str">
+        <v>Controlla il modulo e riprova.</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B534" t="str">
+        <v>Impossibile inviare la richiesta. Riprova.</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B535" t="str">
+        <v>Errore di rete. Riprova.</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B536" t="str">
+        <v>Errore:</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B537" t="str">
+        <v>Converti in XML</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B538" t="str">
+        <v>Converti in JSON</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B539" t="str">
+        <v>Converti in ICC</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B540" t="str">
+        <v>Conversione in XML…</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B541" t="str">
+        <v>Conversione in JSON…</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B542" t="str">
+        <v>Conversione in ICC…</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B543" t="str">
+        <v>Carica profilo ICC</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B544" t="str">
+        <v>Area di rilascio per i file di profilo ICC</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B545" t="str">
+        <v>ID profilo</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B546" t="str">
+        <v>Nessun tag trovato.</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B547" t="str">
+        <v>Nome tag</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B548" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B549" t="str">
+        <v>Offset</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B550" t="str">
+        <v>Dimensione</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B551" t="str">
+        <v>Riempimento</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B552" t="str">
+        <v>Byte modificati dal caricamento</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B553" t="str">
+        <v>Tipo</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B554" t="str">
+        <v>Array di {type}</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B555" t="str">
+        <v>(Nessun contenuto)</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B556" t="str">
+        <v>byte</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B557" t="str">
+        <v>Caricamento descrizione completa…</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B558" t="str">
+        <v>Impossibile caricare la descrizione completa:</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B559" t="str">
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B560" t="str">
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B561" t="str">
+        <v>Nessun output di convalida</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B562" t="str">
+        <v>Il profilo è valido</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B563" t="str">
+        <v>Il profilo presenta avvisi</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B564" t="str">
+        <v>Il profilo non è conforme</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B565" t="str">
+        <v>Errore di convalida critico</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B566" t="str">
+        <v>Stato di convalida sconosciuto</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B567" t="str">
+        <v>Critico — mostrato solo per ispezione</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B568" t="str">
+        <v>Nessun avviso o errore trovato.</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B569" t="str">
+        <v>Valido</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B570" t="str">
+        <v>Avviso</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B571" t="str">
+        <v>Errore</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B572" t="str">
+        <v>Sconosciuto</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B573" t="str">
+        <v>Superato</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B574" t="str">
+        <v>Non superato</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B575" t="str">
+        <v>Mostra nel contesto</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B576" t="str">
+        <v>Dettaglio convalida</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B577" t="str">
+        <v>Attivato da</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B578" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B579" t="str">
+        <v>Valore attuale</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B580" t="str">
+        <v>Richiesto: 0</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B581" t="str">
+        <v>Atteso: {value}</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B582" t="str">
+        <v>Non valido</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B583" t="str">
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B584" t="str">
+        <v>Chiudi</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B585" t="str">
+        <v>Caricamento editor XML…</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B586" t="str">
+        <v>Caricamento editor JSON…</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B587" t="str">
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B588" t="str">
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B589" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B590" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B591" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B592" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B593" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B594" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B530" t="str">
+      <c r="B595" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B530"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B595"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B595"/>
+  <dimension ref="A1:B612"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3894,7 +3894,7 @@
         <v>Gain map</v>
       </c>
       <c r="B436" t="str">
-        <v>Gain map</v>
+        <v>Mappa di guadagno</v>
       </c>
     </row>
     <row r="437">
@@ -4139,1039 +4139,1175 @@
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B467" t="str">
-        <v>IccProfLib non applica questa curva di guadagno: {why}. Un CMM passa al descrittore di tone mapping successivo (clausola 8.10.3).</v>
+        <v>decodificato da profiletool stesso, quindi indipendente dal browser</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>Display headroom</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B468" t="str">
-        <v>Margine del display</v>
+        <v>questo browser lo decodifica</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B469" t="str">
-        <v>{n} stop (≈{r}× il bianco di riferimento)</v>
+        <v>questo browser non lo decodifica</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Baseline</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B470" t="str">
-        <v>Base</v>
+        <v>la visualizzazione HEIC richiede Safari o un altro browser WebKit — Chrome e Firefox non decodificano HEIC su nessuna piattaforma, macOS compreso</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B471" t="str">
-        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
+        <v>la visualizzazione JPEG XL richiede Safari; gli altri browser non lo supportano ancora</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B472" t="str">
-        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
+        <v>rinviato a una versione successiva</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B473" t="str">
-        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
+        <v>questo display non segnala alcun percorso HDR, quindi l’HDR è reso in SDR con tone mapping</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B474" t="str">
-        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
+        <v>questo browser non offre un canvas HDR (serve canvas float16 o WebGPU)</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B475" t="str">
-        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
+        <v>Firefox non mostra immagini HDR e non legge gain map; i contenuti HDR sono mostrati in SDR</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B476" t="str">
-        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
+        <v>l’ispezione richiede solo l’analisi del contenitore, non un codec</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B477" t="str">
-        <v>Curva a {h} stop (nessun guadagno)</v>
+        <v>display HDR e canvas HDR sono entrambi disponibili</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>Curve at {h} stops</v>
+        <v>unknown format</v>
       </c>
       <c r="B478" t="str">
-        <v>Curva a {h} stop</v>
+        <v>formato sconosciuto</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>Applied at {h} stops</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B479" t="str">
-        <v>Applicato a {h} stop</v>
+        <v>{browser} su {os}</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B480" t="str">
-        <v>Guadagno applicato a questo margine</v>
+        <v>{name} · display HDR rilevato</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B481" t="str">
-        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
+        <v>{name} · display SDR</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B482" t="str">
-        <v>Guadagno (stop log2)</v>
+        <v>WebGPU ha applicato il tone mapping «{mode}», quindi l’uscita è limitata a SDR</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B483" t="str">
-        <v>Curva tonale dei grigi a questo margine</v>
+        <v>Questo browser non indica il tone mapping WebGPU applicato, quindi l’uscita HDR non è confermata</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B484" t="str">
-        <v>Ingresso (× bianco di riferimento HDR)</v>
+        <v>IccProfLib non applica questa curva di guadagno: {why}. Un CMM passa al descrittore di tone mapping successivo (clausola 8.10.3).</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B485" t="str">
-        <v>Uscita (× bianco di riferimento HDR)</v>
+        <v>Margine del display</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>No change</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B486" t="str">
-        <v>Nessuna modifica</v>
+        <v>{n} stop (≈{r}× il bianco di riferimento)</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Baseline</v>
       </c>
       <c r="B487" t="str">
-        <v>Picco del display a {h} stop</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Output at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B488" t="str">
-        <v>Uscita a {h} stop</v>
+        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B489" t="str">
-        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
+        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Identify displays</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B490" t="str">
-        <v>Identifica i display</v>
+        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B491" t="str">
-        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
+        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B492" t="str">
-        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
+        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B493" t="str">
-        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
+        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B494" t="str">
-        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
+        <v>Curva a {h} stop (nessun guadagno)</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Could not identify displays.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B495" t="str">
-        <v>Impossibile identificare i display.</v>
+        <v>Curva a {h} stop</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Display events</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B496" t="str">
-        <v>Eventi del display</v>
+        <v>Applicato a {h} stop</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B497" t="str">
-        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
+        <v>Guadagno applicato a questo margine</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Colour primaries</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B498" t="str">
-        <v>Primari di colore</v>
+        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Transfer characteristics</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B499" t="str">
-        <v>Caratteristiche di trasferimento</v>
+        <v>Guadagno (stop log2)</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Matrix coefficients</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B500" t="str">
-        <v>Coefficienti di matrice</v>
+        <v>Curva tonale dei grigi a questo margine</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Video full-range flag</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B501" t="str">
-        <v>Flag intervallo video completo</v>
+        <v>Ingresso (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Full range</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B502" t="str">
-        <v>Intervallo completo</v>
+        <v>Uscita (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Narrow range</v>
+        <v>No change</v>
       </c>
       <c r="B503" t="str">
-        <v>Intervallo ridotto</v>
+        <v>Nessuna modifica</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B504" t="str">
-        <v>non assegnato da ITU-T H.273</v>
+        <v>Picco del display a {h} stop</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B505" t="str">
-        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
+        <v>Uscita a {h} stop</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B506" t="str">
-        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
+        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>REPORT</v>
+        <v>Identify displays</v>
       </c>
       <c r="B507" t="str">
-        <v>RAPPORTO</v>
+        <v>Identifica i display</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>FAIL</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B508" t="str">
-        <v>NON SUPERATO</v>
+        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>checks</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B509" t="str">
-        <v>controlli</v>
+        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B510" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B511" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B512" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Impossibile identificare i display.</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Powered by {lib}</v>
+        <v>Display events</v>
       </c>
       <c r="B513" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Eventi del display</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Subscribe</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B514" t="str">
-        <v>Iscriviti</v>
+        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B515" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Primari di colore</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Get notified about new releases</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B516" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Caratteristiche di trasferimento</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Close</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B517" t="str">
-        <v>Chiudi</v>
+        <v>Coefficienti di matrice</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B518" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Flag intervallo video completo</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Email address</v>
+        <v>Full range</v>
       </c>
       <c r="B519" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>Intervallo completo</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>you@example.com</v>
+        <v>Narrow range</v>
       </c>
       <c r="B520" t="str">
-        <v>tu@esempio.com</v>
+        <v>Intervallo ridotto</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>How will you use profiletool?</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B521" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>non assegnato da ITU-T H.273</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>(optional)</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B522" t="str">
-        <v>(opzionale)</v>
+        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B523" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B524" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B525" t="str">
-        <v>Annulla</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B526" t="str">
-        <v>Iscriviti</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B527" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B528" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B529" t="str">
-        <v>Chiudi</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B530" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B531" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B532" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B533" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B534" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B535" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B536" t="str">
-        <v>Errore:</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B537" t="str">
-        <v>Converti in XML</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B538" t="str">
-        <v>Converti in JSON</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B539" t="str">
-        <v>Converti in ICC</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B540" t="str">
-        <v>Conversione in XML…</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B541" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B542" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B543" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B544" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B545" t="str">
-        <v>ID profilo</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B546" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B547" t="str">
-        <v>Nome tag</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B548" t="str">
-        <v>ID</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B549" t="str">
-        <v>Offset</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B550" t="str">
-        <v>Dimensione</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B551" t="str">
-        <v>Riempimento</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B552" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B553" t="str">
-        <v>Tipo</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B554" t="str">
-        <v>Array di {type}</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B555" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B556" t="str">
-        <v>byte</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B557" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B558" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B559" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B560" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B561" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B562" t="str">
-        <v>Il profilo è valido</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B563" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B564" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B565" t="str">
-        <v>Errore di convalida critico</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B566" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B567" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B568" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B569" t="str">
-        <v>Valido</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B570" t="str">
-        <v>Avviso</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B571" t="str">
-        <v>Errore</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B572" t="str">
-        <v>Sconosciuto</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B573" t="str">
-        <v>Superato</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B574" t="str">
-        <v>Non superato</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B575" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B576" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B577" t="str">
-        <v>Attivato da</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B578" t="str">
-        <v>Campo</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B579" t="str">
-        <v>Valore attuale</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B580" t="str">
-        <v>Richiesto: 0</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B581" t="str">
-        <v>Atteso: {value}</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B582" t="str">
-        <v>Non valido</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B583" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B584" t="str">
-        <v>Chiudi</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B585" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B586" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B587" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B588" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B589" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B590" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B591" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B592" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B593" t="str">
-        <v>rientro</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B594" t="str">
-        <v>ordina chiavi</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B595" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B596" t="str">
+        <v>Valore attuale</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B597" t="str">
+        <v>Richiesto: 0</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B598" t="str">
+        <v>Atteso: {value}</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B599" t="str">
+        <v>Non valido</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B600" t="str">
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B601" t="str">
+        <v>Chiudi</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B602" t="str">
+        <v>Caricamento editor XML…</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B603" t="str">
+        <v>Caricamento editor JSON…</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B604" t="str">
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B605" t="str">
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B606" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B607" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B608" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B609" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B610" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B611" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B595" t="str">
+      <c r="B612" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B595"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B612"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B612"/>
+  <dimension ref="A1:B625"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4275,1039 +4275,1143 @@
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Display peak</v>
       </c>
       <c r="B484" t="str">
-        <v>IccProfLib non applica questa curva di guadagno: {why}. Un CMM passa al descrittore di tone mapping successivo (clausola 8.10.3).</v>
+        <v>Picco del display</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Display headroom</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B485" t="str">
-        <v>Margine del display</v>
+        <v>{r}× il bianco SDR ({n} stop)</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B486" t="str">
-        <v>{n} stop (≈{r}× il bianco di riferimento)</v>
+        <v>1× — display SDR</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>Baseline</v>
+        <v>not known</v>
       </c>
       <c r="B487" t="str">
-        <v>Base</v>
+        <v>non noto</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B488" t="str">
-        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
+        <v>Questo display non segnala HDR, quindi il browser mostra l’immagine in SDR a entrambi gli estremi.</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B489" t="str">
-        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
+        <v>Questo display non segnala HDR, quindi tutto ciò che supera il bianco SDR viene tagliato. «Adatta al display» mostra invece la resa con tone mapping.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B490" t="str">
-        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
+        <v>Questa immagine richiede {img}× il bianco SDR, ma questo display arriva solo a {disp}×, quindi i valori più luminosi vengono tagliati. «Adatta al display» li attenua verso il picco del display.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Fit to display</v>
       </c>
       <c r="B491" t="str">
-        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
+        <v>Adatta al display</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B492" t="str">
-        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
+        <v>Limita la luminosità al picco segnalato dal display. Su Windows questo valore può restare indietro rispetto ai cambi di luminosità.</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>no limit</v>
       </c>
       <c r="B493" t="str">
-        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
+        <v>nessun limite</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B494" t="str">
-        <v>Curva a {h} stop (nessun guadagno)</v>
+        <v>limite {n} stop ({r}×)</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>Curve at {h} stops</v>
+        <v>SDR white</v>
       </c>
       <c r="B495" t="str">
-        <v>Curva a {h} stop</v>
+        <v>Bianco SDR</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B496" t="str">
-        <v>Applicato a {h} stop</v>
+        <v>Bianco SDR semplice, per confronto. Su un display HDR le alte luci HDR appaiono più luminose di questo.</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B497" t="str">
-        <v>Guadagno applicato a questo margine</v>
+        <v>IccProfLib non applica questa curva di guadagno: {why}. Un CMM passa al descrittore di tone mapping successivo (clausola 8.10.3).</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B498" t="str">
-        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
+        <v>Margine del display</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B499" t="str">
-        <v>Guadagno (stop log2)</v>
+        <v>{n} stop (≈{r}× il bianco di riferimento)</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Baseline</v>
       </c>
       <c r="B500" t="str">
-        <v>Curva tonale dei grigi a questo margine</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B501" t="str">
-        <v>Ingresso (× bianco di riferimento HDR)</v>
+        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B502" t="str">
-        <v>Uscita (× bianco di riferimento HDR)</v>
+        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>No change</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B503" t="str">
-        <v>Nessuna modifica</v>
+        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B504" t="str">
-        <v>Picco del display a {h} stop</v>
+        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Output at {h} stops</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B505" t="str">
-        <v>Uscita a {h} stop</v>
+        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B506" t="str">
-        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
+        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Identify displays</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B507" t="str">
-        <v>Identifica i display</v>
+        <v>Curva a {h} stop (nessun guadagno)</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B508" t="str">
-        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
+        <v>Curva a {h} stop</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B509" t="str">
-        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
+        <v>Applicato a {h} stop</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B510" t="str">
-        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
+        <v>Guadagno applicato a questo margine</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B511" t="str">
-        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
+        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Could not identify displays.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B512" t="str">
-        <v>Impossibile identificare i display.</v>
+        <v>Guadagno (stop log2)</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Display events</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B513" t="str">
-        <v>Eventi del display</v>
+        <v>Curva tonale dei grigi a questo margine</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B514" t="str">
-        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
+        <v>Ingresso (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Colour primaries</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B515" t="str">
-        <v>Primari di colore</v>
+        <v>Uscita (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Transfer characteristics</v>
+        <v>No change</v>
       </c>
       <c r="B516" t="str">
-        <v>Caratteristiche di trasferimento</v>
+        <v>Nessuna modifica</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Matrix coefficients</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B517" t="str">
-        <v>Coefficienti di matrice</v>
+        <v>Picco del display a {h} stop</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Video full-range flag</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B518" t="str">
-        <v>Flag intervallo video completo</v>
+        <v>Uscita a {h} stop</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Full range</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B519" t="str">
-        <v>Intervallo completo</v>
+        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Narrow range</v>
+        <v>Identify displays</v>
       </c>
       <c r="B520" t="str">
-        <v>Intervallo ridotto</v>
+        <v>Identifica i display</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B521" t="str">
-        <v>non assegnato da ITU-T H.273</v>
+        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B522" t="str">
-        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
+        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B523" t="str">
-        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
+        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>REPORT</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B524" t="str">
-        <v>RAPPORTO</v>
+        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>FAIL</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B525" t="str">
-        <v>NON SUPERATO</v>
+        <v>Impossibile identificare i display.</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>checks</v>
+        <v>Display events</v>
       </c>
       <c r="B526" t="str">
-        <v>controlli</v>
+        <v>Eventi del display</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B527" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B528" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Primari di colore</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B529" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Caratteristiche di trasferimento</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Powered by {lib}</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B530" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Coefficienti di matrice</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Subscribe</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B531" t="str">
-        <v>Iscriviti</v>
+        <v>Flag intervallo video completo</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Full range</v>
       </c>
       <c r="B532" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Intervallo completo</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Get notified about new releases</v>
+        <v>Narrow range</v>
       </c>
       <c r="B533" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Intervallo ridotto</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Close</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B534" t="str">
-        <v>Chiudi</v>
+        <v>non assegnato da ITU-T H.273</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B535" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Email address</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B536" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>you@example.com</v>
+        <v>REPORT</v>
       </c>
       <c r="B537" t="str">
-        <v>tu@esempio.com</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>How will you use profiletool?</v>
+        <v>FAIL</v>
       </c>
       <c r="B538" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>(optional)</v>
+        <v>checks</v>
       </c>
       <c r="B539" t="str">
-        <v>(opzionale)</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B540" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B541" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Cancel</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B542" t="str">
-        <v>Annulla</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B543" t="str">
-        <v>Iscriviti</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B544" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B545" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B546" t="str">
-        <v>Chiudi</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B547" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B548" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Email address</v>
       </c>
       <c r="B549" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Please check the form and try again.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B550" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B551" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Network error. Please try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B552" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Error:</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B553" t="str">
-        <v>Errore:</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Convert to XML</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B554" t="str">
-        <v>Converti in XML</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Convert to JSON</v>
+        <v>Cancel</v>
       </c>
       <c r="B555" t="str">
-        <v>Converti in JSON</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Convert to ICC</v>
+        <v>Subscribe</v>
       </c>
       <c r="B556" t="str">
-        <v>Converti in ICC</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Converting to XML…</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B557" t="str">
-        <v>Conversione in XML…</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Converting to JSON…</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B558" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Converting to ICC…</v>
+        <v>Close</v>
       </c>
       <c r="B559" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Load ICC profile</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B560" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B561" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Profile ID</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B562" t="str">
-        <v>ID profilo</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>No tags found.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B563" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Tag Name</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B564" t="str">
-        <v>Nome tag</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B565" t="str">
-        <v>ID</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Offset</v>
+        <v>Error:</v>
       </c>
       <c r="B566" t="str">
-        <v>Offset</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Size</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B567" t="str">
-        <v>Dimensione</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Pad</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B568" t="str">
-        <v>Riempimento</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Bytes changed since load</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B569" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Type</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B570" t="str">
-        <v>Tipo</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Array of {type}</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B571" t="str">
-        <v>Array di {type}</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>(No content)</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B572" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>bytes</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B573" t="str">
-        <v>byte</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Loading full description…</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B574" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Could not load full description:</v>
+        <v>Profile ID</v>
       </c>
       <c r="B575" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>No tags found.</v>
       </c>
       <c r="B576" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B577" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>No validation output</v>
+        <v>ID</v>
       </c>
       <c r="B578" t="str">
-        <v>Nessun output di convalida</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Profile is valid</v>
+        <v>Offset</v>
       </c>
       <c r="B579" t="str">
-        <v>Il profilo è valido</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Size</v>
       </c>
       <c r="B580" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Pad</v>
       </c>
       <c r="B581" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Critical validation error</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B582" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Unknown validation status</v>
+        <v>Type</v>
       </c>
       <c r="B583" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B584" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>No warnings or errors found.</v>
+        <v>(No content)</v>
       </c>
       <c r="B585" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Valid</v>
+        <v>bytes</v>
       </c>
       <c r="B586" t="str">
-        <v>Valido</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Warning</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B587" t="str">
-        <v>Avviso</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Error</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B588" t="str">
-        <v>Errore</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Unknown</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B589" t="str">
-        <v>Sconosciuto</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Pass</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B590" t="str">
-        <v>Superato</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Fail</v>
+        <v>No validation output</v>
       </c>
       <c r="B591" t="str">
-        <v>Non superato</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>View in context</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B592" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Validation detail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B593" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Triggered by</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B594" t="str">
-        <v>Attivato da</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Field</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B595" t="str">
-        <v>Campo</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Current value</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B596" t="str">
-        <v>Valore attuale</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Required: 0</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B597" t="str">
-        <v>Richiesto: 0</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Expected: {value}</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B598" t="str">
-        <v>Atteso: {value}</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Invalid</v>
+        <v>Valid</v>
       </c>
       <c r="B599" t="str">
-        <v>Non valido</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Warning</v>
       </c>
       <c r="B600" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Close</v>
+        <v>Error</v>
       </c>
       <c r="B601" t="str">
-        <v>Chiudi</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Loading XML editor…</v>
+        <v>Unknown</v>
       </c>
       <c r="B602" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Pass</v>
       </c>
       <c r="B603" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Fail</v>
       </c>
       <c r="B604" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>View in context</v>
       </c>
       <c r="B605" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Validation detail</v>
       </c>
       <c r="B606" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Triggered by</v>
       </c>
       <c r="B607" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Field</v>
       </c>
       <c r="B608" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Current value</v>
       </c>
       <c r="B609" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>indent</v>
+        <v>Required: 0</v>
       </c>
       <c r="B610" t="str">
-        <v>rientro</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>sort keys</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B611" t="str">
-        <v>ordina chiavi</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B612" t="str">
+        <v>Non valido</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B613" t="str">
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B614" t="str">
+        <v>Chiudi</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B615" t="str">
+        <v>Caricamento editor XML…</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B616" t="str">
+        <v>Caricamento editor JSON…</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B617" t="str">
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B618" t="str">
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B619" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B620" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B621" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B622" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B623" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B624" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B612" t="str">
+      <c r="B625" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B612"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B625"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B625"/>
+  <dimension ref="A1:B627"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4379,1039 +4379,1055 @@
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B497" t="str">
-        <v>IccProfLib non applica questa curva di guadagno: {why}. Un CMM passa al descrittore di tone mapping successivo (clausola 8.10.3).</v>
+        <v>Riquadro bianco SDR</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Display headroom</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B498" t="str">
-        <v>Margine del display</v>
+        <v>Trascinalo per spostarlo; doppio clic per rimetterlo accanto all’immagine.</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B499" t="str">
-        <v>{n} stop (≈{r}× il bianco di riferimento)</v>
+        <v>IccProfLib non applica questa curva di guadagno: {why}. Un CMM passa al descrittore di tone mapping successivo (clausola 8.10.3).</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Baseline</v>
+        <v>Display headroom</v>
       </c>
       <c r="B500" t="str">
-        <v>Base</v>
+        <v>Margine del display</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B501" t="str">
-        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
+        <v>{n} stop (≈{r}× il bianco di riferimento)</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Baseline</v>
       </c>
       <c r="B502" t="str">
-        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B503" t="str">
-        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
+        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B504" t="str">
-        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
+        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B505" t="str">
-        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
+        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B506" t="str">
-        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
+        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B507" t="str">
-        <v>Curva a {h} stop (nessun guadagno)</v>
+        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Curve at {h} stops</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B508" t="str">
-        <v>Curva a {h} stop</v>
+        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B509" t="str">
-        <v>Applicato a {h} stop</v>
+        <v>Curva a {h} stop (nessun guadagno)</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B510" t="str">
-        <v>Guadagno applicato a questo margine</v>
+        <v>Curva a {h} stop</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B511" t="str">
-        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
+        <v>Applicato a {h} stop</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B512" t="str">
-        <v>Guadagno (stop log2)</v>
+        <v>Guadagno applicato a questo margine</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B513" t="str">
-        <v>Curva tonale dei grigi a questo margine</v>
+        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B514" t="str">
-        <v>Ingresso (× bianco di riferimento HDR)</v>
+        <v>Guadagno (stop log2)</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B515" t="str">
-        <v>Uscita (× bianco di riferimento HDR)</v>
+        <v>Curva tonale dei grigi a questo margine</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>No change</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B516" t="str">
-        <v>Nessuna modifica</v>
+        <v>Ingresso (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B517" t="str">
-        <v>Picco del display a {h} stop</v>
+        <v>Uscita (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Output at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B518" t="str">
-        <v>Uscita a {h} stop</v>
+        <v>Nessuna modifica</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B519" t="str">
-        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
+        <v>Picco del display a {h} stop</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Identify displays</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B520" t="str">
-        <v>Identifica i display</v>
+        <v>Uscita a {h} stop</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B521" t="str">
-        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
+        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B522" t="str">
-        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
+        <v>Identifica i display</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B523" t="str">
-        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
+        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B524" t="str">
-        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
+        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Could not identify displays.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B525" t="str">
-        <v>Impossibile identificare i display.</v>
+        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Display events</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B526" t="str">
-        <v>Eventi del display</v>
+        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B527" t="str">
-        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
+        <v>Impossibile identificare i display.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Colour primaries</v>
+        <v>Display events</v>
       </c>
       <c r="B528" t="str">
-        <v>Primari di colore</v>
+        <v>Eventi del display</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Transfer characteristics</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B529" t="str">
-        <v>Caratteristiche di trasferimento</v>
+        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Matrix coefficients</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B530" t="str">
-        <v>Coefficienti di matrice</v>
+        <v>Primari di colore</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Video full-range flag</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B531" t="str">
-        <v>Flag intervallo video completo</v>
+        <v>Caratteristiche di trasferimento</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Full range</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B532" t="str">
-        <v>Intervallo completo</v>
+        <v>Coefficienti di matrice</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Narrow range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B533" t="str">
-        <v>Intervallo ridotto</v>
+        <v>Flag intervallo video completo</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Full range</v>
       </c>
       <c r="B534" t="str">
-        <v>non assegnato da ITU-T H.273</v>
+        <v>Intervallo completo</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B535" t="str">
-        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
+        <v>Intervallo ridotto</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B536" t="str">
-        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
+        <v>non assegnato da ITU-T H.273</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>REPORT</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B537" t="str">
-        <v>RAPPORTO</v>
+        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>FAIL</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B538" t="str">
-        <v>NON SUPERATO</v>
+        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>checks</v>
+        <v>REPORT</v>
       </c>
       <c r="B539" t="str">
-        <v>controlli</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>FAIL</v>
       </c>
       <c r="B540" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>checks</v>
       </c>
       <c r="B541" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B542" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B543" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Subscribe</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B544" t="str">
-        <v>Iscriviti</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B545" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Get notified about new releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B546" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Close</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B547" t="str">
-        <v>Chiudi</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B548" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Email address</v>
+        <v>Close</v>
       </c>
       <c r="B549" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>you@example.com</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B550" t="str">
-        <v>tu@esempio.com</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Email address</v>
       </c>
       <c r="B551" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>(optional)</v>
+        <v>you@example.com</v>
       </c>
       <c r="B552" t="str">
-        <v>(opzionale)</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B553" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>(optional)</v>
       </c>
       <c r="B554" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Cancel</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B555" t="str">
-        <v>Annulla</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Subscribe</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B556" t="str">
-        <v>Iscriviti</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Cancel</v>
       </c>
       <c r="B557" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B558" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Close</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B559" t="str">
-        <v>Chiudi</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Privacy notice</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B560" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Close</v>
       </c>
       <c r="B561" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B562" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B563" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B564" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B565" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Error:</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B566" t="str">
-        <v>Errore:</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Convert to XML</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B567" t="str">
-        <v>Converti in XML</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Convert to JSON</v>
+        <v>Error:</v>
       </c>
       <c r="B568" t="str">
-        <v>Converti in JSON</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B569" t="str">
-        <v>Converti in ICC</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B570" t="str">
-        <v>Conversione in XML…</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B571" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B572" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B573" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B574" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Profile ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B575" t="str">
-        <v>ID profilo</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>No tags found.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B576" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Tag Name</v>
+        <v>Profile ID</v>
       </c>
       <c r="B577" t="str">
-        <v>Nome tag</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B578" t="str">
-        <v>ID</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Offset</v>
+        <v>Tag Name</v>
       </c>
       <c r="B579" t="str">
-        <v>Offset</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Size</v>
+        <v>ID</v>
       </c>
       <c r="B580" t="str">
-        <v>Dimensione</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Pad</v>
+        <v>Offset</v>
       </c>
       <c r="B581" t="str">
-        <v>Riempimento</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Bytes changed since load</v>
+        <v>Size</v>
       </c>
       <c r="B582" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Type</v>
+        <v>Pad</v>
       </c>
       <c r="B583" t="str">
-        <v>Tipo</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Array of {type}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B584" t="str">
-        <v>Array di {type}</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>(No content)</v>
+        <v>Type</v>
       </c>
       <c r="B585" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>bytes</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B586" t="str">
-        <v>byte</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Loading full description…</v>
+        <v>(No content)</v>
       </c>
       <c r="B587" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Could not load full description:</v>
+        <v>bytes</v>
       </c>
       <c r="B588" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B589" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B590" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B591" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Profile is valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B592" t="str">
-        <v>Il profilo è valido</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No validation output</v>
       </c>
       <c r="B593" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B594" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Critical validation error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B595" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B596" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B597" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B598" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Valid</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B599" t="str">
-        <v>Valido</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B600" t="str">
-        <v>Avviso</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B601" t="str">
-        <v>Errore</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B602" t="str">
-        <v>Sconosciuto</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Pass</v>
+        <v>Error</v>
       </c>
       <c r="B603" t="str">
-        <v>Superato</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Fail</v>
+        <v>Unknown</v>
       </c>
       <c r="B604" t="str">
-        <v>Non superato</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>View in context</v>
+        <v>Pass</v>
       </c>
       <c r="B605" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Validation detail</v>
+        <v>Fail</v>
       </c>
       <c r="B606" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B607" t="str">
-        <v>Attivato da</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B608" t="str">
-        <v>Campo</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B609" t="str">
-        <v>Valore attuale</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B610" t="str">
-        <v>Richiesto: 0</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B611" t="str">
-        <v>Atteso: {value}</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B612" t="str">
-        <v>Non valido</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B613" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B614" t="str">
-        <v>Chiudi</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B615" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B616" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B617" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Caricamento editor XML…</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B618" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Caricamento editor JSON…</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B619" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B620" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B621" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● modifiche XML non salvate</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B622" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>● modifiche JSON non salvate</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B623" t="str">
-        <v>rientro</v>
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B624" t="str">
-        <v>ordina chiavi</v>
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B625" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B626" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B625" t="str">
+      <c r="B627" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B625"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B627"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B627"/>
+  <dimension ref="A1:B650"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4395,1039 +4395,1223 @@
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Assign profile</v>
       </c>
       <c r="B499" t="str">
-        <v>IccProfLib non applica questa curva di guadagno: {why}. Un CMM passa al descrittore di tone mapping successivo (clausola 8.10.3).</v>
+        <v>Assegna profilo</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Display headroom</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B500" t="str">
-        <v>Margine del display</v>
+        <v>Nessuno — secondo il file</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B501" t="str">
-        <v>{n} stop (≈{r}× il bianco di riferimento)</v>
+        <v>Profilo incorporato ({n} B)</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B502" t="str">
-        <v>Base</v>
+        <v>Profili HDR nel pool</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Profile</v>
       </c>
       <c r="B503" t="str">
-        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
+        <v>Profilo</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>embedded profile</v>
       </c>
       <c r="B504" t="str">
-        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
+        <v>profilo incorporato</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B505" t="str">
-        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
+        <v>Percorso del motore colore</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B506" t="str">
-        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
+        <v>Percorso HDR, curva di guadagno applicata</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B507" t="str">
-        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
+        <v>Percorso HDR, nessuna curva di guadagno</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B508" t="str">
-        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
+        <v>AToB0 precalcolato — non il percorso HDR</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>Transfer</v>
       </c>
       <c r="B509" t="str">
-        <v>Curva a {h} stop (nessun guadagno)</v>
+        <v>Trasferimento</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Curve at {h} stops</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B510" t="str">
-        <v>Curva a {h} stop</v>
+        <v>Bianco di riferimento HDR</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Target headroom</v>
       </c>
       <c r="B511" t="str">
-        <v>Applicato a {h} stop</v>
+        <v>Margine di destinazione</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B512" t="str">
-        <v>Guadagno applicato a questo margine</v>
+        <v>{r}× il bianco di riferimento ({n} stop)</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B513" t="str">
-        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
+        <v>Tone mapping</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B514" t="str">
-        <v>Guadagno (stop log2)</v>
+        <v>Auto (classifica della clausola 8.10.3)</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B515" t="str">
-        <v>Curva tonale dei grigi a questo margine</v>
+        <v>Curva di guadagno (HAGC)</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B516" t="str">
-        <v>Ingresso (× bianco di riferimento HDR)</v>
+        <v>Ripiego SDR precalcolato (AToB0)</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B517" t="str">
-        <v>Uscita (× bianco di riferimento HDR)</v>
+        <v>Disattivato — come un CMM precedente all’emendamento</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>No change</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B518" t="str">
-        <v>Nessuna modifica</v>
+        <v>Applicazione del profilo…</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>OpenEXR holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B519" t="str">
-        <v>Picco del display a {h} stop</v>
+        <v>OpenEXR contiene luce lineare, quindi serve un profilo con trasferimento Linear (8).</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Output at {h} stops</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B520" t="str">
-        <v>Uscita a {h} stop</v>
+        <v>Per assegnare un profilo serve un’immagine RGB a 3 canali.</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B521" t="str">
-        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
+        <v>Per interpretarne i valori, assegna un profilo qui sopra.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Identify displays</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B522" t="str">
-        <v>Identifica i display</v>
+        <v>IccProfLib non applica questa curva di guadagno: {why}. Un CMM passa al descrittore di tone mapping successivo (clausola 8.10.3).</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B523" t="str">
-        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
+        <v>Margine del display</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B524" t="str">
-        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
+        <v>{n} stop (≈{r}× il bianco di riferimento)</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Baseline</v>
       </c>
       <c r="B525" t="str">
-        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B526" t="str">
-        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
+        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Could not identify displays.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B527" t="str">
-        <v>Impossibile identificare i display.</v>
+        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Display events</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B528" t="str">
-        <v>Eventi del display</v>
+        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B529" t="str">
-        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
+        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Colour primaries</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B530" t="str">
-        <v>Primari di colore</v>
+        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Transfer characteristics</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B531" t="str">
-        <v>Caratteristiche di trasferimento</v>
+        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Matrix coefficients</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B532" t="str">
-        <v>Coefficienti di matrice</v>
+        <v>Curva a {h} stop (nessun guadagno)</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Video full-range flag</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B533" t="str">
-        <v>Flag intervallo video completo</v>
+        <v>Curva a {h} stop</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Full range</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B534" t="str">
-        <v>Intervallo completo</v>
+        <v>Applicato a {h} stop</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Narrow range</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B535" t="str">
-        <v>Intervallo ridotto</v>
+        <v>Guadagno applicato a questo margine</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B536" t="str">
-        <v>non assegnato da ITU-T H.273</v>
+        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B537" t="str">
-        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
+        <v>Guadagno (stop log2)</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B538" t="str">
-        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
+        <v>Curva tonale dei grigi a questo margine</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>REPORT</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B539" t="str">
-        <v>RAPPORTO</v>
+        <v>Ingresso (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>FAIL</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B540" t="str">
-        <v>NON SUPERATO</v>
+        <v>Uscita (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>checks</v>
+        <v>No change</v>
       </c>
       <c r="B541" t="str">
-        <v>controlli</v>
+        <v>Nessuna modifica</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>Picco del display a {h} stop</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B543" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Uscita a {h} stop</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B544" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Powered by {lib}</v>
+        <v>Identify displays</v>
       </c>
       <c r="B545" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Identifica i display</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Subscribe</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B546" t="str">
-        <v>Iscriviti</v>
+        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B547" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Get notified about new releases</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B548" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Close</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B549" t="str">
-        <v>Chiudi</v>
+        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B550" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Impossibile identificare i display.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Email address</v>
+        <v>Display events</v>
       </c>
       <c r="B551" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>Eventi del display</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>you@example.com</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B552" t="str">
-        <v>tu@esempio.com</v>
+        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B553" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>Primari di colore</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>(optional)</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B554" t="str">
-        <v>(opzionale)</v>
+        <v>Caratteristiche di trasferimento</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B555" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>Coefficienti di matrice</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B556" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>Flag intervallo video completo</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Cancel</v>
+        <v>Full range</v>
       </c>
       <c r="B557" t="str">
-        <v>Annulla</v>
+        <v>Intervallo completo</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B558" t="str">
-        <v>Iscriviti</v>
+        <v>Intervallo ridotto</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B559" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>non assegnato da ITU-T H.273</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B560" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B561" t="str">
-        <v>Chiudi</v>
+        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Privacy notice</v>
+        <v>REPORT</v>
       </c>
       <c r="B562" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>FAIL</v>
       </c>
       <c r="B563" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>checks</v>
       </c>
       <c r="B564" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B565" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B566" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Network error. Please try again.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B567" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Error:</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B568" t="str">
-        <v>Errore:</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B569" t="str">
-        <v>Converti in XML</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Convert to JSON</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B570" t="str">
-        <v>Converti in JSON</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Convert to ICC</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B571" t="str">
-        <v>Converti in ICC</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B572" t="str">
-        <v>Conversione in XML…</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Converting to JSON…</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B573" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Converting to ICC…</v>
+        <v>Email address</v>
       </c>
       <c r="B574" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Load ICC profile</v>
+        <v>you@example.com</v>
       </c>
       <c r="B575" t="str">
-        <v>Carica profilo ICC</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B576" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Profile ID</v>
+        <v>(optional)</v>
       </c>
       <c r="B577" t="str">
-        <v>ID profilo</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>No tags found.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B578" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Tag Name</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B579" t="str">
-        <v>Nome tag</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B580" t="str">
-        <v>ID</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Offset</v>
+        <v>Subscribe</v>
       </c>
       <c r="B581" t="str">
-        <v>Offset</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Size</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B582" t="str">
-        <v>Dimensione</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Pad</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B583" t="str">
-        <v>Riempimento</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Bytes changed since load</v>
+        <v>Close</v>
       </c>
       <c r="B584" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Type</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B585" t="str">
-        <v>Tipo</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Array of {type}</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B586" t="str">
-        <v>Array di {type}</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>(No content)</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B587" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>bytes</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B588" t="str">
-        <v>byte</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Loading full description…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B589" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Could not load full description:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B590" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error:</v>
       </c>
       <c r="B591" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B592" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>No validation output</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B593" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Profile is valid</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B594" t="str">
-        <v>Il profilo è valido</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B595" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B596" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Critical validation error</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B597" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Unknown validation status</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B598" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B599" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B600" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Valid</v>
+        <v>No tags found.</v>
       </c>
       <c r="B601" t="str">
-        <v>Valido</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Warning</v>
+        <v>Tag Name</v>
       </c>
       <c r="B602" t="str">
-        <v>Avviso</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Error</v>
+        <v>ID</v>
       </c>
       <c r="B603" t="str">
-        <v>Errore</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Unknown</v>
+        <v>Offset</v>
       </c>
       <c r="B604" t="str">
-        <v>Sconosciuto</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Pass</v>
+        <v>Size</v>
       </c>
       <c r="B605" t="str">
-        <v>Superato</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Fail</v>
+        <v>Pad</v>
       </c>
       <c r="B606" t="str">
-        <v>Non superato</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>View in context</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B607" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Validation detail</v>
+        <v>Type</v>
       </c>
       <c r="B608" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Triggered by</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B609" t="str">
-        <v>Attivato da</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Field</v>
+        <v>(No content)</v>
       </c>
       <c r="B610" t="str">
-        <v>Campo</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Current value</v>
+        <v>bytes</v>
       </c>
       <c r="B611" t="str">
-        <v>Valore attuale</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Required: 0</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B612" t="str">
-        <v>Richiesto: 0</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B613" t="str">
-        <v>Atteso: {value}</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Invalid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B614" t="str">
-        <v>Non valido</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B615" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Close</v>
+        <v>No validation output</v>
       </c>
       <c r="B616" t="str">
-        <v>Chiudi</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Loading XML editor…</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B617" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B618" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B619" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B620" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B621" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B622" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B623" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Valid</v>
       </c>
       <c r="B624" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>indent</v>
+        <v>Warning</v>
       </c>
       <c r="B625" t="str">
-        <v>rientro</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>sort keys</v>
+        <v>Error</v>
       </c>
       <c r="B626" t="str">
-        <v>ordina chiavi</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B627" t="str">
+        <v>Sconosciuto</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B628" t="str">
+        <v>Superato</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B629" t="str">
+        <v>Non superato</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B630" t="str">
+        <v>Mostra nel contesto</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B631" t="str">
+        <v>Dettaglio convalida</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B632" t="str">
+        <v>Attivato da</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B633" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B634" t="str">
+        <v>Valore attuale</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B635" t="str">
+        <v>Richiesto: 0</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B636" t="str">
+        <v>Atteso: {value}</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B637" t="str">
+        <v>Non valido</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B638" t="str">
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B639" t="str">
+        <v>Chiudi</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B640" t="str">
+        <v>Caricamento editor XML…</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B641" t="str">
+        <v>Caricamento editor JSON…</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B642" t="str">
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B643" t="str">
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B644" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B645" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B646" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B647" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B648" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B649" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B627" t="str">
+      <c r="B650" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B627"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B650"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B650"/>
+  <dimension ref="A1:B658"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4579,1039 +4579,1103 @@
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B522" t="str">
-        <v>IccProfLib non applica questa curva di guadagno: {why}. Un CMM passa al descrittore di tone mapping successivo (clausola 8.10.3).</v>
+        <v>Profili HDR</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Display headroom</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B523" t="str">
-        <v>Margine del display</v>
+        <v>Trasferimento lineare</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B524" t="str">
-        <v>{n} stop (≈{r}× il bianco di riferimento)</v>
+        <v>Trasferimento non lineare (PQ, HLG)</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B525" t="str">
-        <v>Base</v>
+        <v>Profili HDR — trasferimento lineare</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
+        <v>Profili HDR — trasferimento PQ / HLG</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>OpenEXR holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B527" t="str">
-        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
+        <v>OpenEXR contiene luce lineare, quindi si possono assegnare solo profili HDR con trasferimento lineare.</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B528" t="str">
-        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
+        <v>{n} profilo/i HDR PQ/HLG nel pool non sono proposti — il pannello Profili li elenca sotto Profili HDR › Trasferimento non lineare.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B529" t="str">
-        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
+        <v>Nel pool non c’è ancora un profilo HDR con trasferimento lineare; il pannello Profili raggruppa i profili HDR per trasferimento.</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B530" t="str">
-        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
+        <v>IccProfLib non applica questa curva di guadagno: {why}. Un CMM passa al descrittore di tone mapping successivo (clausola 8.10.3).</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Display headroom</v>
       </c>
       <c r="B531" t="str">
-        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
+        <v>Margine del display</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B532" t="str">
-        <v>Curva a {h} stop (nessun guadagno)</v>
+        <v>{n} stop (≈{r}× il bianco di riferimento)</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Baseline</v>
       </c>
       <c r="B533" t="str">
-        <v>Curva a {h} stop</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B534" t="str">
-        <v>Applicato a {h} stop</v>
+        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B535" t="str">
-        <v>Guadagno applicato a questo margine</v>
+        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B536" t="str">
-        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
+        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B537" t="str">
-        <v>Guadagno (stop log2)</v>
+        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B538" t="str">
-        <v>Curva tonale dei grigi a questo margine</v>
+        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B539" t="str">
-        <v>Ingresso (× bianco di riferimento HDR)</v>
+        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B540" t="str">
-        <v>Uscita (× bianco di riferimento HDR)</v>
+        <v>Curva a {h} stop (nessun guadagno)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>No change</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B541" t="str">
-        <v>Nessuna modifica</v>
+        <v>Curva a {h} stop</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>Picco del display a {h} stop</v>
+        <v>Applicato a {h} stop</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Output at {h} stops</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B543" t="str">
-        <v>Uscita a {h} stop</v>
+        <v>Guadagno applicato a questo margine</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B544" t="str">
-        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
+        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Identify displays</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B545" t="str">
-        <v>Identifica i display</v>
+        <v>Guadagno (stop log2)</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B546" t="str">
-        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
+        <v>Curva tonale dei grigi a questo margine</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B547" t="str">
-        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
+        <v>Ingresso (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B548" t="str">
-        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
+        <v>Uscita (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>No change</v>
       </c>
       <c r="B549" t="str">
-        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
+        <v>Nessuna modifica</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Could not identify displays.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B550" t="str">
-        <v>Impossibile identificare i display.</v>
+        <v>Picco del display a {h} stop</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Display events</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B551" t="str">
-        <v>Eventi del display</v>
+        <v>Uscita a {h} stop</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B552" t="str">
-        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
+        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Colour primaries</v>
+        <v>Identify displays</v>
       </c>
       <c r="B553" t="str">
-        <v>Primari di colore</v>
+        <v>Identifica i display</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Transfer characteristics</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B554" t="str">
-        <v>Caratteristiche di trasferimento</v>
+        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Matrix coefficients</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B555" t="str">
-        <v>Coefficienti di matrice</v>
+        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Video full-range flag</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B556" t="str">
-        <v>Flag intervallo video completo</v>
+        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Full range</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B557" t="str">
-        <v>Intervallo completo</v>
+        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Narrow range</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B558" t="str">
-        <v>Intervallo ridotto</v>
+        <v>Impossibile identificare i display.</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Display events</v>
       </c>
       <c r="B559" t="str">
-        <v>non assegnato da ITU-T H.273</v>
+        <v>Eventi del display</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B560" t="str">
-        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
+        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B561" t="str">
-        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
+        <v>Primari di colore</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>REPORT</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B562" t="str">
-        <v>RAPPORTO</v>
+        <v>Caratteristiche di trasferimento</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>FAIL</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B563" t="str">
-        <v>NON SUPERATO</v>
+        <v>Coefficienti di matrice</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>checks</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B564" t="str">
-        <v>controlli</v>
+        <v>Flag intervallo video completo</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Full range</v>
       </c>
       <c r="B565" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>Intervallo completo</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Narrow range</v>
       </c>
       <c r="B566" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Intervallo ridotto</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>ICC Profile Tool</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B567" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>non assegnato da ITU-T H.273</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Powered by {lib}</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B568" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Subscribe</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B569" t="str">
-        <v>Iscriviti</v>
+        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>REPORT</v>
       </c>
       <c r="B570" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Get notified about new releases</v>
+        <v>FAIL</v>
       </c>
       <c r="B571" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Close</v>
+        <v>checks</v>
       </c>
       <c r="B572" t="str">
-        <v>Chiudi</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B573" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Email address</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B574" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>you@example.com</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B575" t="str">
-        <v>tu@esempio.com</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B576" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>(optional)</v>
+        <v>Subscribe</v>
       </c>
       <c r="B577" t="str">
-        <v>(opzionale)</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B578" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B579" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Cancel</v>
+        <v>Close</v>
       </c>
       <c r="B580" t="str">
-        <v>Annulla</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Subscribe</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B581" t="str">
-        <v>Iscriviti</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Email address</v>
       </c>
       <c r="B582" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B583" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Close</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B584" t="str">
-        <v>Chiudi</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Privacy notice</v>
+        <v>(optional)</v>
       </c>
       <c r="B585" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B586" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B587" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B588" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B589" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B590" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Error:</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B591" t="str">
-        <v>Errore:</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Convert to XML</v>
+        <v>Close</v>
       </c>
       <c r="B592" t="str">
-        <v>Converti in XML</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Convert to JSON</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B593" t="str">
-        <v>Converti in JSON</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Convert to ICC</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B594" t="str">
-        <v>Converti in ICC</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Converting to XML…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B595" t="str">
-        <v>Conversione in XML…</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B596" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Converting to ICC…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B597" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Load ICC profile</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B598" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Error:</v>
       </c>
       <c r="B599" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Profile ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B600" t="str">
-        <v>ID profilo</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>No tags found.</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B601" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Tag Name</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B602" t="str">
-        <v>Nome tag</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>ID</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B603" t="str">
-        <v>ID</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Offset</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B604" t="str">
-        <v>Offset</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Size</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B605" t="str">
-        <v>Dimensione</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Pad</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B606" t="str">
-        <v>Riempimento</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Bytes changed since load</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B607" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Type</v>
+        <v>Profile ID</v>
       </c>
       <c r="B608" t="str">
-        <v>Tipo</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Array of {type}</v>
+        <v>No tags found.</v>
       </c>
       <c r="B609" t="str">
-        <v>Array di {type}</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>(No content)</v>
+        <v>Tag Name</v>
       </c>
       <c r="B610" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>bytes</v>
+        <v>ID</v>
       </c>
       <c r="B611" t="str">
-        <v>byte</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Loading full description…</v>
+        <v>Offset</v>
       </c>
       <c r="B612" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Could not load full description:</v>
+        <v>Size</v>
       </c>
       <c r="B613" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Pad</v>
       </c>
       <c r="B614" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B615" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>No validation output</v>
+        <v>Type</v>
       </c>
       <c r="B616" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Profile is valid</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B617" t="str">
-        <v>Il profilo è valido</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Profile has warning(s)</v>
+        <v>(No content)</v>
       </c>
       <c r="B618" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Profile is non-compliant</v>
+        <v>bytes</v>
       </c>
       <c r="B619" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Critical validation error</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B620" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Unknown validation status</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B621" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B622" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B623" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B624" t="str">
-        <v>Valido</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Warning</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B625" t="str">
-        <v>Avviso</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B626" t="str">
-        <v>Errore</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Unknown</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B627" t="str">
-        <v>Sconosciuto</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Pass</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B628" t="str">
-        <v>Superato</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Fail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B629" t="str">
-        <v>Non superato</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>View in context</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B630" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Validation detail</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B631" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Triggered by</v>
+        <v>Valid</v>
       </c>
       <c r="B632" t="str">
-        <v>Attivato da</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Field</v>
+        <v>Warning</v>
       </c>
       <c r="B633" t="str">
-        <v>Campo</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Current value</v>
+        <v>Error</v>
       </c>
       <c r="B634" t="str">
-        <v>Valore attuale</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Required: 0</v>
+        <v>Unknown</v>
       </c>
       <c r="B635" t="str">
-        <v>Richiesto: 0</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Expected: {value}</v>
+        <v>Pass</v>
       </c>
       <c r="B636" t="str">
-        <v>Atteso: {value}</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Invalid</v>
+        <v>Fail</v>
       </c>
       <c r="B637" t="str">
-        <v>Non valido</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>View in context</v>
       </c>
       <c r="B638" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Close</v>
+        <v>Validation detail</v>
       </c>
       <c r="B639" t="str">
-        <v>Chiudi</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Loading XML editor…</v>
+        <v>Triggered by</v>
       </c>
       <c r="B640" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Field</v>
       </c>
       <c r="B641" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Current value</v>
       </c>
       <c r="B642" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Required: 0</v>
       </c>
       <c r="B643" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B644" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Invalid</v>
       </c>
       <c r="B645" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B646" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Close</v>
       </c>
       <c r="B647" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>indent</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B648" t="str">
-        <v>rientro</v>
+        <v>Caricamento editor XML…</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>sort keys</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B649" t="str">
-        <v>ordina chiavi</v>
+        <v>Caricamento editor JSON…</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B650" t="str">
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B651" t="str">
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B652" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B653" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B654" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B655" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B656" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B657" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B650" t="str">
+      <c r="B658" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B650"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B658"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B658"/>
+  <dimension ref="A1:B659"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR is decoded and rendered by profiletool.</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
       </c>
       <c r="B426" t="str">
-        <v>Visualizza un’immagine HDR su questo display. I file che il browser sa decodificare sono mostrati dal browser stesso; OpenEXR è decodificato e reso da profiletool.</v>
+        <v>Visualizza un’immagine HDR su questo display. I file che il browser sa decodificare sono mostrati dal browser stesso; OpenEXR e Radiance HDR sono decodificati e resi da profiletool.</v>
       </c>
     </row>
     <row r="427">
@@ -3827,10 +3827,10 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR, AVIF, JPEG (anche JPEG con gain map), PNG — e HEIC su Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (anche JPEG con gain map), PNG — e HEIC su Safari.</v>
       </c>
     </row>
     <row r="429">
@@ -3867,1815 +3867,1823 @@
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>checking…</v>
+        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
       </c>
       <c r="B433" t="str">
-        <v>verifica…</v>
+        <v>nessuno — Radiance HDR indica il colore tramite l’intestazione PRIMARIES</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>none</v>
+        <v>checking…</v>
       </c>
       <c r="B434" t="str">
-        <v>nessuno</v>
+        <v>verifica…</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Open in Profile tab</v>
+        <v>none</v>
       </c>
       <c r="B435" t="str">
-        <v>Apri nella scheda Profilo</v>
+        <v>nessuno</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Gain map</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B436" t="str">
-        <v>Mappa di guadagno</v>
+        <v>Apri nella scheda Profilo</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>detected, not decoded</v>
+        <v>Gain map</v>
       </c>
       <c r="B437" t="str">
-        <v>rilevata, non decodificata</v>
+        <v>Mappa di guadagno</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>That is not an image. Load profiles through the Profiles pane.</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B438" t="str">
-        <v>Non è un’immagine. Carica i profili dal pannello Profili.</v>
+        <v>rilevata, non decodificata</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Not an image format profiletool recognises.</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B439" t="str">
-        <v>Formato immagine non riconosciuto da profiletool.</v>
+        <v>Non è un’immagine. Carica i profili dal pannello Profili.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B440" t="str">
-        <v>I pixel TIFF non sono ancora mostrati qui: i browser non decodificano il TIFF e la codifica HDR in un TIFF a 16 bit non è ancora decisa (fase 4.3). Il profilo incorporato può essere esaminato.</v>
+        <v>Formato immagine non riconosciuto da profiletool.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Cannot display this image here:</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B441" t="str">
-        <v>Impossibile mostrare questa immagine qui:</v>
+        <v>I pixel TIFF non sono ancora mostrati qui: i browser non decodificano il TIFF e la codifica HDR in un TIFF a 16 bit non è ancora decisa (fase 4.3). Il profilo incorporato può essere esaminato.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Its embedded profile can still be inspected.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B442" t="str">
-        <v>Il profilo incorporato può comunque essere esaminato.</v>
+        <v>Impossibile mostrare questa immagine qui:</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Shown by</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B443" t="str">
-        <v>Mostrato da</v>
+        <v>Il profilo incorporato può comunque essere esaminato.</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>the browser</v>
+        <v>Shown by</v>
       </c>
       <c r="B444" t="str">
-        <v>il browser</v>
+        <v>Mostrato da</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>profiletool</v>
+        <v>the browser</v>
       </c>
       <c r="B445" t="str">
-        <v>profiletool</v>
+        <v>il browser</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>HDR display</v>
+        <v>profiletool</v>
       </c>
       <c r="B446" t="str">
-        <v>Display HDR</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
+        <v>HDR display</v>
       </c>
       <c r="B447" t="str">
-        <v>I browser ignorano l’HDR indicato solo da un profilo ICC incorporato, quindi questa immagine può apparire spenta e piatta.</v>
+        <v>Display HDR</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B448" t="str">
-        <v>Questo browser non può passare un’immagine tra SDR e HDR; è mostrata come il browser la rende.</v>
+        <v>I browser ignorano l’HDR indicato solo da un profilo ICC incorporato, quindi questa immagine può apparire spenta e piatta.</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>The browser could not decode this image.</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B449" t="str">
-        <v>Il browser non è riuscito a decodificare questa immagine.</v>
+        <v>Questo browser non può passare un’immagine tra SDR e HDR; è mostrata come il browser la rende.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Output</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B450" t="str">
-        <v>Uscita</v>
+        <v>Il browser non è riuscito a decodificare questa immagine.</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>HDR canvas (float16)</v>
+        <v>Output</v>
       </c>
       <c r="B451" t="str">
-        <v>Canvas HDR (float16)</v>
+        <v>Uscita</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>WebGPU (extended range)</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B452" t="str">
-        <v>WebGPU (gamma estesa)</v>
+        <v>Canvas HDR (float16)</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>SDR canvas (tone-mapped)</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B453" t="str">
-        <v>Canvas SDR (tone mapping)</v>
+        <v>WebGPU (gamma estesa)</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>Size</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B454" t="str">
-        <v>Dimensioni</v>
+        <v>Canvas SDR (tone mapping)</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Brightest pixel</v>
+        <v>Size</v>
       </c>
       <c r="B455" t="str">
-        <v>Pixel più luminoso</v>
+        <v>Dimensioni</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>{n}× SDR white</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B456" t="str">
-        <v>{n}× il bianco SDR</v>
+        <v>Pixel più luminoso</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Chromaticities</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B457" t="str">
-        <v>Cromaticità</v>
+        <v>{n}× il bianco SDR</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>not stated — Rec. 709 assumed</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B458" t="str">
-        <v>non indicate — si assume Rec. 709</v>
+        <v>Cromaticità</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>{from} was not available here ({why}); using the next output.</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B459" t="str">
-        <v>{from} non è disponibile qui ({why}); si usa l’uscita successiva.</v>
+        <v>non indicate — si assume Rec. 709</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B460" t="str">
-        <v>Questa uscita non può trasportare valori più luminosi del bianco; è mostrata la resa SDR con tone mapping.</v>
+        <v>{from} non è disponibile qui ({why}); si usa l’uscita successiva.</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>Exposure</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B461" t="str">
-        <v>Esposizione</v>
+        <v>Questa uscita non può trasportare valori più luminosi del bianco; è mostrata la resa SDR con tone mapping.</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>{n} stops</v>
+        <v>Exposure</v>
       </c>
       <c r="B462" t="str">
-        <v>{n} stop</v>
+        <v>Esposizione</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Could not decode:</v>
+        <v>{n} stops</v>
       </c>
       <c r="B463" t="str">
-        <v>Decodifica non riuscita:</v>
+        <v>{n} stop</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Decoding…</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B464" t="str">
-        <v>Decodifica…</v>
+        <v>Decodifica non riuscita:</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Dynamic range</v>
+        <v>Decoding…</v>
       </c>
       <c r="B465" t="str">
-        <v>Gamma dinamica</v>
+        <v>Decodifica…</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B466" t="str">
-        <v>Questo browser offre solo i due estremi, non una miscela.</v>
+        <v>Gamma dinamica</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B467" t="str">
-        <v>decodificato da profiletool stesso, quindi indipendente dal browser</v>
+        <v>Questo browser offre solo i due estremi, non una miscela.</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>this browser decodes it</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B468" t="str">
-        <v>questo browser lo decodifica</v>
+        <v>decodificato da profiletool stesso, quindi indipendente dal browser</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>this browser does not decode it</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B469" t="str">
-        <v>questo browser non lo decodifica</v>
+        <v>questo browser lo decodifica</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B470" t="str">
-        <v>la visualizzazione HEIC richiede Safari o un altro browser WebKit — Chrome e Firefox non decodificano HEIC su nessuna piattaforma, macOS compreso</v>
+        <v>questo browser non lo decodifica</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B471" t="str">
-        <v>la visualizzazione JPEG XL richiede Safari; gli altri browser non lo supportano ancora</v>
+        <v>la visualizzazione HEIC richiede Safari o un altro browser WebKit — Chrome e Firefox non decodificano HEIC su nessuna piattaforma, macOS compreso</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>deferred to a later release</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B472" t="str">
-        <v>rinviato a una versione successiva</v>
+        <v>la visualizzazione JPEG XL richiede Safari; gli altri browser non lo supportano ancora</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B473" t="str">
-        <v>questo display non segnala alcun percorso HDR, quindi l’HDR è reso in SDR con tone mapping</v>
+        <v>rinviato a una versione successiva</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B474" t="str">
-        <v>questo browser non offre un canvas HDR (serve canvas float16 o WebGPU)</v>
+        <v>questo display non segnala alcun percorso HDR, quindi l’HDR è reso in SDR con tone mapping</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B475" t="str">
-        <v>Firefox non mostra immagini HDR e non legge gain map; i contenuti HDR sono mostrati in SDR</v>
+        <v>questo browser non offre un canvas HDR (serve canvas float16 o WebGPU)</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B476" t="str">
-        <v>l’ispezione richiede solo l’analisi del contenitore, non un codec</v>
+        <v>Firefox non mostra immagini HDR e non legge gain map; i contenuti HDR sono mostrati in SDR</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B477" t="str">
-        <v>display HDR e canvas HDR sono entrambi disponibili</v>
+        <v>l’ispezione richiede solo l’analisi del contenitore, non un codec</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>unknown format</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B478" t="str">
-        <v>formato sconosciuto</v>
+        <v>display HDR e canvas HDR sono entrambi disponibili</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>{browser} on {os}</v>
+        <v>unknown format</v>
       </c>
       <c r="B479" t="str">
-        <v>{browser} su {os}</v>
+        <v>formato sconosciuto</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B480" t="str">
-        <v>{name} · display HDR rilevato</v>
+        <v>{browser} su {os}</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>{name} · SDR display</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B481" t="str">
-        <v>{name} · display SDR</v>
+        <v>{name} · display HDR rilevato</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B482" t="str">
-        <v>WebGPU ha applicato il tone mapping «{mode}», quindi l’uscita è limitata a SDR</v>
+        <v>{name} · display SDR</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B483" t="str">
-        <v>Questo browser non indica il tone mapping WebGPU applicato, quindi l’uscita HDR non è confermata</v>
+        <v>WebGPU ha applicato il tone mapping «{mode}», quindi l’uscita è limitata a SDR</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>Display peak</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B484" t="str">
-        <v>Picco del display</v>
+        <v>Questo browser non indica il tone mapping WebGPU applicato, quindi l’uscita HDR non è confermata</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>Display peak</v>
       </c>
       <c r="B485" t="str">
-        <v>{r}× il bianco SDR ({n} stop)</v>
+        <v>Picco del display</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>1× — SDR display</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B486" t="str">
-        <v>1× — display SDR</v>
+        <v>{r}× il bianco SDR ({n} stop)</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>not known</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B487" t="str">
-        <v>non noto</v>
+        <v>1× — display SDR</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>not known</v>
       </c>
       <c r="B488" t="str">
-        <v>Questo display non segnala HDR, quindi il browser mostra l’immagine in SDR a entrambi gli estremi.</v>
+        <v>non noto</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B489" t="str">
-        <v>Questo display non segnala HDR, quindi tutto ciò che supera il bianco SDR viene tagliato. «Adatta al display» mostra invece la resa con tone mapping.</v>
+        <v>Questo display non segnala HDR, quindi il browser mostra l’immagine in SDR a entrambi gli estremi.</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B490" t="str">
-        <v>Questa immagine richiede {img}× il bianco SDR, ma questo display arriva solo a {disp}×, quindi i valori più luminosi vengono tagliati. «Adatta al display» li attenua verso il picco del display.</v>
+        <v>Questo display non segnala HDR, quindi tutto ciò che supera il bianco SDR viene tagliato. «Adatta al display» mostra invece la resa con tone mapping.</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>Fit to display</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B491" t="str">
-        <v>Adatta al display</v>
+        <v>Questa immagine richiede {img}× il bianco SDR, ma questo display arriva solo a {disp}×, quindi i valori più luminosi vengono tagliati. «Adatta al display» li attenua verso il picco del display.</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Fit to display</v>
       </c>
       <c r="B492" t="str">
-        <v>Limita la luminosità al picco segnalato dal display. Su Windows questo valore può restare indietro rispetto ai cambi di luminosità.</v>
+        <v>Adatta al display</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>no limit</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B493" t="str">
-        <v>nessun limite</v>
+        <v>Limita la luminosità al picco segnalato dal display. Su Windows questo valore può restare indietro rispetto ai cambi di luminosità.</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>no limit</v>
       </c>
       <c r="B494" t="str">
-        <v>limite {n} stop ({r}×)</v>
+        <v>nessun limite</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>SDR white</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B495" t="str">
-        <v>Bianco SDR</v>
+        <v>limite {n} stop ({r}×)</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>SDR white</v>
       </c>
       <c r="B496" t="str">
-        <v>Bianco SDR semplice, per confronto. Su un display HDR le alte luci HDR appaiono più luminose di questo.</v>
+        <v>Bianco SDR</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>SDR white patch</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B497" t="str">
-        <v>Riquadro bianco SDR</v>
+        <v>Bianco SDR semplice, per confronto. Su un display HDR le alte luci HDR appaiono più luminose di questo.</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B498" t="str">
-        <v>Trascinalo per spostarlo; doppio clic per rimetterlo accanto all’immagine.</v>
+        <v>Riquadro bianco SDR</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Assign profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B499" t="str">
-        <v>Assegna profilo</v>
+        <v>Trascinalo per spostarlo; doppio clic per rimetterlo accanto all’immagine.</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>None — use what the file signals</v>
+        <v>Assign profile</v>
       </c>
       <c r="B500" t="str">
-        <v>Nessuno — secondo il file</v>
+        <v>Assegna profilo</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B501" t="str">
-        <v>Profilo incorporato ({n} B)</v>
+        <v>Nessuno — secondo il file</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B502" t="str">
-        <v>Profili HDR nel pool</v>
+        <v>Profilo incorporato ({n} B)</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Profile</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B503" t="str">
-        <v>Profilo</v>
+        <v>Profili HDR nel pool</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>embedded profile</v>
+        <v>Profile</v>
       </c>
       <c r="B504" t="str">
-        <v>profilo incorporato</v>
+        <v>Profilo</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Colour engine path</v>
+        <v>embedded profile</v>
       </c>
       <c r="B505" t="str">
-        <v>Percorso del motore colore</v>
+        <v>profilo incorporato</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B506" t="str">
-        <v>Percorso HDR, curva di guadagno applicata</v>
+        <v>Percorso del motore colore</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B507" t="str">
-        <v>Percorso HDR, nessuna curva di guadagno</v>
+        <v>Percorso HDR, curva di guadagno applicata</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B508" t="str">
-        <v>AToB0 precalcolato — non il percorso HDR</v>
+        <v>Percorso HDR, nessuna curva di guadagno</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Transfer</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B509" t="str">
-        <v>Trasferimento</v>
+        <v>AToB0 precalcolato — non il percorso HDR</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>HDR reference white</v>
+        <v>Transfer</v>
       </c>
       <c r="B510" t="str">
-        <v>Bianco di riferimento HDR</v>
+        <v>Trasferimento</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Target headroom</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B511" t="str">
-        <v>Margine di destinazione</v>
+        <v>Bianco di riferimento HDR</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B512" t="str">
-        <v>{r}× il bianco di riferimento ({n} stop)</v>
+        <v>Margine di destinazione</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Tone mapping</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B513" t="str">
-        <v>Tone mapping</v>
+        <v>{r}× il bianco di riferimento ({n} stop)</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B514" t="str">
-        <v>Auto (classifica della clausola 8.10.3)</v>
+        <v>Tone mapping</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B515" t="str">
-        <v>Curva di guadagno (HAGC)</v>
+        <v>Auto (classifica della clausola 8.10.3)</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B516" t="str">
-        <v>Ripiego SDR precalcolato (AToB0)</v>
+        <v>Curva di guadagno (HAGC)</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B517" t="str">
-        <v>Disattivato — come un CMM precedente all’emendamento</v>
+        <v>Ripiego SDR precalcolato (AToB0)</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Applying the profile…</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B518" t="str">
-        <v>Applicazione del profilo…</v>
+        <v>Disattivato — come un CMM precedente all’emendamento</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>OpenEXR holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B519" t="str">
-        <v>OpenEXR contiene luce lineare, quindi serve un profilo con trasferimento Linear (8).</v>
+        <v>Applicazione del profilo…</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B520" t="str">
-        <v>Per assegnare un profilo serve un’immagine RGB a 3 canali.</v>
+        <v>{format} contiene luce lineare, quindi serve un profilo con trasferimento Linear (8).</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B521" t="str">
-        <v>Per interpretarne i valori, assegna un profilo qui sopra.</v>
+        <v>Per assegnare un profilo serve un’immagine RGB a 3 canali.</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>HDR Profiles</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B522" t="str">
-        <v>Profili HDR</v>
+        <v>Per interpretarne i valori, assegna un profilo qui sopra.</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Linear transfer</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B523" t="str">
-        <v>Trasferimento lineare</v>
+        <v>Profili HDR</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B524" t="str">
-        <v>Trasferimento non lineare (PQ, HLG)</v>
+        <v>Trasferimento lineare</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B525" t="str">
-        <v>Profili HDR — trasferimento lineare</v>
+        <v>Trasferimento non lineare (PQ, HLG)</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>Profili HDR — trasferimento PQ / HLG</v>
+        <v>Profili HDR — trasferimento lineare</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>OpenEXR holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B527" t="str">
-        <v>OpenEXR contiene luce lineare, quindi si possono assegnare solo profili HDR con trasferimento lineare.</v>
+        <v>Profili HDR — trasferimento PQ / HLG</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B528" t="str">
-        <v>{n} profilo/i HDR PQ/HLG nel pool non sono proposti — il pannello Profili li elenca sotto Profili HDR › Trasferimento non lineare.</v>
+        <v>{format} contiene luce lineare, quindi si possono assegnare solo profili HDR con trasferimento lineare.</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B529" t="str">
-        <v>Nel pool non c’è ancora un profilo HDR con trasferimento lineare; il pannello Profili raggruppa i profili HDR per trasferimento.</v>
+        <v>{n} profilo/i HDR PQ/HLG nel pool non sono proposti — il pannello Profili li elenca sotto Profili HDR › Trasferimento non lineare.</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B530" t="str">
-        <v>IccProfLib non applica questa curva di guadagno: {why}. Un CMM passa al descrittore di tone mapping successivo (clausola 8.10.3).</v>
+        <v>Nel pool non c’è ancora un profilo HDR con trasferimento lineare; il pannello Profili raggruppa i profili HDR per trasferimento.</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B531" t="str">
-        <v>Margine del display</v>
+        <v>IccProfLib non applica questa curva di guadagno: {why}. Un CMM passa al descrittore di tone mapping successivo (clausola 8.10.3).</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B532" t="str">
-        <v>{n} stop (≈{r}× il bianco di riferimento)</v>
+        <v>Margine del display</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B533" t="str">
-        <v>Base</v>
+        <v>{n} stop (≈{r}× il bianco di riferimento)</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Baseline</v>
       </c>
       <c r="B534" t="str">
-        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B535" t="str">
-        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
+        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B536" t="str">
-        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
+        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B537" t="str">
-        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
+        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B538" t="str">
-        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
+        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B539" t="str">
-        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
+        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B540" t="str">
-        <v>Curva a {h} stop (nessun guadagno)</v>
+        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B541" t="str">
-        <v>Curva a {h} stop</v>
+        <v>Curva a {h} stop (nessun guadagno)</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B542" t="str">
-        <v>Applicato a {h} stop</v>
+        <v>Curva a {h} stop</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B543" t="str">
-        <v>Guadagno applicato a questo margine</v>
+        <v>Applicato a {h} stop</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B544" t="str">
-        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
+        <v>Guadagno applicato a questo margine</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B545" t="str">
-        <v>Guadagno (stop log2)</v>
+        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B546" t="str">
-        <v>Curva tonale dei grigi a questo margine</v>
+        <v>Guadagno (stop log2)</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B547" t="str">
-        <v>Ingresso (× bianco di riferimento HDR)</v>
+        <v>Curva tonale dei grigi a questo margine</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B548" t="str">
-        <v>Uscita (× bianco di riferimento HDR)</v>
+        <v>Ingresso (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B549" t="str">
-        <v>Nessuna modifica</v>
+        <v>Uscita (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B550" t="str">
-        <v>Picco del display a {h} stop</v>
+        <v>Nessuna modifica</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B551" t="str">
-        <v>Uscita a {h} stop</v>
+        <v>Picco del display a {h} stop</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B552" t="str">
-        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
+        <v>Uscita a {h} stop</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B553" t="str">
-        <v>Identifica i display</v>
+        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B554" t="str">
-        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
+        <v>Identifica i display</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B555" t="str">
-        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
+        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B556" t="str">
-        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
+        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B557" t="str">
-        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
+        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B558" t="str">
-        <v>Impossibile identificare i display.</v>
+        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B559" t="str">
-        <v>Eventi del display</v>
+        <v>Impossibile identificare i display.</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B560" t="str">
-        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
+        <v>Eventi del display</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B561" t="str">
-        <v>Primari di colore</v>
+        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B562" t="str">
-        <v>Caratteristiche di trasferimento</v>
+        <v>Primari di colore</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B563" t="str">
-        <v>Coefficienti di matrice</v>
+        <v>Caratteristiche di trasferimento</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B564" t="str">
-        <v>Flag intervallo video completo</v>
+        <v>Coefficienti di matrice</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B565" t="str">
-        <v>Intervallo completo</v>
+        <v>Flag intervallo video completo</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B566" t="str">
-        <v>Intervallo ridotto</v>
+        <v>Intervallo completo</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B567" t="str">
-        <v>non assegnato da ITU-T H.273</v>
+        <v>Intervallo ridotto</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B568" t="str">
-        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
+        <v>non assegnato da ITU-T H.273</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B569" t="str">
-        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
+        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B570" t="str">
-        <v>RAPPORTO</v>
+        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B571" t="str">
-        <v>NON SUPERATO</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B572" t="str">
-        <v>controlli</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B573" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B574" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B575" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B576" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B577" t="str">
-        <v>Iscriviti</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B578" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B579" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B580" t="str">
-        <v>Chiudi</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B581" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B582" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B583" t="str">
-        <v>tu@esempio.com</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B584" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B585" t="str">
-        <v>(opzionale)</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B586" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B587" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B588" t="str">
-        <v>Annulla</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B589" t="str">
-        <v>Iscriviti</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B590" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B591" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B592" t="str">
-        <v>Chiudi</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B593" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B594" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B595" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B596" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B597" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B598" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B599" t="str">
-        <v>Errore:</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B600" t="str">
-        <v>Converti in XML</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B601" t="str">
-        <v>Converti in JSON</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B602" t="str">
-        <v>Converti in ICC</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B603" t="str">
-        <v>Conversione in XML…</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B604" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B605" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B606" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B607" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B608" t="str">
-        <v>ID profilo</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B609" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B610" t="str">
-        <v>Nome tag</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B611" t="str">
-        <v>ID</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B612" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B613" t="str">
-        <v>Dimensione</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B614" t="str">
-        <v>Riempimento</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B615" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B616" t="str">
-        <v>Tipo</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B617" t="str">
-        <v>Array di {type}</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B618" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B619" t="str">
-        <v>byte</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B620" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B621" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B622" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B623" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B624" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B625" t="str">
-        <v>Il profilo è valido</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B626" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B627" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B628" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B629" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B630" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B631" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B632" t="str">
-        <v>Valido</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B633" t="str">
-        <v>Avviso</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B634" t="str">
-        <v>Errore</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B635" t="str">
-        <v>Sconosciuto</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B636" t="str">
-        <v>Superato</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B637" t="str">
-        <v>Non superato</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B638" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B639" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B640" t="str">
-        <v>Attivato da</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B641" t="str">
-        <v>Campo</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B642" t="str">
-        <v>Valore attuale</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B643" t="str">
-        <v>Richiesto: 0</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B644" t="str">
-        <v>Atteso: {value}</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B645" t="str">
-        <v>Non valido</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B646" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B647" t="str">
-        <v>Chiudi</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B648" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B649" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Caricamento editor XML…</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B650" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Caricamento editor JSON…</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B651" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B652" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B653" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>● modifiche XML non salvate</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B654" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● modifiche JSON non salvate</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B655" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B656" t="str">
-        <v>rientro</v>
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B657" t="str">
-        <v>ordina chiavi</v>
+        <v>rientro</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B658" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B658" t="str">
+      <c r="B659" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B658"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B659"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B659"/>
+  <dimension ref="A1:B670"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4347,1343 +4347,1431 @@
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Image details</v>
       </c>
       <c r="B493" t="str">
-        <v>Limita la luminosità al picco segnalato dal display. Su Windows questo valore può restare indietro rispetto ai cambi di luminosità.</v>
+        <v>Dettagli immagine</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>no limit</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B494" t="str">
-        <v>nessun limite</v>
+        <v>non disponibile — il browser rende questa immagine e non può limitarla a un picco dato</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B495" t="str">
-        <v>limite {n} stop ({r}×)</v>
+        <v>non disponibile — questa uscita non mostra nulla sopra il bianco SDR</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>SDR white</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B496" t="str">
-        <v>Bianco SDR</v>
+        <v>non disponibile — il picco di questo display non è noto</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>Zoom in</v>
       </c>
       <c r="B497" t="str">
-        <v>Bianco SDR semplice, per confronto. Su un display HDR le alte luci HDR appaiono più luminose di questo.</v>
+        <v>Ingrandisci</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>SDR white patch</v>
+        <v>Zoom out</v>
       </c>
       <c r="B498" t="str">
-        <v>Riquadro bianco SDR</v>
+        <v>Riduci</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>Fit image</v>
       </c>
       <c r="B499" t="str">
-        <v>Trascinalo per spostarlo; doppio clic per rimetterlo accanto all’immagine.</v>
+        <v>Adatta immagine</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Assign profile</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B500" t="str">
-        <v>Assegna profilo</v>
+        <v>Pixel reali (1:1)</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>None — use what the file signals</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B501" t="str">
-        <v>Nessuno — secondo il file</v>
+        <v>Trascina per spostare · Ctrl+rotellina per lo zoom · doppio clic per ripristinare</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B502" t="str">
-        <v>Profilo incorporato ({n} B)</v>
+        <v>Trascina per ridimensionare l’area immagine; doppio clic per tornare alla dimensione predefinita</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Image view</v>
       </c>
       <c r="B503" t="str">
-        <v>Profili HDR nel pool</v>
+        <v>Vista immagine</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Profile</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B504" t="str">
-        <v>Profilo</v>
+        <v>Limita la luminosità al picco segnalato dal display. Su Windows questo valore può restare indietro rispetto ai cambi di luminosità.</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>embedded profile</v>
+        <v>no limit</v>
       </c>
       <c r="B505" t="str">
-        <v>profilo incorporato</v>
+        <v>nessun limite</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Colour engine path</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B506" t="str">
-        <v>Percorso del motore colore</v>
+        <v>limite {n} stop ({r}×)</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>SDR white</v>
       </c>
       <c r="B507" t="str">
-        <v>Percorso HDR, curva di guadagno applicata</v>
+        <v>Bianco SDR</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B508" t="str">
-        <v>Percorso HDR, nessuna curva di guadagno</v>
+        <v>Bianco SDR semplice, per confronto. Su un display HDR le alte luci HDR appaiono più luminose di questo.</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B509" t="str">
-        <v>AToB0 precalcolato — non il percorso HDR</v>
+        <v>Riquadro bianco SDR</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Transfer</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B510" t="str">
-        <v>Trasferimento</v>
+        <v>Trascinalo per spostarlo; doppio clic per rimetterlo accanto all’immagine.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>HDR reference white</v>
+        <v>Assign profile</v>
       </c>
       <c r="B511" t="str">
-        <v>Bianco di riferimento HDR</v>
+        <v>Assegna profilo</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>Target headroom</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B512" t="str">
-        <v>Margine di destinazione</v>
+        <v>Nessuno — secondo il file</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B513" t="str">
-        <v>{r}× il bianco di riferimento ({n} stop)</v>
+        <v>Profilo incorporato ({n} B)</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>Tone mapping</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B514" t="str">
-        <v>Tone mapping</v>
+        <v>Profili HDR nel pool</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Profile</v>
       </c>
       <c r="B515" t="str">
-        <v>Auto (classifica della clausola 8.10.3)</v>
+        <v>Profilo</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>embedded profile</v>
       </c>
       <c r="B516" t="str">
-        <v>Curva di guadagno (HAGC)</v>
+        <v>profilo incorporato</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B517" t="str">
-        <v>Ripiego SDR precalcolato (AToB0)</v>
+        <v>Percorso del motore colore</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B518" t="str">
-        <v>Disattivato — come un CMM precedente all’emendamento</v>
+        <v>Percorso HDR, curva di guadagno applicata</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>Applying the profile…</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B519" t="str">
-        <v>Applicazione del profilo…</v>
+        <v>Percorso HDR, nessuna curva di guadagno</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B520" t="str">
-        <v>{format} contiene luce lineare, quindi serve un profilo con trasferimento Linear (8).</v>
+        <v>AToB0 precalcolato — non il percorso HDR</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Transfer</v>
       </c>
       <c r="B521" t="str">
-        <v>Per assegnare un profilo serve un’immagine RGB a 3 canali.</v>
+        <v>Trasferimento</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B522" t="str">
-        <v>Per interpretarne i valori, assegna un profilo qui sopra.</v>
+        <v>Bianco di riferimento HDR</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>HDR Profiles</v>
+        <v>Target headroom</v>
       </c>
       <c r="B523" t="str">
-        <v>Profili HDR</v>
+        <v>Margine di destinazione</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>Linear transfer</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B524" t="str">
-        <v>Trasferimento lineare</v>
+        <v>{r}× il bianco di riferimento ({n} stop)</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B525" t="str">
-        <v>Trasferimento non lineare (PQ, HLG)</v>
+        <v>Tone mapping</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B526" t="str">
-        <v>Profili HDR — trasferimento lineare</v>
+        <v>Auto (classifica della clausola 8.10.3)</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B527" t="str">
-        <v>Profili HDR — trasferimento PQ / HLG</v>
+        <v>Curva di guadagno (HAGC)</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B528" t="str">
-        <v>{format} contiene luce lineare, quindi si possono assegnare solo profili HDR con trasferimento lineare.</v>
+        <v>Ripiego SDR precalcolato (AToB0)</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B529" t="str">
-        <v>{n} profilo/i HDR PQ/HLG nel pool non sono proposti — il pannello Profili li elenca sotto Profili HDR › Trasferimento non lineare.</v>
+        <v>Disattivato — come un CMM precedente all’emendamento</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B530" t="str">
-        <v>Nel pool non c’è ancora un profilo HDR con trasferimento lineare; il pannello Profili raggruppa i profili HDR per trasferimento.</v>
+        <v>Applicazione del profilo…</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B531" t="str">
-        <v>IccProfLib non applica questa curva di guadagno: {why}. Un CMM passa al descrittore di tone mapping successivo (clausola 8.10.3).</v>
+        <v>{format} contiene luce lineare, quindi serve un profilo con trasferimento Linear (8).</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Display headroom</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B532" t="str">
-        <v>Margine del display</v>
+        <v>Per assegnare un profilo serve un’immagine RGB a 3 canali.</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B533" t="str">
-        <v>{n} stop (≈{r}× il bianco di riferimento)</v>
+        <v>Per interpretarne i valori, assegna un profilo qui sopra.</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B534" t="str">
-        <v>Base</v>
+        <v>Profili HDR</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B535" t="str">
-        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
+        <v>Trasferimento lineare</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B536" t="str">
-        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
+        <v>Trasferimento non lineare (PQ, HLG)</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B537" t="str">
-        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
+        <v>Profili HDR — trasferimento lineare</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B538" t="str">
-        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
+        <v>Profili HDR — trasferimento PQ / HLG</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B539" t="str">
-        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
+        <v>{format} contiene luce lineare, quindi si possono assegnare solo profili HDR con trasferimento lineare.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B540" t="str">
-        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
+        <v>{n} profilo/i HDR PQ/HLG nel pool non sono proposti — il pannello Profili li elenca sotto Profili HDR › Trasferimento non lineare.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B541" t="str">
-        <v>Curva a {h} stop (nessun guadagno)</v>
+        <v>Nel pool non c’è ancora un profilo HDR con trasferimento lineare; il pannello Profili raggruppa i profili HDR per trasferimento.</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Curve at {h} stops</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B542" t="str">
-        <v>Curva a {h} stop</v>
+        <v>IccProfLib non applica questa curva di guadagno: {why}. Un CMM passa al descrittore di tone mapping successivo (clausola 8.10.3).</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Display headroom</v>
       </c>
       <c r="B543" t="str">
-        <v>Applicato a {h} stop</v>
+        <v>Margine del display</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B544" t="str">
-        <v>Guadagno applicato a questo margine</v>
+        <v>{n} stop (≈{r}× il bianco di riferimento)</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B545" t="str">
-        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B546" t="str">
-        <v>Guadagno (stop log2)</v>
+        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B547" t="str">
-        <v>Curva tonale dei grigi a questo margine</v>
+        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B548" t="str">
-        <v>Ingresso (× bianco di riferimento HDR)</v>
+        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B549" t="str">
-        <v>Uscita (× bianco di riferimento HDR)</v>
+        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>No change</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B550" t="str">
-        <v>Nessuna modifica</v>
+        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B551" t="str">
-        <v>Picco del display a {h} stop</v>
+        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Output at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B552" t="str">
-        <v>Uscita a {h} stop</v>
+        <v>Curva a {h} stop (nessun guadagno)</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B553" t="str">
-        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
+        <v>Curva a {h} stop</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Identify displays</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B554" t="str">
-        <v>Identifica i display</v>
+        <v>Applicato a {h} stop</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B555" t="str">
-        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
+        <v>Guadagno applicato a questo margine</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
+        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B557" t="str">
-        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
+        <v>Guadagno (stop log2)</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B558" t="str">
-        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
+        <v>Curva tonale dei grigi a questo margine</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Could not identify displays.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B559" t="str">
-        <v>Impossibile identificare i display.</v>
+        <v>Ingresso (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Display events</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B560" t="str">
-        <v>Eventi del display</v>
+        <v>Uscita (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>No change</v>
       </c>
       <c r="B561" t="str">
-        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
+        <v>Nessuna modifica</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Colour primaries</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B562" t="str">
-        <v>Primari di colore</v>
+        <v>Picco del display a {h} stop</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Transfer characteristics</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B563" t="str">
-        <v>Caratteristiche di trasferimento</v>
+        <v>Uscita a {h} stop</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Matrix coefficients</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B564" t="str">
-        <v>Coefficienti di matrice</v>
+        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Video full-range flag</v>
+        <v>Identify displays</v>
       </c>
       <c r="B565" t="str">
-        <v>Flag intervallo video completo</v>
+        <v>Identifica i display</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Full range</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B566" t="str">
-        <v>Intervallo completo</v>
+        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Narrow range</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B567" t="str">
-        <v>Intervallo ridotto</v>
+        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B568" t="str">
-        <v>non assegnato da ITU-T H.273</v>
+        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B569" t="str">
-        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
+        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B570" t="str">
-        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
+        <v>Impossibile identificare i display.</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>REPORT</v>
+        <v>Display events</v>
       </c>
       <c r="B571" t="str">
-        <v>RAPPORTO</v>
+        <v>Eventi del display</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>FAIL</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B572" t="str">
-        <v>NON SUPERATO</v>
+        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>checks</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B573" t="str">
-        <v>controlli</v>
+        <v>Primari di colore</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B574" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>Caratteristiche di trasferimento</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B575" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Coefficienti di matrice</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B576" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Flag intervallo video completo</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Powered by {lib}</v>
+        <v>Full range</v>
       </c>
       <c r="B577" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Intervallo completo</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B578" t="str">
-        <v>Iscriviti</v>
+        <v>Intervallo ridotto</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B579" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>non assegnato da ITU-T H.273</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Get notified about new releases</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B580" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B581" t="str">
-        <v>Chiudi</v>
+        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>REPORT</v>
       </c>
       <c r="B582" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Email address</v>
+        <v>FAIL</v>
       </c>
       <c r="B583" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>you@example.com</v>
+        <v>checks</v>
       </c>
       <c r="B584" t="str">
-        <v>tu@esempio.com</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B585" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B586" t="str">
-        <v>(opzionale)</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B587" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B588" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Cancel</v>
+        <v>Subscribe</v>
       </c>
       <c r="B589" t="str">
-        <v>Annulla</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B590" t="str">
-        <v>Iscriviti</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B591" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Close</v>
       </c>
       <c r="B592" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Close</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B593" t="str">
-        <v>Chiudi</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Privacy notice</v>
+        <v>Email address</v>
       </c>
       <c r="B594" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B595" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B596" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Please check the form and try again.</v>
+        <v>(optional)</v>
       </c>
       <c r="B597" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B598" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Network error. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B599" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Error:</v>
+        <v>Cancel</v>
       </c>
       <c r="B600" t="str">
-        <v>Errore:</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B601" t="str">
-        <v>Converti in XML</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Convert to JSON</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B602" t="str">
-        <v>Converti in JSON</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Convert to ICC</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B603" t="str">
-        <v>Converti in ICC</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B604" t="str">
-        <v>Conversione in XML…</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Converting to JSON…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B605" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Converting to ICC…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B606" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Load ICC profile</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B607" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B608" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Profile ID</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B609" t="str">
-        <v>ID profilo</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>No tags found.</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B610" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Tag Name</v>
+        <v>Error:</v>
       </c>
       <c r="B611" t="str">
-        <v>Nome tag</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B612" t="str">
-        <v>ID</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Offset</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B613" t="str">
-        <v>Offset</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Size</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B614" t="str">
-        <v>Dimensione</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Pad</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B615" t="str">
-        <v>Riempimento</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B616" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Type</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B617" t="str">
-        <v>Tipo</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Array of {type}</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B618" t="str">
-        <v>Array di {type}</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>(No content)</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B619" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>bytes</v>
+        <v>Profile ID</v>
       </c>
       <c r="B620" t="str">
-        <v>byte</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Loading full description…</v>
+        <v>No tags found.</v>
       </c>
       <c r="B621" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Could not load full description:</v>
+        <v>Tag Name</v>
       </c>
       <c r="B622" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ID</v>
       </c>
       <c r="B623" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Offset</v>
       </c>
       <c r="B624" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>No validation output</v>
+        <v>Size</v>
       </c>
       <c r="B625" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Profile is valid</v>
+        <v>Pad</v>
       </c>
       <c r="B626" t="str">
-        <v>Il profilo è valido</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B627" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Type</v>
       </c>
       <c r="B628" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Critical validation error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B629" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Unknown validation status</v>
+        <v>(No content)</v>
       </c>
       <c r="B630" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>bytes</v>
       </c>
       <c r="B631" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B632" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B633" t="str">
-        <v>Valido</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Warning</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B634" t="str">
-        <v>Avviso</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B635" t="str">
-        <v>Errore</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Unknown</v>
+        <v>No validation output</v>
       </c>
       <c r="B636" t="str">
-        <v>Sconosciuto</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Pass</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B637" t="str">
-        <v>Superato</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Fail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B638" t="str">
-        <v>Non superato</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>View in context</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B639" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Validation detail</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B640" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Triggered by</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B641" t="str">
-        <v>Attivato da</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Field</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B642" t="str">
-        <v>Campo</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Current value</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B643" t="str">
-        <v>Valore attuale</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Required: 0</v>
+        <v>Valid</v>
       </c>
       <c r="B644" t="str">
-        <v>Richiesto: 0</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Expected: {value}</v>
+        <v>Warning</v>
       </c>
       <c r="B645" t="str">
-        <v>Atteso: {value}</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Invalid</v>
+        <v>Error</v>
       </c>
       <c r="B646" t="str">
-        <v>Non valido</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown</v>
       </c>
       <c r="B647" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Close</v>
+        <v>Pass</v>
       </c>
       <c r="B648" t="str">
-        <v>Chiudi</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Loading XML editor…</v>
+        <v>Fail</v>
       </c>
       <c r="B649" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Loading JSON editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B650" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B651" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B652" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Field</v>
       </c>
       <c r="B653" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Current value</v>
       </c>
       <c r="B654" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B655" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B656" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>indent</v>
+        <v>Invalid</v>
       </c>
       <c r="B657" t="str">
-        <v>rientro</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>sort keys</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B658" t="str">
-        <v>ordina chiavi</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B659" t="str">
+        <v>Chiudi</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B660" t="str">
+        <v>Caricamento editor XML…</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B661" t="str">
+        <v>Caricamento editor JSON…</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B662" t="str">
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B663" t="str">
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B664" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B665" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B666" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B667" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B668" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B669" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B659" t="str">
+      <c r="B670" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B659"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B670"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B670"/>
+  <dimension ref="A1:B693"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4771,1007 +4771,1191 @@
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B546" t="str">
-        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
+        <v>Anteprima tramite il motore colore</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B547" t="str">
-        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
+        <v>Come creata (base {h} stop, senza guadagno)</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B548" t="str">
-        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
+        <v>Mappata per {h} stop</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B549" t="str">
-        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
+        <v>Gli stessi pixel di prova (segnale {transfer} crescente da sinistra a destra: grigio, poi R, G, B, Y, C, M) attraverso la trasformazione HDR di IccProfLib. Entrambe le strisce sono limitate a {r}× il bianco di riferimento HDR, come le mostrerebbe un display con {h} stop di headroom: dove la striscia superiore satura piatta, la curva di guadagno attenua le alte luci.</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>reference white</v>
       </c>
       <c r="B550" t="str">
-        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
+        <v>bianco di riferimento</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>display peak</v>
       </c>
       <c r="B551" t="str">
-        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
+        <v>picco del display</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B552" t="str">
-        <v>Curva a {h} stop (nessun guadagno)</v>
+        <v>Anteprima non disponibile: {why}</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Curve at {h} stops</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B553" t="str">
-        <v>Curva a {h} stop</v>
+        <v>il motore colore non ha seguito il percorso HDR per questo profilo</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B554" t="str">
-        <v>Applicato a {h} stop</v>
+        <v>Guadagno a ogni headroom</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B555" t="str">
-        <v>Guadagno applicato a questo margine</v>
+        <v>Guadagno applicato a un ingresso grigio a ogni headroom del display: il blu comprime, il rosso espande, il bianco lo lascia invariato. Le linee punteggiate indicano le curve del tag, quella continua la base, quella ambra il cursore; la diagonale tratteggiata è dove l’ingresso raggiunge il picco del display. Fai clic per spostare il cursore.</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
+        <v>Ingresso (stop rispetto al bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B557" t="str">
-        <v>Guadagno (stop log2)</v>
+        <v>Headroom del display (stop)</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B558" t="str">
-        <v>Curva tonale dei grigi a questo margine</v>
+        <v>Guadagno (stop)</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B559" t="str">
-        <v>Ingresso (× bianco di riferimento HDR)</v>
+        <v>Curva nel tag</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B560" t="str">
-        <v>Uscita (× bianco di riferimento HDR)</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>No change</v>
+        <v>Slider</v>
       </c>
       <c r="B561" t="str">
-        <v>Nessuna modifica</v>
+        <v>Cursore</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B562" t="str">
-        <v>Picco del display a {h} stop</v>
+        <v>Ingresso = picco del display</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Output at {h} stops</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B563" t="str">
-        <v>Uscita a {h} stop</v>
+        <v>Curve tonali del grigio per headroom</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B564" t="str">
-        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
+        <v>La curva tonale del grigio a ogni headroom memorizzato nel tag, colorata dal basso (blu) all’alto (rosso), con la curva del cursore in ambra. Entrambi gli assi sono in stop, quindi la diagonale indica nessuna modifica.</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Identify displays</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B565" t="str">
-        <v>Identifica i display</v>
+        <v>Uscita (stop rispetto al bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B566" t="str">
-        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
+        <v>{h} stop</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B567" t="str">
-        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
+        <v>{h} stop (base)</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B568" t="str">
-        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
+        <v>A {h} stop (cursore)</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B569" t="str">
-        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
+        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Could not identify displays.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B570" t="str">
-        <v>Impossibile identificare i display.</v>
+        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Display events</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B571" t="str">
-        <v>Eventi del display</v>
+        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B572" t="str">
-        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
+        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Colour primaries</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B573" t="str">
-        <v>Primari di colore</v>
+        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Transfer characteristics</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B574" t="str">
-        <v>Caratteristiche di trasferimento</v>
+        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Matrix coefficients</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B575" t="str">
-        <v>Coefficienti di matrice</v>
+        <v>Curva a {h} stop (nessun guadagno)</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Video full-range flag</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B576" t="str">
-        <v>Flag intervallo video completo</v>
+        <v>Curva a {h} stop</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Full range</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B577" t="str">
-        <v>Intervallo completo</v>
+        <v>Applicato a {h} stop</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Narrow range</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B578" t="str">
-        <v>Intervallo ridotto</v>
+        <v>Guadagno applicato a questo margine</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B579" t="str">
-        <v>non assegnato da ITU-T H.273</v>
+        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B580" t="str">
-        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
+        <v>Guadagno (stop log2)</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B581" t="str">
-        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
+        <v>Curva tonale dei grigi a questo margine</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>REPORT</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B582" t="str">
-        <v>RAPPORTO</v>
+        <v>Ingresso (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>FAIL</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B583" t="str">
-        <v>NON SUPERATO</v>
+        <v>Uscita (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>checks</v>
+        <v>No change</v>
       </c>
       <c r="B584" t="str">
-        <v>controlli</v>
+        <v>Nessuna modifica</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B585" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>Picco del display a {h} stop</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B586" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Uscita a {h} stop</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>ICC Profile Tool</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B587" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Powered by {lib}</v>
+        <v>Identify displays</v>
       </c>
       <c r="B588" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Identifica i display</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Subscribe</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B589" t="str">
-        <v>Iscriviti</v>
+        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B590" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Get notified about new releases</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B591" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Close</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B592" t="str">
-        <v>Chiudi</v>
+        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B593" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Impossibile identificare i display.</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Email address</v>
+        <v>Display events</v>
       </c>
       <c r="B594" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>Eventi del display</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>you@example.com</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B595" t="str">
-        <v>tu@esempio.com</v>
+        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B596" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>Primari di colore</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>(optional)</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B597" t="str">
-        <v>(opzionale)</v>
+        <v>Caratteristiche di trasferimento</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B598" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>Coefficienti di matrice</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B599" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>Flag intervallo video completo</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Cancel</v>
+        <v>Full range</v>
       </c>
       <c r="B600" t="str">
-        <v>Annulla</v>
+        <v>Intervallo completo</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Subscribe</v>
+        <v>Narrow range</v>
       </c>
       <c r="B601" t="str">
-        <v>Iscriviti</v>
+        <v>Intervallo ridotto</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B602" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>non assegnato da ITU-T H.273</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B603" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Close</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B604" t="str">
-        <v>Chiudi</v>
+        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Privacy notice</v>
+        <v>REPORT</v>
       </c>
       <c r="B605" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>FAIL</v>
       </c>
       <c r="B606" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>checks</v>
       </c>
       <c r="B607" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B608" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B609" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Network error. Please try again.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B610" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Error:</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B611" t="str">
-        <v>Errore:</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Convert to XML</v>
+        <v>Subscribe</v>
       </c>
       <c r="B612" t="str">
-        <v>Converti in XML</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Convert to JSON</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B613" t="str">
-        <v>Converti in JSON</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Convert to ICC</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B614" t="str">
-        <v>Converti in ICC</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Converting to XML…</v>
+        <v>Close</v>
       </c>
       <c r="B615" t="str">
-        <v>Conversione in XML…</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Converting to JSON…</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B616" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Converting to ICC…</v>
+        <v>Email address</v>
       </c>
       <c r="B617" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Load ICC profile</v>
+        <v>you@example.com</v>
       </c>
       <c r="B618" t="str">
-        <v>Carica profilo ICC</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B619" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Profile ID</v>
+        <v>(optional)</v>
       </c>
       <c r="B620" t="str">
-        <v>ID profilo</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>No tags found.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B621" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Tag Name</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B622" t="str">
-        <v>Nome tag</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>ID</v>
+        <v>Cancel</v>
       </c>
       <c r="B623" t="str">
-        <v>ID</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Offset</v>
+        <v>Subscribe</v>
       </c>
       <c r="B624" t="str">
-        <v>Offset</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Size</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B625" t="str">
-        <v>Dimensione</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Pad</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B626" t="str">
-        <v>Riempimento</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Bytes changed since load</v>
+        <v>Close</v>
       </c>
       <c r="B627" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Type</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B628" t="str">
-        <v>Tipo</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Array of {type}</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B629" t="str">
-        <v>Array di {type}</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>(No content)</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B630" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>bytes</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B631" t="str">
-        <v>byte</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Loading full description…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B632" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Could not load full description:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B633" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error:</v>
       </c>
       <c r="B634" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B635" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>No validation output</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B636" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Profile is valid</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B637" t="str">
-        <v>Il profilo è valido</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B638" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B639" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Critical validation error</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B640" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Unknown validation status</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B641" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B642" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B643" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Valid</v>
+        <v>No tags found.</v>
       </c>
       <c r="B644" t="str">
-        <v>Valido</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Warning</v>
+        <v>Tag Name</v>
       </c>
       <c r="B645" t="str">
-        <v>Avviso</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Error</v>
+        <v>ID</v>
       </c>
       <c r="B646" t="str">
-        <v>Errore</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Unknown</v>
+        <v>Offset</v>
       </c>
       <c r="B647" t="str">
-        <v>Sconosciuto</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Pass</v>
+        <v>Size</v>
       </c>
       <c r="B648" t="str">
-        <v>Superato</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Fail</v>
+        <v>Pad</v>
       </c>
       <c r="B649" t="str">
-        <v>Non superato</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>View in context</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B650" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Validation detail</v>
+        <v>Type</v>
       </c>
       <c r="B651" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Triggered by</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B652" t="str">
-        <v>Attivato da</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Field</v>
+        <v>(No content)</v>
       </c>
       <c r="B653" t="str">
-        <v>Campo</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Current value</v>
+        <v>bytes</v>
       </c>
       <c r="B654" t="str">
-        <v>Valore attuale</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Required: 0</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B655" t="str">
-        <v>Richiesto: 0</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B656" t="str">
-        <v>Atteso: {value}</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Invalid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B657" t="str">
-        <v>Non valido</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B658" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Close</v>
+        <v>No validation output</v>
       </c>
       <c r="B659" t="str">
-        <v>Chiudi</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Loading XML editor…</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B660" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B661" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B662" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B663" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B664" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B665" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B666" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Valid</v>
       </c>
       <c r="B667" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>indent</v>
+        <v>Warning</v>
       </c>
       <c r="B668" t="str">
-        <v>rientro</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>sort keys</v>
+        <v>Error</v>
       </c>
       <c r="B669" t="str">
-        <v>ordina chiavi</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B670" t="str">
+        <v>Sconosciuto</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B671" t="str">
+        <v>Superato</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B672" t="str">
+        <v>Non superato</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B673" t="str">
+        <v>Mostra nel contesto</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B674" t="str">
+        <v>Dettaglio convalida</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B675" t="str">
+        <v>Attivato da</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B676" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B677" t="str">
+        <v>Valore attuale</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B678" t="str">
+        <v>Richiesto: 0</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B679" t="str">
+        <v>Atteso: {value}</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B680" t="str">
+        <v>Non valido</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B681" t="str">
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B682" t="str">
+        <v>Chiudi</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B683" t="str">
+        <v>Caricamento editor XML…</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B684" t="str">
+        <v>Caricamento editor JSON…</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B685" t="str">
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B686" t="str">
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B687" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B688" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B689" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B690" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B691" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B692" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B670" t="str">
+      <c r="B693" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B670"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B693"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B693"/>
+  <dimension ref="A1:B700"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4587,1375 +4587,1431 @@
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Target headroom</v>
+        <v>Linear values</v>
       </c>
       <c r="B523" t="str">
-        <v>Margine di destinazione</v>
+        <v>Valori lineari</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B524" t="str">
-        <v>{r}× il bianco di riferimento ({n} stop)</v>
+        <v>File 1,0 = bianco di riferimento HDR</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Tone mapping</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B525" t="str">
-        <v>Tone mapping</v>
+        <v>File 1,0 = 1 cd/m² (ICC.1 clausola 8.10.2 a)</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B526" t="str">
-        <v>Auto (classifica della clausola 8.10.3)</v>
+        <v>I file OpenEXR e Radiance HDR pongono per convenzione il bianco SDR a 1,0, mentre un trasferimento ICC lineare legge 1,0 come 1 cd/m². Per impostazione predefinita il file viene scalato in modo che il suo 1,0 cada sul bianco di riferimento HDR del profilo.</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Input scale</v>
       </c>
       <c r="B527" t="str">
-        <v>Curva di guadagno (HAGC)</v>
+        <v>Scala di ingresso</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B528" t="str">
-        <v>Ripiego SDR precalcolato (AToB0)</v>
+        <v>×{w} — file 1,0 = bianco di riferimento</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B529" t="str">
-        <v>Disattivato — come un CMM precedente all’emendamento</v>
+        <v>nessuna — file 1,0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Applying the profile…</v>
+        <v>Target headroom</v>
       </c>
       <c r="B530" t="str">
-        <v>Applicazione del profilo…</v>
+        <v>Margine di destinazione</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B531" t="str">
-        <v>{format} contiene luce lineare, quindi serve un profilo con trasferimento Linear (8).</v>
+        <v>{r}× il bianco di riferimento ({n} stop)</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B532" t="str">
-        <v>Per assegnare un profilo serve un’immagine RGB a 3 canali.</v>
+        <v>Tone mapping</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B533" t="str">
-        <v>Per interpretarne i valori, assegna un profilo qui sopra.</v>
+        <v>Auto (classifica della clausola 8.10.3)</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>HDR Profiles</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B534" t="str">
-        <v>Profili HDR</v>
+        <v>Curva di guadagno (HAGC)</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Linear transfer</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B535" t="str">
-        <v>Trasferimento lineare</v>
+        <v>Ripiego SDR precalcolato (AToB0)</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B536" t="str">
-        <v>Trasferimento non lineare (PQ, HLG)</v>
+        <v>Disattivato — come un CMM precedente all’emendamento</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B537" t="str">
-        <v>Profili HDR — trasferimento lineare</v>
+        <v>Applicazione del profilo…</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B538" t="str">
-        <v>Profili HDR — trasferimento PQ / HLG</v>
+        <v>{format} contiene luce lineare, quindi serve un profilo con trasferimento Linear (8).</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B539" t="str">
-        <v>{format} contiene luce lineare, quindi si possono assegnare solo profili HDR con trasferimento lineare.</v>
+        <v>Per assegnare un profilo serve un’immagine RGB a 3 canali.</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B540" t="str">
-        <v>{n} profilo/i HDR PQ/HLG nel pool non sono proposti — il pannello Profili li elenca sotto Profili HDR › Trasferimento non lineare.</v>
+        <v>Per interpretarne i valori, assegna un profilo qui sopra.</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B541" t="str">
-        <v>Nel pool non c’è ancora un profilo HDR con trasferimento lineare; il pannello Profili raggruppa i profili HDR per trasferimento.</v>
+        <v>Profili HDR</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B542" t="str">
-        <v>IccProfLib non applica questa curva di guadagno: {why}. Un CMM passa al descrittore di tone mapping successivo (clausola 8.10.3).</v>
+        <v>Trasferimento lineare</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Display headroom</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B543" t="str">
-        <v>Margine del display</v>
+        <v>Trasferimento non lineare (PQ, HLG)</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B544" t="str">
-        <v>{n} stop (≈{r}× il bianco di riferimento)</v>
+        <v>Profili HDR — trasferimento lineare</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>Baseline</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B545" t="str">
-        <v>Base</v>
+        <v>Profili HDR — trasferimento PQ / HLG</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>Preview through the colour engine</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B546" t="str">
-        <v>Anteprima tramite il motore colore</v>
+        <v>{format} contiene luce lineare, quindi si possono assegnare solo profili HDR con trasferimento lineare.</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B547" t="str">
-        <v>Come creata (base {h} stop, senza guadagno)</v>
+        <v>{n} profilo/i HDR PQ/HLG nel pool non sono proposti — il pannello Profili li elenca sotto Profili HDR › Trasferimento non lineare.</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B548" t="str">
-        <v>Mappata per {h} stop</v>
+        <v>Nel pool non c’è ancora un profilo HDR con trasferimento lineare; il pannello Profili raggruppa i profili HDR per trasferimento.</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B549" t="str">
-        <v>Gli stessi pixel di prova (segnale {transfer} crescente da sinistra a destra: grigio, poi R, G, B, Y, C, M) attraverso la trasformazione HDR di IccProfLib. Entrambe le strisce sono limitate a {r}× il bianco di riferimento HDR, come le mostrerebbe un display con {h} stop di headroom: dove la striscia superiore satura piatta, la curva di guadagno attenua le alte luci.</v>
+        <v>IccProfLib non applica questa curva di guadagno: {why}. Un CMM passa al descrittore di tone mapping successivo (clausola 8.10.3).</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>reference white</v>
+        <v>Display headroom</v>
       </c>
       <c r="B550" t="str">
-        <v>bianco di riferimento</v>
+        <v>Margine del display</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>display peak</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B551" t="str">
-        <v>picco del display</v>
+        <v>{n} stop (≈{r}× il bianco di riferimento)</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>Baseline</v>
       </c>
       <c r="B552" t="str">
-        <v>Anteprima non disponibile: {why}</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B553" t="str">
-        <v>il motore colore non ha seguito il percorso HDR per questo profilo</v>
+        <v>Anteprima tramite il motore colore</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>Gain across every headroom</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B554" t="str">
-        <v>Guadagno a ogni headroom</v>
+        <v>Come creata (base {h} stop, senza guadagno)</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B555" t="str">
-        <v>Guadagno applicato a un ingresso grigio a ogni headroom del display: il blu comprime, il rosso espande, il bianco lo lascia invariato. Le linee punteggiate indicano le curve del tag, quella continua la base, quella ambra il cursore; la diagonale tratteggiata è dove l’ingresso raggiunge il picco del display. Fai clic per spostare il cursore.</v>
+        <v>Mappata per {h} stop</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B556" t="str">
-        <v>Ingresso (stop rispetto al bianco di riferimento HDR)</v>
+        <v>Gli stessi pixel di prova (segnale {transfer} crescente da sinistra a destra: grigio, poi R, G, B, Y, C, M) attraverso la trasformazione HDR di IccProfLib. Entrambe le strisce sono limitate a {r}× il bianco di riferimento HDR, come le mostrerebbe un display con {h} stop di headroom: dove la striscia superiore satura piatta, la curva di guadagno attenua le alte luci.</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Display headroom (stops)</v>
+        <v>reference white</v>
       </c>
       <c r="B557" t="str">
-        <v>Headroom del display (stop)</v>
+        <v>bianco di riferimento</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Gain (stops)</v>
+        <v>display peak</v>
       </c>
       <c r="B558" t="str">
-        <v>Guadagno (stop)</v>
+        <v>picco del display</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Curve in the tag</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B559" t="str">
-        <v>Curva nel tag</v>
+        <v>Anteprima non disponibile: {why}</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Baseline</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B560" t="str">
-        <v>Base</v>
+        <v>il motore colore non ha seguito il percorso HDR per questo profilo</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Slider</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B561" t="str">
-        <v>Cursore</v>
+        <v>Guadagno a ogni headroom</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Input = display peak</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B562" t="str">
-        <v>Ingresso = picco del display</v>
+        <v>Guadagno applicato a un ingresso grigio a ogni headroom del display: il blu comprime, il rosso espande, il bianco lo lascia invariato. Le linee punteggiate indicano le curve del tag, quella continua la base, quella ambra il cursore; la diagonale tratteggiata è dove l’ingresso raggiunge il picco del display. Fai clic per spostare il cursore.</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B563" t="str">
-        <v>Curve tonali del grigio per headroom</v>
+        <v>Ingresso (stop rispetto al bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B564" t="str">
-        <v>La curva tonale del grigio a ogni headroom memorizzato nel tag, colorata dal basso (blu) all’alto (rosso), con la curva del cursore in ambra. Entrambi gli assi sono in stop, quindi la diagonale indica nessuna modifica.</v>
+        <v>Headroom del display (stop)</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B565" t="str">
-        <v>Uscita (stop rispetto al bianco di riferimento HDR)</v>
+        <v>Guadagno (stop)</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>{h} stops</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B566" t="str">
-        <v>{h} stop</v>
+        <v>Curva nel tag</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>Baseline</v>
       </c>
       <c r="B567" t="str">
-        <v>{h} stop (base)</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>Slider</v>
       </c>
       <c r="B568" t="str">
-        <v>A {h} stop (cursore)</v>
+        <v>Cursore</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B569" t="str">
-        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
+        <v>Ingresso = picco del display</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B570" t="str">
-        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
+        <v>Curve tonali del grigio per headroom</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B571" t="str">
-        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
+        <v>La curva tonale del grigio a ogni headroom memorizzato nel tag, colorata dal basso (blu) all’alto (rosso), con la curva del cursore in ambra. Entrambi gli assi sono in stop, quindi la diagonale indica nessuna modifica.</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B572" t="str">
-        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
+        <v>Uscita (stop rispetto al bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B573" t="str">
-        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
+        <v>{h} stop</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B574" t="str">
-        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
+        <v>{h} stop (base)</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B575" t="str">
-        <v>Curva a {h} stop (nessun guadagno)</v>
+        <v>A {h} stop (cursore)</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B576" t="str">
-        <v>Curva a {h} stop</v>
+        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Applied at {h} stops</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B577" t="str">
-        <v>Applicato a {h} stop</v>
+        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B578" t="str">
-        <v>Guadagno applicato a questo margine</v>
+        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B579" t="str">
-        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
+        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B580" t="str">
-        <v>Guadagno (stop log2)</v>
+        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B581" t="str">
-        <v>Curva tonale dei grigi a questo margine</v>
+        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B582" t="str">
-        <v>Ingresso (× bianco di riferimento HDR)</v>
+        <v>Curva a {h} stop (nessun guadagno)</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B583" t="str">
-        <v>Uscita (× bianco di riferimento HDR)</v>
+        <v>Curva a {h} stop</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>No change</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B584" t="str">
-        <v>Nessuna modifica</v>
+        <v>Applicato a {h} stop</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B585" t="str">
-        <v>Picco del display a {h} stop</v>
+        <v>Guadagno applicato a questo margine</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Output at {h} stops</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B586" t="str">
-        <v>Uscita a {h} stop</v>
+        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B587" t="str">
-        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
+        <v>Guadagno (stop log2)</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Identify displays</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B588" t="str">
-        <v>Identifica i display</v>
+        <v>Curva tonale dei grigi a questo margine</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B589" t="str">
-        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
+        <v>Ingresso (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B590" t="str">
-        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
+        <v>Uscita (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>No change</v>
       </c>
       <c r="B591" t="str">
-        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
+        <v>Nessuna modifica</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B592" t="str">
-        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
+        <v>Picco del display a {h} stop</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Could not identify displays.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B593" t="str">
-        <v>Impossibile identificare i display.</v>
+        <v>Uscita a {h} stop</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Display events</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B594" t="str">
-        <v>Eventi del display</v>
+        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B595" t="str">
-        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
+        <v>Identifica i display</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Colour primaries</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B596" t="str">
-        <v>Primari di colore</v>
+        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Transfer characteristics</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B597" t="str">
-        <v>Caratteristiche di trasferimento</v>
+        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Matrix coefficients</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B598" t="str">
-        <v>Coefficienti di matrice</v>
+        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Video full-range flag</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B599" t="str">
-        <v>Flag intervallo video completo</v>
+        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Full range</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B600" t="str">
-        <v>Intervallo completo</v>
+        <v>Impossibile identificare i display.</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Narrow range</v>
+        <v>Display events</v>
       </c>
       <c r="B601" t="str">
-        <v>Intervallo ridotto</v>
+        <v>Eventi del display</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B602" t="str">
-        <v>non assegnato da ITU-T H.273</v>
+        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B603" t="str">
-        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
+        <v>Primari di colore</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B604" t="str">
-        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
+        <v>Caratteristiche di trasferimento</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>REPORT</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B605" t="str">
-        <v>RAPPORTO</v>
+        <v>Coefficienti di matrice</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>FAIL</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B606" t="str">
-        <v>NON SUPERATO</v>
+        <v>Flag intervallo video completo</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>checks</v>
+        <v>Full range</v>
       </c>
       <c r="B607" t="str">
-        <v>controlli</v>
+        <v>Intervallo completo</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Narrow range</v>
       </c>
       <c r="B608" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>Intervallo ridotto</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B609" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>non assegnato da ITU-T H.273</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B610" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Powered by {lib}</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B611" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Subscribe</v>
+        <v>REPORT</v>
       </c>
       <c r="B612" t="str">
-        <v>Iscriviti</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>FAIL</v>
       </c>
       <c r="B613" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Get notified about new releases</v>
+        <v>checks</v>
       </c>
       <c r="B614" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Close</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B615" t="str">
-        <v>Chiudi</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B616" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>Email address</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B617" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>you@example.com</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B618" t="str">
-        <v>tu@esempio.com</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Subscribe</v>
       </c>
       <c r="B619" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>(optional)</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B620" t="str">
-        <v>(opzionale)</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B621" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Close</v>
       </c>
       <c r="B622" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Cancel</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B623" t="str">
-        <v>Annulla</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Subscribe</v>
+        <v>Email address</v>
       </c>
       <c r="B624" t="str">
-        <v>Iscriviti</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B625" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B626" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Close</v>
+        <v>(optional)</v>
       </c>
       <c r="B627" t="str">
-        <v>Chiudi</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Privacy notice</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B628" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B629" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Cancel</v>
       </c>
       <c r="B630" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B631" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B632" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B633" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Error:</v>
+        <v>Close</v>
       </c>
       <c r="B634" t="str">
-        <v>Errore:</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Convert to XML</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B635" t="str">
-        <v>Converti in XML</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Convert to JSON</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B636" t="str">
-        <v>Converti in JSON</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Convert to ICC</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B637" t="str">
-        <v>Converti in ICC</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Converting to XML…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B638" t="str">
-        <v>Conversione in XML…</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Converting to JSON…</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B639" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Converting to ICC…</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B640" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Load ICC profile</v>
+        <v>Error:</v>
       </c>
       <c r="B641" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B642" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Profile ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B643" t="str">
-        <v>ID profilo</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>No tags found.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B644" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Tag Name</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B645" t="str">
-        <v>Nome tag</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B646" t="str">
-        <v>ID</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Offset</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B647" t="str">
-        <v>Offset</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Size</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B648" t="str">
-        <v>Dimensione</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Pad</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B649" t="str">
-        <v>Riempimento</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile ID</v>
       </c>
       <c r="B650" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Type</v>
+        <v>No tags found.</v>
       </c>
       <c r="B651" t="str">
-        <v>Tipo</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Array of {type}</v>
+        <v>Tag Name</v>
       </c>
       <c r="B652" t="str">
-        <v>Array di {type}</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>(No content)</v>
+        <v>ID</v>
       </c>
       <c r="B653" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>bytes</v>
+        <v>Offset</v>
       </c>
       <c r="B654" t="str">
-        <v>byte</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Loading full description…</v>
+        <v>Size</v>
       </c>
       <c r="B655" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Could not load full description:</v>
+        <v>Pad</v>
       </c>
       <c r="B656" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B657" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Type</v>
       </c>
       <c r="B658" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>No validation output</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B659" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Profile is valid</v>
+        <v>(No content)</v>
       </c>
       <c r="B660" t="str">
-        <v>Il profilo è valido</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Profile has warning(s)</v>
+        <v>bytes</v>
       </c>
       <c r="B661" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B662" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Critical validation error</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B663" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Unknown validation status</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B664" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B665" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>No warnings or errors found.</v>
+        <v>No validation output</v>
       </c>
       <c r="B666" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Valid</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B667" t="str">
-        <v>Valido</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Warning</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B668" t="str">
-        <v>Avviso</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B669" t="str">
-        <v>Errore</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Unknown</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B670" t="str">
-        <v>Sconosciuto</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Pass</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B671" t="str">
-        <v>Superato</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Fail</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B672" t="str">
-        <v>Non superato</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>View in context</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B673" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Validation detail</v>
+        <v>Valid</v>
       </c>
       <c r="B674" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Triggered by</v>
+        <v>Warning</v>
       </c>
       <c r="B675" t="str">
-        <v>Attivato da</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Field</v>
+        <v>Error</v>
       </c>
       <c r="B676" t="str">
-        <v>Campo</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Current value</v>
+        <v>Unknown</v>
       </c>
       <c r="B677" t="str">
-        <v>Valore attuale</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Required: 0</v>
+        <v>Pass</v>
       </c>
       <c r="B678" t="str">
-        <v>Richiesto: 0</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Expected: {value}</v>
+        <v>Fail</v>
       </c>
       <c r="B679" t="str">
-        <v>Atteso: {value}</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Invalid</v>
+        <v>View in context</v>
       </c>
       <c r="B680" t="str">
-        <v>Non valido</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Validation detail</v>
       </c>
       <c r="B681" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Close</v>
+        <v>Triggered by</v>
       </c>
       <c r="B682" t="str">
-        <v>Chiudi</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Loading XML editor…</v>
+        <v>Field</v>
       </c>
       <c r="B683" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Current value</v>
       </c>
       <c r="B684" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Required: 0</v>
       </c>
       <c r="B685" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B686" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Invalid</v>
       </c>
       <c r="B687" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B688" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Close</v>
       </c>
       <c r="B689" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B690" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Caricamento editor XML…</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>indent</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B691" t="str">
-        <v>rientro</v>
+        <v>Caricamento editor JSON…</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>sort keys</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B692" t="str">
-        <v>ordina chiavi</v>
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B693" t="str">
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B694" t="str">
+        <v>● modifiche XML non salvate</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B695" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B696" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B697" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B698" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B699" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B693" t="str">
+      <c r="B700" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B693"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B700"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -4662,7 +4662,7 @@
         <v>Tone mapping</v>
       </c>
       <c r="B532" t="str">
-        <v>Tone mapping</v>
+        <v>Mappatura dei toni</v>
       </c>
     </row>
     <row r="533">

--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B700"/>
+  <dimension ref="A1:B705"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -4123,1895 +4123,1935 @@
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>Decoding…</v>
+        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
       </c>
       <c r="B465" t="str">
-        <v>Decodifica…</v>
+        <v>Questo file è di {size} MB; la scheda HDR apre immagini fino a {max} MB.</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Dynamic range</v>
+        <v>Could not apply the profile:</v>
       </c>
       <c r="B466" t="str">
-        <v>Gamma dinamica</v>
+        <v>Impossibile applicare il profilo:</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Could not draw the image:</v>
       </c>
       <c r="B467" t="str">
-        <v>Questo browser offre solo i due estremi, non una miscela.</v>
+        <v>Impossibile disegnare l’immagine:</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
       </c>
       <c r="B468" t="str">
-        <v>decodificato da profiletool stesso, quindi indipendente dal browser</v>
+        <v>(questi primari non definiscono uno spazio colore — ignorati, si usa Rec. 709)</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>this browser decodes it</v>
+        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
       </c>
       <c r="B469" t="str">
-        <v>questo browser lo decodifica</v>
+        <v>il profilo di un JPEG XL è compresso nel codestream, che profiletool non decomprime ancora</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>this browser does not decode it</v>
+        <v>Decoding…</v>
       </c>
       <c r="B470" t="str">
-        <v>questo browser non lo decodifica</v>
+        <v>Decodifica…</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B471" t="str">
-        <v>la visualizzazione HEIC richiede Safari o un altro browser WebKit — Chrome e Firefox non decodificano HEIC su nessuna piattaforma, macOS compreso</v>
+        <v>Gamma dinamica</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B472" t="str">
-        <v>la visualizzazione JPEG XL richiede Safari; gli altri browser non lo supportano ancora</v>
+        <v>Questo browser offre solo i due estremi, non una miscela.</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>deferred to a later release</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B473" t="str">
-        <v>rinviato a una versione successiva</v>
+        <v>decodificato da profiletool stesso, quindi indipendente dal browser</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B474" t="str">
-        <v>questo display non segnala alcun percorso HDR, quindi l’HDR è reso in SDR con tone mapping</v>
+        <v>questo browser lo decodifica</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B475" t="str">
-        <v>questo browser non offre un canvas HDR (serve canvas float16 o WebGPU)</v>
+        <v>questo browser non lo decodifica</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B476" t="str">
-        <v>Firefox non mostra immagini HDR e non legge gain map; i contenuti HDR sono mostrati in SDR</v>
+        <v>la visualizzazione HEIC richiede Safari o un altro browser WebKit — Chrome e Firefox non decodificano HEIC su nessuna piattaforma, macOS compreso</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B477" t="str">
-        <v>l’ispezione richiede solo l’analisi del contenitore, non un codec</v>
+        <v>la visualizzazione JPEG XL richiede Safari; gli altri browser non lo supportano ancora</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B478" t="str">
-        <v>display HDR e canvas HDR sono entrambi disponibili</v>
+        <v>rinviato a una versione successiva</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>unknown format</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B479" t="str">
-        <v>formato sconosciuto</v>
+        <v>questo display non segnala alcun percorso HDR, quindi l’HDR è reso in SDR con tone mapping</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>{browser} on {os}</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B480" t="str">
-        <v>{browser} su {os}</v>
+        <v>questo browser non offre un canvas HDR (serve canvas float16 o WebGPU)</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B481" t="str">
-        <v>{name} · display HDR rilevato</v>
+        <v>Firefox non mostra immagini HDR e non legge gain map; i contenuti HDR sono mostrati in SDR</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>{name} · SDR display</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B482" t="str">
-        <v>{name} · display SDR</v>
+        <v>l’ispezione richiede solo l’analisi del contenitore, non un codec</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B483" t="str">
-        <v>WebGPU ha applicato il tone mapping «{mode}», quindi l’uscita è limitata a SDR</v>
+        <v>display HDR e canvas HDR sono entrambi disponibili</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>unknown format</v>
       </c>
       <c r="B484" t="str">
-        <v>Questo browser non indica il tone mapping WebGPU applicato, quindi l’uscita HDR non è confermata</v>
+        <v>formato sconosciuto</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>Display peak</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B485" t="str">
-        <v>Picco del display</v>
+        <v>{browser} su {os}</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B486" t="str">
-        <v>{r}× il bianco SDR ({n} stop)</v>
+        <v>{name} · display HDR rilevato</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>1× — SDR display</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B487" t="str">
-        <v>1× — display SDR</v>
+        <v>{name} · display SDR</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>not known</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B488" t="str">
-        <v>non noto</v>
+        <v>WebGPU ha applicato il tone mapping «{mode}», quindi l’uscita è limitata a SDR</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B489" t="str">
-        <v>Questo display non segnala HDR, quindi il browser mostra l’immagine in SDR a entrambi gli estremi.</v>
+        <v>Questo browser non indica il tone mapping WebGPU applicato, quindi l’uscita HDR non è confermata</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>Display peak</v>
       </c>
       <c r="B490" t="str">
-        <v>Questo display non segnala HDR, quindi tutto ciò che supera il bianco SDR viene tagliato. «Adatta al display» mostra invece la resa con tone mapping.</v>
+        <v>Picco del display</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B491" t="str">
-        <v>Questa immagine richiede {img}× il bianco SDR, ma questo display arriva solo a {disp}×, quindi i valori più luminosi vengono tagliati. «Adatta al display» li attenua verso il picco del display.</v>
+        <v>{r}× il bianco SDR ({n} stop)</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>Fit to display</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B492" t="str">
-        <v>Adatta al display</v>
+        <v>1× — display SDR</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>Image details</v>
+        <v>not known</v>
       </c>
       <c r="B493" t="str">
-        <v>Dettagli immagine</v>
+        <v>non noto</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B494" t="str">
-        <v>non disponibile — il browser rende questa immagine e non può limitarla a un picco dato</v>
+        <v>Questo display non segnala HDR, quindi il browser mostra l’immagine in SDR a entrambi gli estremi.</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>not available — this output shows nothing above SDR white</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B495" t="str">
-        <v>non disponibile — questa uscita non mostra nulla sopra il bianco SDR</v>
+        <v>Questo display non segnala HDR, quindi tutto ciò che supera il bianco SDR viene tagliato. «Adatta al display» mostra invece la resa con tone mapping.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>not available — this display’s peak is not known</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B496" t="str">
-        <v>non disponibile — il picco di questo display non è noto</v>
+        <v>Questa immagine richiede {img}× il bianco SDR, ma questo display arriva solo a {disp}×, quindi i valori più luminosi vengono tagliati. «Adatta al display» li attenua verso il picco del display.</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Zoom in</v>
+        <v>Fit to display</v>
       </c>
       <c r="B497" t="str">
-        <v>Ingrandisci</v>
+        <v>Adatta al display</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Zoom out</v>
+        <v>Image details</v>
       </c>
       <c r="B498" t="str">
-        <v>Riduci</v>
+        <v>Dettagli immagine</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>Fit image</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B499" t="str">
-        <v>Adatta immagine</v>
+        <v>non disponibile — il browser rende questa immagine e non può limitarla a un picco dato</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>Actual pixels (1:1)</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B500" t="str">
-        <v>Pixel reali (1:1)</v>
+        <v>non disponibile — questa uscita non mostra nulla sopra il bianco SDR</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B501" t="str">
-        <v>Trascina per spostare · Ctrl+rotellina per lo zoom · doppio clic per ripristinare</v>
+        <v>non disponibile — il picco di questo display non è noto</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Drag to resize the image area; double-click to restore the default size</v>
+        <v>Zoom in</v>
       </c>
       <c r="B502" t="str">
-        <v>Trascina per ridimensionare l’area immagine; doppio clic per tornare alla dimensione predefinita</v>
+        <v>Ingrandisci</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Image view</v>
+        <v>Zoom out</v>
       </c>
       <c r="B503" t="str">
-        <v>Vista immagine</v>
+        <v>Riduci</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Fit image</v>
       </c>
       <c r="B504" t="str">
-        <v>Limita la luminosità al picco segnalato dal display. Su Windows questo valore può restare indietro rispetto ai cambi di luminosità.</v>
+        <v>Adatta immagine</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>no limit</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B505" t="str">
-        <v>nessun limite</v>
+        <v>Pixel reali (1:1)</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B506" t="str">
-        <v>limite {n} stop ({r}×)</v>
+        <v>Trascina per spostare · Ctrl+rotellina per lo zoom · doppio clic per ripristinare</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>SDR white</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B507" t="str">
-        <v>Bianco SDR</v>
+        <v>Trascina per ridimensionare l’area immagine; doppio clic per tornare alla dimensione predefinita</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>Image view</v>
       </c>
       <c r="B508" t="str">
-        <v>Bianco SDR semplice, per confronto. Su un display HDR le alte luci HDR appaiono più luminose di questo.</v>
+        <v>Vista immagine</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>SDR white patch</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B509" t="str">
-        <v>Riquadro bianco SDR</v>
+        <v>Limita la luminosità al picco segnalato dal display. Su Windows questo valore può restare indietro rispetto ai cambi di luminosità.</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>no limit</v>
       </c>
       <c r="B510" t="str">
-        <v>Trascinalo per spostarlo; doppio clic per rimetterlo accanto all’immagine.</v>
+        <v>nessun limite</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>Assign profile</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B511" t="str">
-        <v>Assegna profilo</v>
+        <v>limite {n} stop ({r}×)</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>None — use what the file signals</v>
+        <v>SDR white</v>
       </c>
       <c r="B512" t="str">
-        <v>Nessuno — secondo il file</v>
+        <v>Bianco SDR</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B513" t="str">
-        <v>Profilo incorporato ({n} B)</v>
+        <v>Bianco SDR semplice, per confronto. Su un display HDR le alte luci HDR appaiono più luminose di questo.</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B514" t="str">
-        <v>Profili HDR nel pool</v>
+        <v>Riquadro bianco SDR</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B515" t="str">
-        <v>Profilo</v>
+        <v>Trascinalo per spostarlo; doppio clic per rimetterlo accanto all’immagine.</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>embedded profile</v>
+        <v>Assign profile</v>
       </c>
       <c r="B516" t="str">
-        <v>profilo incorporato</v>
+        <v>Assegna profilo</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>Colour engine path</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B517" t="str">
-        <v>Percorso del motore colore</v>
+        <v>Nessuno — secondo il file</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B518" t="str">
-        <v>Percorso HDR, curva di guadagno applicata</v>
+        <v>Profilo incorporato ({n} B)</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B519" t="str">
-        <v>Percorso HDR, nessuna curva di guadagno</v>
+        <v>Profili HDR nel pool</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>Profile</v>
       </c>
       <c r="B520" t="str">
-        <v>AToB0 precalcolato — non il percorso HDR</v>
+        <v>Profilo</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>Transfer</v>
+        <v>embedded profile</v>
       </c>
       <c r="B521" t="str">
-        <v>Trasferimento</v>
+        <v>profilo incorporato</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>HDR reference white</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B522" t="str">
-        <v>Bianco di riferimento HDR</v>
+        <v>Percorso del motore colore</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>Linear values</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B523" t="str">
-        <v>Valori lineari</v>
+        <v>Percorso HDR, curva di guadagno applicata</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>File 1.0 = HDR reference white</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B524" t="str">
-        <v>File 1,0 = bianco di riferimento HDR</v>
+        <v>Percorso HDR, nessuna curva di guadagno</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B525" t="str">
-        <v>File 1,0 = 1 cd/m² (ICC.1 clausola 8.10.2 a)</v>
+        <v>AToB0 precalcolato — non il percorso HDR</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
+        <v>Transfer</v>
       </c>
       <c r="B526" t="str">
-        <v>I file OpenEXR e Radiance HDR pongono per convenzione il bianco SDR a 1,0, mentre un trasferimento ICC lineare legge 1,0 come 1 cd/m². Per impostazione predefinita il file viene scalato in modo che il suo 1,0 cada sul bianco di riferimento HDR del profilo.</v>
+        <v>Trasferimento</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>Input scale</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B527" t="str">
-        <v>Scala di ingresso</v>
+        <v>Bianco di riferimento HDR</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>×{w} — file 1.0 = reference white</v>
+        <v>Linear values</v>
       </c>
       <c r="B528" t="str">
-        <v>×{w} — file 1,0 = bianco di riferimento</v>
+        <v>Valori lineari</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>none — file 1.0 = 1 cd/m²</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B529" t="str">
-        <v>nessuna — file 1,0 = 1 cd/m²</v>
+        <v>File 1,0 = bianco di riferimento HDR</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>Target headroom</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B530" t="str">
-        <v>Margine di destinazione</v>
+        <v>File 1,0 = 1 cd/m² (ICC.1 clausola 8.10.2 a)</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B531" t="str">
-        <v>{r}× il bianco di riferimento ({n} stop)</v>
+        <v>I file OpenEXR e Radiance HDR pongono per convenzione il bianco SDR a 1,0, mentre un trasferimento ICC lineare legge 1,0 come 1 cd/m². Per impostazione predefinita il file viene scalato in modo che il suo 1,0 cada sul bianco di riferimento HDR del profilo.</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Tone mapping</v>
+        <v>Input scale</v>
       </c>
       <c r="B532" t="str">
-        <v>Mappatura dei toni</v>
+        <v>Scala di ingresso</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B533" t="str">
-        <v>Auto (classifica della clausola 8.10.3)</v>
+        <v>×{w} — file 1,0 = bianco di riferimento</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B534" t="str">
-        <v>Curva di guadagno (HAGC)</v>
+        <v>nessuna — file 1,0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B535" t="str">
-        <v>Ripiego SDR precalcolato (AToB0)</v>
+        <v>Margine di destinazione</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B536" t="str">
-        <v>Disattivato — come un CMM precedente all’emendamento</v>
+        <v>{r}× il bianco di riferimento ({n} stop)</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Applying the profile…</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B537" t="str">
-        <v>Applicazione del profilo…</v>
+        <v>Mappatura dei toni</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B538" t="str">
-        <v>{format} contiene luce lineare, quindi serve un profilo con trasferimento Linear (8).</v>
+        <v>Auto (classifica della clausola 8.10.3)</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B539" t="str">
-        <v>Per assegnare un profilo serve un’immagine RGB a 3 canali.</v>
+        <v>Curva di guadagno (HAGC)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B540" t="str">
-        <v>Per interpretarne i valori, assegna un profilo qui sopra.</v>
+        <v>Ripiego SDR precalcolato (AToB0)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>HDR Profiles</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B541" t="str">
-        <v>Profili HDR</v>
+        <v>Disattivato — come un CMM precedente all’emendamento</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Linear transfer</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B542" t="str">
-        <v>Trasferimento lineare</v>
+        <v>Applicazione del profilo…</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B543" t="str">
-        <v>Trasferimento non lineare (PQ, HLG)</v>
+        <v>{format} contiene luce lineare, quindi serve un profilo con trasferimento Linear (8).</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B544" t="str">
-        <v>Profili HDR — trasferimento lineare</v>
+        <v>Per assegnare un profilo serve un’immagine RGB a 3 canali.</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B545" t="str">
-        <v>Profili HDR — trasferimento PQ / HLG</v>
+        <v>Per interpretarne i valori, assegna un profilo qui sopra.</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B546" t="str">
-        <v>{format} contiene luce lineare, quindi si possono assegnare solo profili HDR con trasferimento lineare.</v>
+        <v>Profili HDR</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B547" t="str">
-        <v>{n} profilo/i HDR PQ/HLG nel pool non sono proposti — il pannello Profili li elenca sotto Profili HDR › Trasferimento non lineare.</v>
+        <v>Trasferimento lineare</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B548" t="str">
-        <v>Nel pool non c’è ancora un profilo HDR con trasferimento lineare; il pannello Profili raggruppa i profili HDR per trasferimento.</v>
+        <v>Trasferimento non lineare (PQ, HLG)</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B549" t="str">
-        <v>IccProfLib non applica questa curva di guadagno: {why}. Un CMM passa al descrittore di tone mapping successivo (clausola 8.10.3).</v>
+        <v>Profili HDR — trasferimento lineare</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>Display headroom</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>Margine del display</v>
+        <v>Profili HDR — trasferimento PQ / HLG</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B551" t="str">
-        <v>{n} stop (≈{r}× il bianco di riferimento)</v>
+        <v>{format} contiene luce lineare, quindi si possono assegnare solo profili HDR con trasferimento lineare.</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>Baseline</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B552" t="str">
-        <v>Base</v>
+        <v>{n} profilo/i HDR PQ/HLG nel pool non sono proposti — il pannello Profili li elenca sotto Profili HDR › Trasferimento non lineare.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>Preview through the colour engine</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>Anteprima tramite il motore colore</v>
+        <v>Nel pool non c’è ancora un profilo HDR con trasferimento lineare; il pannello Profili raggruppa i profili HDR per trasferimento.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B554" t="str">
-        <v>Come creata (base {h} stop, senza guadagno)</v>
+        <v>IccProfLib non applica questa curva di guadagno: {why}. Un CMM passa al descrittore di tone mapping successivo (clausola 8.10.3).</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>Display headroom</v>
       </c>
       <c r="B555" t="str">
-        <v>Mappata per {h} stop</v>
+        <v>Margine del display</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B556" t="str">
-        <v>Gli stessi pixel di prova (segnale {transfer} crescente da sinistra a destra: grigio, poi R, G, B, Y, C, M) attraverso la trasformazione HDR di IccProfLib. Entrambe le strisce sono limitate a {r}× il bianco di riferimento HDR, come le mostrerebbe un display con {h} stop di headroom: dove la striscia superiore satura piatta, la curva di guadagno attenua le alte luci.</v>
+        <v>{n} stop (≈{r}× il bianco di riferimento)</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>reference white</v>
+        <v>Baseline</v>
       </c>
       <c r="B557" t="str">
-        <v>bianco di riferimento</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>display peak</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B558" t="str">
-        <v>picco del display</v>
+        <v>Anteprima tramite il motore colore</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B559" t="str">
-        <v>Anteprima non disponibile: {why}</v>
+        <v>Come creata (base {h} stop, senza guadagno)</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B560" t="str">
-        <v>il motore colore non ha seguito il percorso HDR per questo profilo</v>
+        <v>Mappata per {h} stop</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Gain across every headroom</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B561" t="str">
-        <v>Guadagno a ogni headroom</v>
+        <v>Gli stessi pixel di prova (segnale {transfer} crescente da sinistra a destra: grigio, poi R, G, B, Y, C, M) attraverso la trasformazione HDR di IccProfLib. Entrambe le strisce sono limitate a {r}× il bianco di riferimento HDR, come le mostrerebbe un display con {h} stop di headroom: dove la striscia superiore satura piatta, la curva di guadagno attenua le alte luci.</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>reference white</v>
       </c>
       <c r="B562" t="str">
-        <v>Guadagno applicato a un ingresso grigio a ogni headroom del display: il blu comprime, il rosso espande, il bianco lo lascia invariato. Le linee punteggiate indicano le curve del tag, quella continua la base, quella ambra il cursore; la diagonale tratteggiata è dove l’ingresso raggiunge il picco del display. Fai clic per spostare il cursore.</v>
+        <v>bianco di riferimento</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>display peak</v>
       </c>
       <c r="B563" t="str">
-        <v>Ingresso (stop rispetto al bianco di riferimento HDR)</v>
+        <v>picco del display</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B564" t="str">
-        <v>Headroom del display (stop)</v>
+        <v>Anteprima non disponibile: {why}</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Gain (stops)</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B565" t="str">
-        <v>Guadagno (stop)</v>
+        <v>il motore colore non ha seguito il percorso HDR per questo profilo</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B566" t="str">
-        <v>Curva nel tag</v>
+        <v>Guadagno a ogni headroom</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Baseline</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B567" t="str">
-        <v>Base</v>
+        <v>Guadagno applicato a un ingresso grigio a ogni headroom del display: il blu comprime, il rosso espande, il bianco lo lascia invariato. Le linee punteggiate indicano le curve del tag, quella continua la base, quella ambra il cursore; la diagonale tratteggiata è dove l’ingresso raggiunge il picco del display. Fai clic per spostare il cursore.</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Slider</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B568" t="str">
-        <v>Cursore</v>
+        <v>Ingresso (stop rispetto al bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Input = display peak</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B569" t="str">
-        <v>Ingresso = picco del display</v>
+        <v>Headroom del display (stop)</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B570" t="str">
-        <v>Curve tonali del grigio per headroom</v>
+        <v>Guadagno (stop)</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B571" t="str">
-        <v>La curva tonale del grigio a ogni headroom memorizzato nel tag, colorata dal basso (blu) all’alto (rosso), con la curva del cursore in ambra. Entrambi gli assi sono in stop, quindi la diagonale indica nessuna modifica.</v>
+        <v>Curva nel tag</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>Baseline</v>
       </c>
       <c r="B572" t="str">
-        <v>Uscita (stop rispetto al bianco di riferimento HDR)</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>{h} stops</v>
+        <v>Slider</v>
       </c>
       <c r="B573" t="str">
-        <v>{h} stop</v>
+        <v>Cursore</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B574" t="str">
-        <v>{h} stop (base)</v>
+        <v>Ingresso = picco del display</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B575" t="str">
-        <v>A {h} stop (cursore)</v>
+        <v>Curve tonali del grigio per headroom</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B576" t="str">
-        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
+        <v>La curva tonale del grigio a ogni headroom memorizzato nel tag, colorata dal basso (blu) all’alto (rosso), con la curva del cursore in ambra. Entrambi gli assi sono in stop, quindi la diagonale indica nessuna modifica.</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B577" t="str">
-        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
+        <v>Uscita (stop rispetto al bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>{h} stops</v>
       </c>
       <c r="B578" t="str">
-        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
+        <v>{h} stop</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B579" t="str">
-        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
+        <v>{h} stop (base)</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B580" t="str">
-        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
+        <v>A {h} stop (cursore)</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B581" t="str">
-        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
+        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B582" t="str">
-        <v>Curva a {h} stop (nessun guadagno)</v>
+        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B583" t="str">
-        <v>Curva a {h} stop</v>
+        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Applied at {h} stops</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B584" t="str">
-        <v>Applicato a {h} stop</v>
+        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B585" t="str">
-        <v>Guadagno applicato a questo margine</v>
+        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B586" t="str">
-        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
+        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B587" t="str">
-        <v>Guadagno (stop log2)</v>
+        <v>Curva a {h} stop (nessun guadagno)</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B588" t="str">
-        <v>Curva tonale dei grigi a questo margine</v>
+        <v>Curva a {h} stop</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B589" t="str">
-        <v>Ingresso (× bianco di riferimento HDR)</v>
+        <v>Applicato a {h} stop</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B590" t="str">
-        <v>Uscita (× bianco di riferimento HDR)</v>
+        <v>Guadagno applicato a questo margine</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>No change</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B591" t="str">
-        <v>Nessuna modifica</v>
+        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B592" t="str">
-        <v>Picco del display a {h} stop</v>
+        <v>Guadagno (stop log2)</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Output at {h} stops</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B593" t="str">
-        <v>Uscita a {h} stop</v>
+        <v>Curva tonale dei grigi a questo margine</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B594" t="str">
-        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
+        <v>Ingresso (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Identify displays</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B595" t="str">
-        <v>Identifica i display</v>
+        <v>Uscita (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>No change</v>
       </c>
       <c r="B596" t="str">
-        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
+        <v>Nessuna modifica</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B597" t="str">
-        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
+        <v>Picco del display a {h} stop</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B598" t="str">
-        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
+        <v>Uscita a {h} stop</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B599" t="str">
-        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
+        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Could not identify displays.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B600" t="str">
-        <v>Impossibile identificare i display.</v>
+        <v>Identifica i display</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Display events</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B601" t="str">
-        <v>Eventi del display</v>
+        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B602" t="str">
-        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
+        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Colour primaries</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B603" t="str">
-        <v>Primari di colore</v>
+        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Transfer characteristics</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B604" t="str">
-        <v>Caratteristiche di trasferimento</v>
+        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Matrix coefficients</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B605" t="str">
-        <v>Coefficienti di matrice</v>
+        <v>Impossibile identificare i display.</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Video full-range flag</v>
+        <v>Display events</v>
       </c>
       <c r="B606" t="str">
-        <v>Flag intervallo video completo</v>
+        <v>Eventi del display</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Full range</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B607" t="str">
-        <v>Intervallo completo</v>
+        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Narrow range</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B608" t="str">
-        <v>Intervallo ridotto</v>
+        <v>Primari di colore</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B609" t="str">
-        <v>non assegnato da ITU-T H.273</v>
+        <v>Caratteristiche di trasferimento</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B610" t="str">
-        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
+        <v>Coefficienti di matrice</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B611" t="str">
-        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
+        <v>Flag intervallo video completo</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>REPORT</v>
+        <v>Full range</v>
       </c>
       <c r="B612" t="str">
-        <v>RAPPORTO</v>
+        <v>Intervallo completo</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>FAIL</v>
+        <v>Narrow range</v>
       </c>
       <c r="B613" t="str">
-        <v>NON SUPERATO</v>
+        <v>Intervallo ridotto</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>checks</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B614" t="str">
-        <v>controlli</v>
+        <v>non assegnato da ITU-T H.273</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B615" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B616" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>ICC Profile Tool</v>
+        <v>REPORT</v>
       </c>
       <c r="B617" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>Powered by {lib}</v>
+        <v>FAIL</v>
       </c>
       <c r="B618" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B619" t="str">
-        <v>Iscriviti</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B620" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B621" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B622" t="str">
-        <v>Chiudi</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B623" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Email address</v>
+        <v>Subscribe</v>
       </c>
       <c r="B624" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B625" t="str">
-        <v>tu@esempio.com</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B626" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>(optional)</v>
+        <v>Close</v>
       </c>
       <c r="B627" t="str">
-        <v>(opzionale)</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B628" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Email address</v>
       </c>
       <c r="B629" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Cancel</v>
+        <v>you@example.com</v>
       </c>
       <c r="B630" t="str">
-        <v>Annulla</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>Subscribe</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B631" t="str">
-        <v>Iscriviti</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>(optional)</v>
       </c>
       <c r="B632" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B633" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>Close</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B634" t="str">
-        <v>Chiudi</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Privacy notice</v>
+        <v>Cancel</v>
       </c>
       <c r="B635" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B636" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B637" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B638" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B639" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B640" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Error:</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B641" t="str">
-        <v>Errore:</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Convert to XML</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B642" t="str">
-        <v>Converti in XML</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Convert to JSON</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B643" t="str">
-        <v>Converti in JSON</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Convert to ICC</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B644" t="str">
-        <v>Converti in ICC</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Converting to XML…</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>Conversione in XML…</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Converting to JSON…</v>
+        <v>Error:</v>
       </c>
       <c r="B646" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B647" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B648" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B649" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Profile ID</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B650" t="str">
-        <v>ID profilo</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>No tags found.</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B651" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Tag Name</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B652" t="str">
-        <v>Nome tag</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B653" t="str">
-        <v>ID</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Offset</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B654" t="str">
-        <v>Offset</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Size</v>
+        <v>Profile ID</v>
       </c>
       <c r="B655" t="str">
-        <v>Dimensione</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Pad</v>
+        <v>No tags found.</v>
       </c>
       <c r="B656" t="str">
-        <v>Riempimento</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Bytes changed since load</v>
+        <v>Tag Name</v>
       </c>
       <c r="B657" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Type</v>
+        <v>ID</v>
       </c>
       <c r="B658" t="str">
-        <v>Tipo</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Array of {type}</v>
+        <v>Offset</v>
       </c>
       <c r="B659" t="str">
-        <v>Array di {type}</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>(No content)</v>
+        <v>Size</v>
       </c>
       <c r="B660" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>bytes</v>
+        <v>Pad</v>
       </c>
       <c r="B661" t="str">
-        <v>byte</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Loading full description…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B662" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Could not load full description:</v>
+        <v>Type</v>
       </c>
       <c r="B663" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B664" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>(No content)</v>
       </c>
       <c r="B665" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>No validation output</v>
+        <v>bytes</v>
       </c>
       <c r="B666" t="str">
-        <v>Nessun output di convalida</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Profile is valid</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B667" t="str">
-        <v>Il profilo è valido</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B668" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Profile is non-compliant</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B669" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Critical validation error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B670" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Unknown validation status</v>
+        <v>No validation output</v>
       </c>
       <c r="B671" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B672" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B673" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Valid</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B674" t="str">
-        <v>Valido</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Warning</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B675" t="str">
-        <v>Avviso</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Error</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B676" t="str">
-        <v>Errore</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Unknown</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B677" t="str">
-        <v>Sconosciuto</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Pass</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B678" t="str">
-        <v>Superato</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Fail</v>
+        <v>Valid</v>
       </c>
       <c r="B679" t="str">
-        <v>Non superato</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>View in context</v>
+        <v>Warning</v>
       </c>
       <c r="B680" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Validation detail</v>
+        <v>Error</v>
       </c>
       <c r="B681" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Triggered by</v>
+        <v>Unknown</v>
       </c>
       <c r="B682" t="str">
-        <v>Attivato da</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Field</v>
+        <v>Pass</v>
       </c>
       <c r="B683" t="str">
-        <v>Campo</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Current value</v>
+        <v>Fail</v>
       </c>
       <c r="B684" t="str">
-        <v>Valore attuale</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>Required: 0</v>
+        <v>View in context</v>
       </c>
       <c r="B685" t="str">
-        <v>Richiesto: 0</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>Expected: {value}</v>
+        <v>Validation detail</v>
       </c>
       <c r="B686" t="str">
-        <v>Atteso: {value}</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Invalid</v>
+        <v>Triggered by</v>
       </c>
       <c r="B687" t="str">
-        <v>Non valido</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Field</v>
       </c>
       <c r="B688" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Close</v>
+        <v>Current value</v>
       </c>
       <c r="B689" t="str">
-        <v>Chiudi</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Loading XML editor…</v>
+        <v>Required: 0</v>
       </c>
       <c r="B690" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B691" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Invalid</v>
       </c>
       <c r="B692" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B693" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Close</v>
       </c>
       <c r="B694" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B695" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>Caricamento editor XML…</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B696" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Caricamento editor JSON…</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B697" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>indent</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B698" t="str">
-        <v>rientro</v>
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>sort keys</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B699" t="str">
-        <v>ordina chiavi</v>
+        <v>● modifiche XML non salvate</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B700" t="str">
+        <v>● modifiche JSON non salvate</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B701" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B702" t="str">
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B703" t="str">
+        <v>rientro</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B704" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B700" t="str">
+      <c r="B705" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B700"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B705"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -3827,10 +3827,10 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC on Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (anche JPEG con gain map), PNG — e HEIC su Safari.</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (anche JPEG con gain map), PNG — e HEIC e JPEG XL su Safari.</v>
       </c>
     </row>
     <row r="429">

--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -1221,10 +1221,10 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B103" t="str">
-        <v>Crea un DeviceLink ICC da una LUT 3D .cube di Adobe/Resolve. Il risultato viene aggiunto al tuo pool e scaricato.</v>
+        <v>Crea un DeviceLink ICC da una LUT 3D .cube di Adobe/Resolve. Il risultato viene aggiunto al tuo pool e aperto; nulla viene scaricato finché non fai clic su Salva profilo ICC.</v>
       </c>
     </row>
     <row r="104">

--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B705"/>
+  <dimension ref="A1:B706"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1197,4861 +1197,4869 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sort by name</v>
+        <v>Tap to select, then tap a tab to send.</v>
       </c>
       <c r="B100" t="str">
-        <v>Ordina per nome</v>
+        <v>Tocca per selezionare, poi tocca una scheda per inviare.</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B101" t="str">
-        <v>A–Z</v>
+        <v>Ordina per nome</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B102" t="str">
-        <v>Nuovo profilo da .cube</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B103" t="str">
-        <v>Crea un DeviceLink ICC da una LUT 3D .cube di Adobe/Resolve. Il risultato viene aggiunto al tuo pool e aperto; nulla viene scaricato finché non fai clic su Salva profilo ICC.</v>
+        <v>Nuovo profilo da .cube</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B104" t="str">
-        <v>Scegli file .cube</v>
+        <v>Crea un DeviceLink ICC da una LUT 3D .cube di Adobe/Resolve. Il risultato viene aggiunto al tuo pool e aperto; nulla viene scaricato finché non fai clic su Salva profilo ICC.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Scegli file .cube</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B105" t="str">
+      <c r="B106" t="str">
         <v>oppure trascinalo qui o incolla sotto</v>
       </c>
     </row>
-    <row r="106" xml:space="preserve">
-      <c r="A106" t="str" xml:space="preserve">
+    <row r="107" xml:space="preserve">
+      <c r="A107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B106" t="str" xml:space="preserve">
+      <c r="B107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B107" t="str">
-        <v>Annulla</v>
-      </c>
-    </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B108" t="str">
-        <v>Crea DeviceLink</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B109" t="str">
-        <v>Creazione…</v>
+        <v>Crea DeviceLink</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B110" t="str">
-        <v>Impossibile leggere questo file.</v>
+        <v>Creazione…</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B111" t="str">
-        <v>Profilo</v>
+        <v>Impossibile leggere questo file.</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B112" t="str">
-        <v>Confronta</v>
+        <v>Profilo</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B113" t="str">
-        <v>Collega</v>
+        <v>Confronta</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B114" t="str">
-        <v>Spettrale</v>
+        <v>Collega</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B115" t="str">
-        <v>Trascina i profili dal pool su questa scheda</v>
+        <v>Spettrale</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B116" t="str">
-        <v>Rimuovi</v>
+        <v>Trascina i profili dal pool su questa scheda</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B117" t="str">
-        <v>Nessun profilo selezionato</v>
+        <v>Rimuovi</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B118" t="str">
-        <v>Trascina un profilo dal pool sulla scheda Profilo per ispezionarlo.</v>
+        <v>Nessun profilo selezionato</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B119" t="str">
-        <v>Ancora niente da confrontare</v>
+        <v>Trascina un profilo dal pool sulla scheda Profilo per ispezionarlo.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B120" t="str">
-        <v>Trascina uno o più profili sulla scheda Confronta.</v>
+        <v>Ancora niente da confrontare</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B121" t="str">
-        <v>Confronto di gamut</v>
+        <v>Trascina uno o più profili sulla scheda Confronta.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B122" t="str">
-        <v>Le viste gamut 3D e sezione 2D arriveranno qui. Accumulati:</v>
+        <v>Confronto di gamut</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B123" t="str">
-        <v>Intento di rendering</v>
+        <v>Le viste gamut 3D e sezione 2D arriveranno qui. Accumulati:</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B124" t="str">
-        <v>Guscio</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B125" t="str">
-        <v>Wireframe</v>
+        <v>Guscio</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B126" t="str">
-        <v>Numeri degli assi</v>
+        <v>Wireframe</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B127" t="str">
-        <v>Opacità</v>
+        <v>Numeri degli assi</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B128" t="str">
-        <v>Colore</v>
+        <v>Opacità</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B129" t="str">
-        <v>Pieno</v>
+        <v>Colore</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B130" t="str">
-        <v>Per valore</v>
+        <v>Pieno</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B131" t="str">
-        <v>Per tonalità</v>
+        <v>Per valore</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B132" t="str">
-        <v>Rotazione</v>
+        <v>Per tonalità</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B133" t="str">
-        <v>Piattaforma girevole</v>
+        <v>Rotazione</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B134" t="str">
-        <v>Orbita</v>
+        <v>Piattaforma girevole</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B135" t="str">
-        <v>Velocità di trascinamento</v>
+        <v>Orbita</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B136" t="str">
-        <v>Rollio</v>
+        <v>Velocità di trascinamento</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B137" t="str">
-        <v>Velocità di rollio</v>
+        <v>Rollio</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B138" t="str">
-        <v>Creazione del gamut…</v>
+        <v>Velocità di rollio</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B139" t="str">
-        <v>nessun gamut</v>
+        <v>Creazione del gamut…</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B140" t="str">
-        <v>Mostra / nascondi</v>
+        <v>nessun gamut</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B141" t="str">
-        <v>Guscio del gamut 3D</v>
+        <v>Mostra / nascondi</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B142" t="str">
-        <v>Sezione del gamut 2D</v>
+        <v>Guscio del gamut 3D</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B143" t="str">
-        <v>Piano</v>
+        <v>Sezione del gamut 2D</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B144" t="str">
-        <v>L*</v>
+        <v>Piano</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B147" t="str">
-        <v>Nessuno dei profili selezionati ha una trasformazione dispositivo→PCS da cui derivare un gamut.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B148" t="str">
-        <v>Collegamento</v>
+        <v>Nessuno dei profili selezionati ha una trasformazione dispositivo→PCS da cui derivare un gamut.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B149" t="str">
-        <v>La produzione di DeviceLink e le trasformazioni multi-profilo arriveranno in una fase successiva.</v>
+        <v>Collegamento</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B150" t="str">
-        <v>Altri strumenti di collegamento (DeviceLink, …) arriveranno qui.</v>
+        <v>La produzione di DeviceLink e le trasformazioni multi-profilo arriveranno in una fase successiva.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B151" t="str">
-        <v>Generatore di display V4</v>
+        <v>Altri strumenti di collegamento (DeviceLink, …) arriveranno qui.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B152" t="str">
-        <v>Trascina qui un profilo display RGB V5 e un profilo osservatore V5 per creare un profilo display V4.</v>
+        <v>Generatore di display V4</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B153" t="str">
-        <v>Display RGB V5</v>
+        <v>Trascina qui un profilo display RGB V5 e un profilo osservatore V5 per creare un profilo display V4.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B154" t="str">
-        <v>rilascia un profilo display</v>
+        <v>Display RGB V5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B155" t="str">
-        <v>Osservatore V5 (PCC)</v>
+        <v>rilascia un profilo display</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B156" t="str">
-        <v>rilascia un profilo osservatore</v>
+        <v>Osservatore V5 (PCC)</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B157" t="str">
-        <v>Ignorato un profilo che non è né un display RGB V5 né un osservatore.</v>
+        <v>rilascia un profilo osservatore</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B158" t="str">
-        <v>Crea profilo display V4</v>
+        <v>Ignorato un profilo che non è né un display RGB V5 né un osservatore.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B159" t="str">
-        <v>Nome del profilo</v>
+        <v>Crea profilo display V4</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B160" t="str">
-        <v>Crea</v>
+        <v>Nome del profilo</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B161" t="str">
-        <v>Creazione…</v>
+        <v>Crea</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B162" t="str">
-        <v>«{name}» creato — aggiunto al pool e a questa scheda.</v>
+        <v>Creazione…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B163" t="str">
-        <v>Pipeline di collegamento</v>
+        <v>«{name}» creato — aggiunto al pool e a questa scheda.</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B164" t="str">
-        <v>Crea una catena di profili, quindi genera un DeviceLink, trasforma un'immagine o trasforma un set di dati colore attraverso di essa.</v>
+        <v>Pipeline di collegamento</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B165" t="str">
-        <v>Fatto</v>
+        <v>Crea una catena di profili, quindi genera un DeviceLink, trasforma un'immagine o trasforma un set di dati colore attraverso di essa.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B166" t="str">
-        <v>Trascina un'immagine da trasformare (TIFF/PNG/JPEG)</v>
+        <v>Fatto</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B167" t="str">
-        <v>Controllo immagine…</v>
+        <v>Trascina un'immagine da trasformare (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B168" t="str">
-        <v>Immagine non supportata (TIFF, PNG o JPEG).</v>
+        <v>Controllo immagine…</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B169" t="str">
-        <v>Immagine troppo grande ({mp} MP; limite {max} MP).</v>
+        <v>Immagine non supportata (TIFF, PNG o JPEG).</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B170" t="str">
-        <v>Trasforma immagine</v>
+        <v>Immagine troppo grande ({mp} MP; limite {max} MP).</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B171" t="str">
-        <v>Trasformazione…</v>
+        <v>Trasforma immagine</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B172" t="str">
-        <v>Trascina i profili per avviare la catena</v>
+        <v>Trasformazione…</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B173" t="str">
-        <v>rimosso</v>
+        <v>Trascina i profili per avviare la catena</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B174" t="str">
-        <v>Sposta prima</v>
+        <v>rimosso</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B175" t="str">
-        <v>Sposta dopo</v>
+        <v>Sposta prima</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B176" t="str">
-        <v>Sposta su</v>
+        <v>Sposta dopo</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B177" t="str">
-        <v>Sposta giù</v>
+        <v>Sposta su</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B178" t="str">
-        <v>Intento di rendering (tutti)</v>
+        <v>Sposta giù</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B179" t="str">
-        <v>Intento di rendering per questa trasformazione</v>
+        <v>Intento di rendering (tutti)</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B180" t="str">
-        <v>Le trasformazioni usano intenti di rendering diversi</v>
+        <v>Intento di rendering per questa trasformazione</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B181" t="str">
-        <v>Inverti la direzione della catena (inverte la trasformazione iniziale, propagandosi lungo la catena)</v>
+        <v>Le trasformazioni usano intenti di rendering diversi</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B182" t="str">
-        <v>Un profilo della catena è stato rimosso dal pool — rimuovilo per continuare.</v>
+        <v>Inverti la direzione della catena (inverte la trasformazione iniziale, propagandosi lungo la catena)</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B183" t="str">
-        <v>Catena</v>
+        <v>Un profilo della catena è stato rimosso dal pool — rimuovilo per continuare.</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B184" t="str">
-        <v>Non è stato possibile analizzare la catena.</v>
+        <v>Catena</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B185" t="str">
-        <v>Controllo della catena…</v>
+        <v>Non è stato possibile analizzare la catena.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B186" t="str">
-        <v>La catena non si collega ({detail}).</v>
+        <v>Controllo della catena…</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>Il profilo {n} non si collega alla fase precedente ({detail}).</v>
+        <v>La catena non si collega ({detail}).</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B188" t="str">
-        <v>Correggi la catena prima di elaborare le immagini</v>
+        <v>Il profilo {n} non si collega alla fase precedente ({detail}).</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B189" t="str">
-        <v>Svuota</v>
+        <v>Correggi la catena prima di elaborare le immagini</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B190" t="str">
-        <v>Crea DeviceLink</v>
+        <v>Svuota</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B191" t="str">
-        <v>Nome del DeviceLink</v>
+        <v>Crea DeviceLink</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B192" t="str">
-        <v>Creazione…</v>
+        <v>Nome del DeviceLink</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B193" t="str">
-        <v>Creato «{name}» — aggiunto al pool e a questa scheda.</v>
+        <v>Creazione…</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B194" t="str">
-        <v>Trascina immagini {src} da convertire in {dst} — i risultati si scaricano, nulla viene memorizzato.</v>
+        <v>Creato «{name}» — aggiunto al pool e a questa scheda.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B195" t="str">
-        <v>Crea una catena per elaborare le immagini</v>
+        <v>Trascina immagini {src} da convertire in {dst} — i risultati si scaricano, nulla viene memorizzato.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B196" t="str">
-        <v>Questa catena non inizia e non termina in uno spazio colore per immagini</v>
+        <v>Crea una catena per elaborare le immagini</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B197" t="str">
-        <v>Immagine trasformata salvata.</v>
+        <v>Questa catena non inizia e non termina in uno spazio colore per immagini</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B198" t="str">
-        <v>Trascina un set di dati colore (CGATS/CSV/CxF/JSON)</v>
+        <v>Immagine trasformata salvata.</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B199" t="str">
-        <v>Impossibile leggere il file.</v>
+        <v>Trascina un set di dati colore (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B200" t="str">
-        <v>File di dati troppo grande.</v>
+        <v>Impossibile leggere il file.</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B201" t="str">
-        <v>Trasforma dati</v>
+        <v>File di dati troppo grande.</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B202" t="str">
-        <v>Trasformazione…</v>
+        <v>Trasforma dati</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B203" t="str">
-        <v>Preferisci</v>
+        <v>Trasformazione…</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B204" t="str">
-        <v>Osservatore</v>
+        <v>Preferisci</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B205" t="str">
-        <v>Illuminante</v>
+        <v>Osservatore</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B206" t="str">
-        <v>Condizione</v>
+        <v>Illuminante</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B207" t="str">
-        <v>Filtra {n} duplicato/i</v>
+        <v>Condizione</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B208" t="str">
-        <v>mediana</v>
+        <v>Filtra {n} duplicato/i</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B209" t="str">
-        <v>media</v>
+        <v>mediana</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B210" t="str">
-        <v>patch</v>
+        <v>media</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B211" t="str">
-        <v>{n} duplicati</v>
+        <v>patch</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B212" t="str">
-        <v>Risultato della trasformazione</v>
+        <v>{n} duplicati</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B213" t="str">
-        <v>{src} → {dst} · {n} patch</v>
+        <v>Risultato della trasformazione</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B214" t="str">
-        <v>Visualizzati i primi {shown} di {total} — Salva li scrive tutti.</v>
+        <v>{src} → {dst} · {n} patch</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B215" t="str">
-        <v>Salva con nome</v>
+        <v>Visualizzati i primi {shown} di {total} — Salva li scrive tutti.</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B216" t="str">
-        <v>Salva</v>
+        <v>Salva con nome</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B217" t="str">
-        <v>Inverti trasformazione</v>
+        <v>Salva</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B218" t="str">
-        <v>Inversione…</v>
+        <v>Inverti trasformazione</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B219" t="str">
-        <v>Inverti</v>
+        <v>Inversione…</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B220" t="str">
-        <v>ultima fase</v>
+        <v>Inverti</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B221" t="str">
-        <v>prima fase</v>
+        <v>ultima fase</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B222" t="str">
-        <v>Dati in {in} → ricerca {out}</v>
+        <v>prima fase</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B223" t="str">
-        <v>L'inversione richiede una catena di 2–3 profili</v>
+        <v>Dati in {in} → ricerca {out}</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B224" t="str">
-        <v>Il set di dati deve essere in {in}; la ricerca inversa produce {out} più un costo di invertibilità per patch.</v>
+        <v>L'inversione richiede una catena di 2–3 profili</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B225" t="str">
-        <v>Costo ΔE</v>
+        <v>Il set di dati deve essere in {in}; la ricerca inversa produce {out} più un costo di invertibilità per patch.</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B226" t="str">
-        <v>Questa immagine contiene un profilo ICC incorporato.</v>
+        <v>Costo ΔE</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B227" t="str">
-        <v>Estrai e aggiungi alla catena</v>
+        <v>Questa immagine contiene un profilo ICC incorporato.</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B228" t="str">
-        <v>Estrazione…</v>
+        <v>Estrai e aggiungi alla catena</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B229" t="str">
-        <v>Ignora</v>
+        <v>Estrazione…</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B230" t="str">
-        <v>Profilo incorporato estratto — aggiunto al pool e posizionato all'inizio della catena.</v>
+        <v>Ignora</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B231" t="str">
-        <v>Opzioni di output dell'immagine</v>
+        <v>Profilo incorporato estratto — aggiunto al pool e posizionato all'inizio della catena.</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B232" t="str">
-        <v>Codifica</v>
+        <v>Opzioni di output dell'immagine</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B233" t="str">
-        <v>Come l'origine</v>
+        <v>Codifica</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B234" t="str">
-        <v>8 bit</v>
+        <v>Come l'origine</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>16 bit</v>
+        <v>8 bit</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B236" t="str">
-        <v>Virgola mobile (32 bit)</v>
+        <v>16 bit</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B237" t="str">
-        <v>Compressione</v>
+        <v>Virgola mobile (32 bit)</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B238" t="str">
-        <v>Nessuna</v>
+        <v>Compressione</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B239" t="str">
-        <v>Planare</v>
+        <v>Nessuna</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B240" t="str">
-        <v>Interlacciato</v>
+        <v>Planare</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B241" t="str">
-        <v>Separato</v>
+        <v>Interlacciato</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B242" t="str">
-        <v>Interpolazione CMM</v>
+        <v>Separato</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B243" t="str">
-        <v>Tetraedrica</v>
+        <v>Interpolazione CMM</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B244" t="str">
-        <v>Lineare</v>
+        <v>Tetraedrica</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B245" t="str">
-        <v>Incorpora profilo ICC</v>
+        <v>Lineare</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B246" t="str">
-        <v>Codifica, compressione e disposizione planare determinano il TIFF salvato. L'output RGB/Gray resta PNG a meno che non sia impostata un'opzione esclusiva del TIFF (virgola mobile, LZW/ZIP, separato).</v>
+        <v>Incorpora profilo ICC</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B247" t="str">
-        <v>Assembla TIFF spettrale</v>
+        <v>Codifica, compressione e disposizione planare determinano il TIFF salvato. L'output RGB/Gray resta PNG a meno che non sia impostata un'opzione esclusiva del TIFF (virgola mobile, LZW/ZIP, separato).</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B248" t="str">
-        <v>Trascina immagini spettrali monocanale nell'ordine dei canali, quindi assemblale in un unico TIFF multicanale.</v>
+        <v>Assembla TIFF spettrale</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B249" t="str">
-        <v>Trascina qui le immagini spettrali (o clicca per selezionarle)</v>
+        <v>Trascina immagini spettrali monocanale nell'ordine dei canali, quindi assemblale in un unico TIFF multicanale.</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B250" t="str">
-        <v>can</v>
+        <v>Trascina qui le immagini spettrali (o clicca per selezionarle)</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B251" t="str">
-        <v>Assembla e salva</v>
+        <v>can</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B252" t="str">
-        <v>Assemblaggio…</v>
+        <v>Assembla e salva</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B253" t="str">
-        <v>Assemblati {n} canali.</v>
+        <v>Assemblaggio…</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B254" t="str">
-        <v>Nessuno di questi sembra un'immagine (TIFF, PNG o JPEG).</v>
+        <v>Assemblati {n} canali.</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B255" t="str">
-        <v>Annulla</v>
+        <v>Nessuno di questi sembra un'immagine (TIFF, PNG o JPEG).</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B256" t="str">
-        <v>{n} file non caricati</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B257" t="str">
-        <v>Questi file non sono profili ICC, quindi non sono stati aggiunti al pool:</v>
+        <v>{n} file non caricati</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B258" t="str">
-        <v>OK</v>
+        <v>Questi file non sono profili ICC, quindi non sono stati aggiunti al pool:</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B259" t="str">
-        <v>Trascina qui un profilo ICC</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B260" t="str">
-        <v>oppure</v>
+        <v>Trascina qui un profilo ICC</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B261" t="str">
-        <v>Scegli file</v>
+        <v>oppure</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B262" t="str">
-        <v>File .icc e .icm</v>
+        <v>Scegli file</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B263" t="str">
-        <v>Intestazione</v>
+        <v>File .icc e .icm</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B264" t="str">
-        <v>Tag</v>
+        <v>Intestazione</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B265" t="str">
-        <v>Convalida</v>
+        <v>Tag</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B266" t="str">
-        <v>Analisi</v>
+        <v>Convalida</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B267" t="str">
-        <v>Inchiostrazione dell’asse neutro</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B268" t="str">
-        <v>Colorante depositato lungo l’asse neutro (a*=b*=0) mentre la luminosità passa dal bianco (L*=100) al nero (L*=0).</v>
+        <v>Inchiostrazione dell’asse neutro</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B269" t="str">
-        <v>L’inchiostrazione dell’asse neutro è disponibile solo per i profili di output (stampante).</v>
+        <v>Colorante depositato lungo l’asse neutro (a*=b*=0) mentre la luminosità passa dal bianco (L*=100) al nero (L*=0).</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B270" t="str">
-        <v>Questo profilo non ha una tabella B2A (PCS→dispositivo) da campionare.</v>
+        <v>L’inchiostrazione dell’asse neutro è disponibile solo per i profili di output (stampante).</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B271" t="str">
-        <v>Intento di rendering</v>
+        <v>Questo profilo non ha una tabella B2A (PCS→dispositivo) da campionare.</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B272" t="str">
-        <v>% inchiostro</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>L* out (tone)</v>
+        <v>% ink</v>
       </c>
       <c r="B273" t="str">
-        <v>L* in uscita (tono)</v>
+        <v>% inchiostro</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Δa*b*</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B274" t="str">
-        <v>Δa*b*</v>
+        <v>L* in uscita (tono)</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B275" t="str">
-        <v>Colorimetria degli estremi</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B276" t="str">
-        <v>Gli estremi dell’intervallo di riproduzione del profilo: il bianco del supporto, il nero più scuro che stamperà, l’inchiostro che quel nero costa e il punto in cui ogni tinta raggiunge la massima saturazione.</v>
+        <v>Colorimetria degli estremi</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B277" t="str">
-        <v>Il punto di bianco è il colore con colorante nullo — il supporto nudo. Il punto di nero si ottiene facendo passare il nero PCS (L*=0, a*=b*=0) attraverso la tabella B2A selezionata per ricavare l’inchiostrazione che il profilo sceglie per il nero, e rileggendo poi tale inchiostrazione tramite A2B1. La copertura totale d’inchiostro (TAC) è la somma di tale inchiostrazione. La colorimetria assoluta mostra il colore proprio del supporto; quella relativa lo riferisce a un bianco perfetto.</v>
+        <v>Gli estremi dell’intervallo di riproduzione del profilo: il bianco del supporto, il nero più scuro che stamperà, l’inchiostro che quel nero costa e il punto in cui ogni tinta raggiunge la massima saturazione.</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Relative</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B278" t="str">
-        <v>Relativa</v>
+        <v>Il punto di bianco è il colore con colorante nullo — il supporto nudo. Il punto di nero si ottiene facendo passare il nero PCS (L*=0, a*=b*=0) attraverso la tabella B2A selezionata per ricavare l’inchiostrazione che il profilo sceglie per il nero, e rileggendo poi tale inchiostrazione tramite A2B1. La copertura totale d’inchiostro (TAC) è la somma di tale inchiostrazione. La colorimetria assoluta mostra il colore proprio del supporto; quella relativa lo riferisce a un bianco perfetto.</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Absolute</v>
+        <v>Relative</v>
       </c>
       <c r="B279" t="str">
-        <v>Assoluta</v>
+        <v>Relativa</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>White point</v>
+        <v>Absolute</v>
       </c>
       <c r="B280" t="str">
-        <v>Punto di bianco</v>
+        <v>Assoluta</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Black point</v>
+        <v>White point</v>
       </c>
       <c r="B281" t="str">
-        <v>Punto di nero</v>
+        <v>Punto di bianco</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Inking at black point</v>
+        <v>Black point</v>
       </c>
       <c r="B282" t="str">
-        <v>Inchiostrazione al punto di nero</v>
+        <v>Punto di nero</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>TAC</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B283" t="str">
-        <v>TAC</v>
+        <v>Inchiostrazione al punto di nero</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>TAC</v>
       </c>
       <c r="B284" t="str">
-        <v>Questo profilo non ha il tag del punto di bianco del supporto, quindi la colorimetria assoluta non è disponibile.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B285" t="str">
-        <v>La colorimetria degli estremi è disponibile solo per i profili di output (stampante) — presuppone che colorante nullo significhi supporto nudo.</v>
+        <v>Questo profilo non ha il tag del punto di bianco del supporto, quindi la colorimetria assoluta non è disponibile.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B286" t="str">
-        <v>Pieno e croma massima</v>
+        <v>La colorimetria degli estremi è disponibile solo per i profili di output (stampante) — presuppone che colorante nullo significhi supporto nudo.</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B287" t="str">
-        <v>Dove si colloca ogni vertice d’inchiostro e il punto più cromatico lungo il percorso. Misurato tramite A2B1, quindi queste righe non cambiano con l’intento di rendering sopra. In un profilo ben formato le due righe coincidono; se la croma massima arriva prima del pieno, l’inchiostro oltre quel punto si limita a scurire.</v>
+        <v>Pieno e croma massima</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Hue</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B288" t="str">
-        <v>Tinta</v>
+        <v>Dove si colloca ogni vertice d’inchiostro e il punto più cromatico lungo il percorso. Misurato tramite A2B1, quindi queste righe non cambiano con l’intento di rendering sopra. In un profilo ben formato le due righe coincidono; se la croma massima arriva prima del pieno, l’inchiostro oltre quel punto si limita a scurire.</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Full tone</v>
+        <v>Hue</v>
       </c>
       <c r="B289" t="str">
-        <v>Pieno</v>
+        <v>Tinta</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Max C*</v>
+        <v>Full tone</v>
       </c>
       <c r="B290" t="str">
-        <v>C* max</v>
+        <v>Pieno</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>At ink</v>
+        <v>Max C*</v>
       </c>
       <c r="B291" t="str">
-        <v>All’inchiostrazione</v>
+        <v>C* max</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>At ink</v>
       </c>
       <c r="B292" t="str">
-        <v>La croma massima viene raggiunta prima del pieno — oltre questo punto l’inchiostro si limita a scurire.</v>
+        <v>All’inchiostrazione</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B293" t="str">
-        <v>Uso dell’inchiostro nelle ombre</v>
+        <v>La croma massima viene raggiunta prima del pieno — oltre questo punto l’inchiostro si limita a scurire.</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B294" t="str">
-        <v>Quattro percorsi rettilinei sul piano a*b* a una luminosità costante e deliberatamente scura, passati attraverso la tabella B2A selezionata. Tutti i campioni condividono la stessa L*, perciò ogni scalino brusco o inversione di un colorante deriva unicamente dalla gestione di tinta e croma — la firma di un artefatto di mappatura del gamut nelle ombre.</v>
+        <v>Uso dell’inchiostro nelle ombre</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B295" t="str">
-        <v>L’uso dell’inchiostro nelle ombre è disponibile solo per i profili di output (stampante).</v>
+        <v>Quattro percorsi rettilinei sul piano a*b* a una luminosità costante e deliberatamente scura, passati attraverso la tabella B2A selezionata. Tutti i campioni condividono la stessa L*, perciò ogni scalino brusco o inversione di un colorante deriva unicamente dalla gestione di tinta e croma — la firma di un artefatto di mappatura del gamut nelle ombre.</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Constant L* plane</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B296" t="str">
-        <v>Piano a L* costante</v>
+        <v>L’uso dell’inchiostro nelle ombre è disponibile solo per i profili di output (stampante).</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>black-point compensated from</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B297" t="str">
-        <v>con compensazione del punto di nero da</v>
+        <v>Piano a L* costante</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Position along path</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B298" t="str">
-        <v>Posizione lungo il percorso</v>
+        <v>con compensazione del punto di nero da</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Path</v>
+        <v>Position along path</v>
       </c>
       <c r="B299" t="str">
-        <v>Percorso</v>
+        <v>Posizione lungo il percorso</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Primary-Inking Paths through Neutral</v>
+        <v>Path</v>
       </c>
       <c r="B300" t="str">
-        <v>Percorsi d’inchiostrazione primaria attraverso il neutro</v>
+        <v>Percorso</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B301" t="str">
-        <v>Tre percorsi nel gamut — ciano→rosso, magenta→verde, giallo→blu — ciascuno attraverso l’asse neutro alla chiarezza mediana dei suoi estremi, attraverso la tabella B2A selezionata. Ogni campione è nel gamut, quindi a differenza dei percorsi in ombra qualsiasi salto o inversione di un colorante è un difetto di regolarità della CLUT e non un artefatto di mappatura del gamut.</v>
+        <v>Percorsi d’inchiostrazione primaria attraverso il neutro</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Primary-inking paths are only available for output (printer) profiles.</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B302" t="str">
-        <v>I percorsi d’inchiostrazione primaria sono disponibili solo per i profili di output (stampante).</v>
+        <v>Tre percorsi nel gamut — ciano→rosso, magenta→verde, giallo→blu — ciascuno attraverso l’asse neutro alla chiarezza mediana dei suoi estremi, attraverso la tabella B2A selezionata. Ogni campione è nel gamut, quindi a differenza dei percorsi in ombra qualsiasi salto o inversione di un colorante è un difetto di regolarità della CLUT e non un artefatto di mappatura del gamut.</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Position along path (neutral at midpoint)</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B303" t="str">
-        <v>Posizione lungo il percorso (neutro al centro)</v>
+        <v>I percorsi d’inchiostrazione primaria sono disponibili solo per i profili di output (stampante).</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Black-point compensated for this intent.</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B304" t="str">
-        <v>Compensazione del punto nero applicata per questo intento.</v>
+        <v>Posizione lungo il percorso (neutro al centro)</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Ink Usage Statistics</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B305" t="str">
-        <v>Statistiche di utilizzo dell’inchiostro</v>
+        <v>Compensazione del punto nero applicata per questo intento.</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B306" t="str">
-        <v>Quanto di ogni colorante il profilo deposita, come somma e come quota del totale — la firma di consumo d’inchiostro della separazione.</v>
+        <v>Statistiche di utilizzo dell’inchiostro</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Ink usage statistics are only available for output (printer) profiles.</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B307" t="str">
-        <v>Le statistiche di utilizzo dell’inchiostro sono disponibili solo per i profili di output (stampante).</v>
+        <v>Quanto di ogni colorante il profilo deposita, come somma e come quota del totale — la firma di consumo d’inchiostro della separazione.</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Neutral axis</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B308" t="str">
-        <v>Asse neutro</v>
+        <v>Le statistiche di utilizzo dell’inchiostro sono disponibili solo per i profili di output (stampante).</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Mean coverage</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B309" t="str">
-        <v>Copertura media</v>
+        <v>Asse neutro</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Share of ink</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B310" t="str">
-        <v>Quota d’inchiostro</v>
+        <v>Copertura media</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
+        <v>Share of ink</v>
       </c>
       <c r="B311" t="str">
-        <v>La quota d’inchiostro è l’impronta della costruzione del neutro — la frazione di ogni colorante sul totale d’inchiostro depositato, indipendentemente dal numero di campioni.</v>
+        <v>Quota d’inchiostro</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>On &amp; in-gamut points</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B312" t="str">
-        <v>Punti nel gamut</v>
+        <v>La quota d’inchiostro è l’impronta della costruzione del neutro — la frazione di ogni colorante sul totale d’inchiostro depositato, indipendentemente dal numero di campioni.</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B313" t="str">
-        <v>L’utilizzo d’inchiostro su tutti i colori nel gamut richiede il confine del gamut lato B2A, non ancora implementato — in arrivo.</v>
+        <v>Punti nel gamut</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>No colorant data to summarize.</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B314" t="str">
-        <v>Nessun dato di colorante da riepilogare.</v>
+        <v>L’utilizzo d’inchiostro su tutti i colori nel gamut richiede il confine del gamut lato B2A, non ancora implementato — in arrivo.</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B315" t="str">
-        <v>Seleziona una tabella B2A (PCS→dispositivo) qui sotto per visualizzare anche un’immagine in scala di grigi della copertura d’inchiostro per ogni colorante.</v>
+        <v>Nessun dato di colorante da riepilogare.</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B316" t="str">
-        <v>Copertura d’inchiostro di ogni colorante sullo stesso reticolo (più scuro = più inchiostro).</v>
+        <v>Seleziona una tabella B2A (PCS→dispositivo) qui sotto per visualizzare anche un’immagine in scala di grigi della copertura d’inchiostro per ogni colorante.</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Cyan</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B317" t="str">
-        <v>Ciano</v>
+        <v>Copertura d’inchiostro di ogni colorante sullo stesso reticolo (più scuro = più inchiostro).</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Magenta</v>
+        <v>Cyan</v>
       </c>
       <c r="B318" t="str">
-        <v>Magenta</v>
+        <v>Ciano</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Yellow</v>
+        <v>Magenta</v>
       </c>
       <c r="B319" t="str">
-        <v>Giallo</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Red</v>
+        <v>Yellow</v>
       </c>
       <c r="B320" t="str">
-        <v>Rosso</v>
+        <v>Giallo</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="B321" t="str">
-        <v>Verde</v>
+        <v>Rosso</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Blue</v>
+        <v>Green</v>
       </c>
       <c r="B322" t="str">
-        <v>Blu</v>
+        <v>Verde</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Black</v>
+        <v>Blue</v>
       </c>
       <c r="B323" t="str">
-        <v>Nero</v>
+        <v>Blu</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Perceptual</v>
+        <v>Black</v>
       </c>
       <c r="B324" t="str">
-        <v>Percettivo</v>
+        <v>Nero</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B325" t="str">
-        <v>Colorimetrico relativo</v>
+        <v>Percettivo</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B326" t="str">
-        <v>Saturazione</v>
+        <v>Colorimetrico relativo</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B327" t="str">
-        <v>Colorimetrico assoluto</v>
+        <v>Saturazione</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B328" t="str">
-        <v>Statistiche del profilo</v>
+        <v>Colorimetrico assoluto</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B329" t="str">
-        <v>Metriche dell’intero profilo per intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e l’accuratezza del round-trip B2A — ΔE*ab di un percorso Lab → dispositivo → Lab attraverso il profilo.</v>
+        <v>Statistiche del profilo</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B330" t="str">
-        <v>Nessuna CLUT dispositivo↔PCS in questo profilo — le statistiche del profilo non si applicano (ad es. un profilo monitor matrice/TRC).</v>
+        <v>Metriche dell’intero profilo per intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e l’accuratezza del round-trip B2A — ΔE*ab di un percorso Lab → dispositivo → Lab attraverso il profilo.</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B331" t="str">
-        <v>Intento di rendering</v>
+        <v>Nessuna CLUT dispositivo↔PCS in questo profilo — le statistiche del profilo non si applicano (ad es. un profilo monitor matrice/TRC).</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B332" t="str">
-        <v>Volume del gamut (ΔE³)</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B333" t="str">
-        <v>ΔE round-trip</v>
+        <v>Volume del gamut (ΔE³)</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B334" t="str">
-        <v>Il confine del gamut è collassato o era in gran parte indefinito; questo volume di gamut non è affidabile.</v>
+        <v>ΔE round-trip</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B335" t="str">
-        <v>media</v>
+        <v>Il confine del gamut è collassato o era in gran parte indefinito; questo volume di gamut non è affidabile.</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B336" t="str">
-        <v>P90</v>
+        <v>media</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B337" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B338" t="str">
-        <v>Analisi in corso…</v>
+        <v>max</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B339" t="str">
-        <v>Analisi</v>
+        <v>Analisi in corso…</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B340" t="str">
-        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B341" t="str">
-        <v>Grafico</v>
+        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B342" t="str">
-        <v>Output grezzo</v>
+        <v>Grafico</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B343" t="str">
-        <v>XML</v>
+        <v>Output grezzo</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B345" t="str">
-        <v>Curve</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B346" t="str">
-        <v>Curve di ingresso</v>
+        <v>Curve</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B347" t="str">
-        <v>Curve di uscita</v>
+        <v>Curve di ingresso</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B348" t="str">
-        <v>Immagine CLUT</v>
+        <v>Curve di uscita</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B349" t="str">
-        <v>Immagine gamut</v>
+        <v>Immagine CLUT</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B350" t="str">
-        <v>Cromaticità</v>
+        <v>Immagine gamut</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B351" t="str">
-        <v>Grafico a dispersione</v>
+        <v>Cromaticità</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B352" t="str">
-        <v>Curva di risposta tonale</v>
+        <v>Grafico a dispersione</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B353" t="str">
-        <v>Tabella della curva</v>
+        <v>Curva di risposta tonale</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B354" t="str">
-        <v>Tabelle</v>
+        <v>Tabella della curva</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B355" t="str">
-        <v>Dati</v>
+        <v>Tabelle</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B356" t="str">
-        <v>Valuta</v>
+        <v>Dati</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B357" t="str">
-        <v>Caricamento…</v>
+        <v>Valuta</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B358" t="str">
-        <v>Ingresso</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B359" t="str">
-        <v>Uscita</v>
+        <v>Ingresso</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B360" t="str">
-        <v>Virgola mobile</v>
+        <v>Uscita</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B361" t="str">
-        <v>Punto griglia</v>
+        <v>Virgola mobile</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B362" t="str">
-        <v>Normalizzato</v>
+        <v>Punto griglia</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B363" t="str">
-        <v>Leggibile</v>
+        <v>Normalizzato</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B364" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Leggibile</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B365" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B366" t="str">
-        <v>Nessuna griglia CLUT</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B367" t="str">
-        <v>Caricamento…</v>
+        <v>Nessuna griglia CLUT</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B368" t="str">
-        <v>Neutro = nel gamut · rosso = fuori gamut</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B369" t="str">
-        <v>URL del profilo non valido:</v>
+        <v>Neutro = nel gamut · rosso = fuori gamut</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B370" t="str">
-        <v>Impossibile recuperare il profilo da</v>
+        <v>URL del profilo non valido:</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B371" t="str">
-        <v>Caricare un profilo ICC da questo sito esterno?</v>
+        <v>Impossibile recuperare il profilo da</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B372" t="str">
-        <v>Caricamento del rapporto Profile Assessment WG…</v>
+        <v>Caricare un profilo ICC da questo sito esterno?</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B373" t="str">
-        <v>Esecuzione dei controlli Profile Assessment WG…</v>
+        <v>Caricamento del rapporto Profile Assessment WG…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B374" t="str">
-        <v>Rapporto Profile Assessment WG</v>
+        <v>Esecuzione dei controlli Profile Assessment WG…</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B375" t="str">
-        <v>Sicurezza</v>
+        <v>Rapporto Profile Assessment WG</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B376" t="str">
-        <v>Conformità</v>
+        <v>Sicurezza</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B377" t="str">
-        <v>Qualità</v>
+        <v>Conformità</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>HDR</v>
+        <v>Quality</v>
       </c>
       <c r="B378" t="str">
-        <v>HDR</v>
+        <v>Qualità</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Code points</v>
+        <v>HDR</v>
       </c>
       <c r="B379" t="str">
-        <v>Punti di codice</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Gain curve</v>
+        <v>Code points</v>
       </c>
       <c r="B380" t="str">
-        <v>Curva di guadagno</v>
+        <v>Punti di codice</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Environment</v>
+        <v>Gain curve</v>
       </c>
       <c r="B381" t="str">
-        <v>Ambiente</v>
+        <v>Curva di guadagno</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Showing the SDR fallback</v>
+        <v>Environment</v>
       </c>
       <c r="B382" t="str">
-        <v>Visualizzazione del ripiego SDR</v>
+        <v>Ambiente</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>HDR Profile in the chain</v>
+        <v>Showing the SDR fallback</v>
       </c>
       <c r="B383" t="str">
-        <v>Profilo HDR nella catena</v>
+        <v>Visualizzazione del ripiego SDR</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
+        <v>HDR Profile in the chain</v>
       </c>
       <c r="B384" t="str">
-        <v>Le trasformazioni attraverso un profilo HDR usano il suo AToB0Tag — il rendering SDR fissato richiesto dalla clausola 8.10.6 — perché la clausola 8.10.1 non gli lascia tag TRC. Il risultato è quel ripiego, non comportamento HDR.</v>
+        <v>Profilo HDR nella catena</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
+        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B385" t="str">
-        <v>Sono profili HDR, privi di tag TRC: il gamut è quindi costruito dall’AToB0Tag, il rendering SDR fissato che la clausola 8.10.6 richiede per i consumatori senza elaborazione HDR. Non è il gamut HDR del profilo, che non può essere tracciato in un PCS limitato.</v>
+        <v>Le trasformazioni attraverso un profilo HDR usano il suo AToB0Tag — il rendering SDR fissato richiesto dalla clausola 8.10.6 — perché la clausola 8.10.1 non gli lascia tag TRC. Il risultato è quel ripiego, non comportamento HDR.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Detecting…</v>
+        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B386" t="str">
-        <v>Rilevamento…</v>
+        <v>Sono profili HDR, privi di tag TRC: il gamut è quindi costruito dall’AToB0Tag, il rendering SDR fissato che la clausola 8.10.6 richiede per i consumatori senza elaborazione HDR. Non è il gamut HDR del profilo, che non può essere tracciato in un PCS limitato.</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Could not detect environment.</v>
+        <v>Detecting…</v>
       </c>
       <c r="B387" t="str">
-        <v>Impossibile rilevare l’ambiente.</v>
+        <v>Rilevamento…</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>HDR display</v>
+        <v>Could not detect environment.</v>
       </c>
       <c r="B388" t="str">
-        <v>Display HDR</v>
+        <v>Impossibile rilevare l’ambiente.</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Wide gamut</v>
+        <v>HDR display</v>
       </c>
       <c r="B389" t="str">
-        <v>Gamut esteso</v>
+        <v>Display HDR</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>HDR canvas path</v>
+        <v>Wide gamut</v>
       </c>
       <c r="B390" t="str">
-        <v>Percorso canvas HDR</v>
+        <v>Gamut esteso</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>sRGB</v>
+        <v>HDR canvas path</v>
       </c>
       <c r="B391" t="str">
-        <v>sRGB</v>
+        <v>Percorso canvas HDR</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>none</v>
+        <v>sRGB</v>
       </c>
       <c r="B392" t="str">
-        <v>nessuno</v>
+        <v>sRGB</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>yes</v>
+        <v>none</v>
       </c>
       <c r="B393" t="str">
-        <v>sì</v>
+        <v>nessuno</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>no</v>
+        <v>yes</v>
       </c>
       <c r="B394" t="str">
-        <v>no</v>
+        <v>sì</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>not reported</v>
+        <v>no</v>
       </c>
       <c r="B395" t="str">
-        <v>non riportato</v>
+        <v>no</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Format</v>
+        <v>not reported</v>
       </c>
       <c r="B396" t="str">
-        <v>Formato</v>
+        <v>non riportato</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Inspect</v>
+        <v>Format</v>
       </c>
       <c r="B397" t="str">
-        <v>Ispeziona</v>
+        <v>Formato</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Display</v>
+        <v>Inspect</v>
       </c>
       <c r="B398" t="str">
-        <v>Visualizza</v>
+        <v>Ispeziona</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>HDR</v>
+        <v>Display</v>
       </c>
       <c r="B399" t="str">
-        <v>HDR</v>
+        <v>Visualizza</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Read the embedded ICC profile — needs no codec</v>
+        <v>HDR</v>
       </c>
       <c r="B400" t="str">
-        <v>Legge il profilo ICC incorporato — nessun codec richiesto</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Show the pixels</v>
+        <v>Read the embedded ICC profile — needs no codec</v>
       </c>
       <c r="B401" t="str">
-        <v>Mostra i pixel</v>
+        <v>Legge il profilo ICC incorporato — nessun codec richiesto</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Render brighter-than-white</v>
+        <v>Show the pixels</v>
       </c>
       <c r="B402" t="str">
-        <v>Resa più luminosa del bianco</v>
+        <v>Mostra i pixel</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Decoded by profiletool itself, so browser-independent</v>
+        <v>Render brighter-than-white</v>
       </c>
       <c r="B403" t="str">
-        <v>Decodificato da profiletool, quindi indipendente dal browser</v>
+        <v>Resa più luminosa del bianco</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
+        <v>Decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B404" t="str">
-        <v>Questo browser non ha indicato il margine HDR del display, solo se esiste un percorso HDR.</v>
+        <v>Decodificato da profiletool, quindi indipendente dal browser</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Browser flags</v>
+        <v>This browser has not reported the display’s HDR headroom, only whether an HDR path exists.</v>
       </c>
       <c r="B405" t="str">
-        <v>Flag del browser</v>
+        <v>Questo browser non ha indicato il margine HDR del display, solo se esiste un percorso HDR.</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>on</v>
+        <v>Browser flags</v>
       </c>
       <c r="B406" t="str">
-        <v>attivo</v>
+        <v>Flag del browser</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>not enabled</v>
+        <v>on</v>
       </c>
       <c r="B407" t="str">
-        <v>non attivo</v>
+        <v>attivo</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>cannot be detected here</v>
+        <v>not enabled</v>
       </c>
       <c r="B408" t="str">
-        <v>non rilevabile qui</v>
+        <v>non attivo</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
+        <v>cannot be detected here</v>
       </c>
       <c r="B409" t="str">
-        <v>Necessario per il rendering HDR in questo browser: senza WebGPU il canvas HDR è l’unica via. L’ispezione dei profili funziona anche senza.</v>
+        <v>non rilevabile qui</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
+        <v>Needed for HDR rendering in this browser: it has no WebGPU, so the HDR canvas is the only route. Profile inspection works without it.</v>
       </c>
       <c r="B410" t="str">
-        <v>Facoltativo: l’HDR può passare da WebGPU, ma questo aggiunge il percorso canvas HDR e permette a profiletool di leggere il vero margine HDR dello schermo.</v>
+        <v>Necessario per il rendering HDR in questo browser: senza WebGPU il canvas HDR è l’unica via. L’ispezione dei profili funziona anche senza.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
+        <v>Optional: HDR can render through WebGPU, but this adds the HDR canvas route and lets profiletool read the screen’s real HDR headroom.</v>
       </c>
       <c r="B411" t="str">
-        <v>Le pagine web non possono aprire le pagine dei flag. Incolla questo nella barra degli indirizzi, imposta Enabled e riavvia il browser.</v>
+        <v>Facoltativo: l’HDR può passare da WebGPU, ma questo aggiunge il percorso canvas HDR e permette a profiletool di leggere il vero margine HDR dello schermo.</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Copy</v>
+        <v>Web pages cannot open flag pages. Paste this into the address bar, set it to Enabled, then relaunch the browser.</v>
       </c>
       <c r="B412" t="str">
-        <v>Copia</v>
+        <v>Le pagine web non possono aprire le pagine dei flag. Incolla questo nella barra degli indirizzi, imposta Enabled e riavvia il browser.</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Copied</v>
+        <v>Copy</v>
       </c>
       <c r="B413" t="str">
-        <v>Copiato</v>
+        <v>Copia</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Copy failed — select the address and copy it.</v>
+        <v>Copied</v>
       </c>
       <c r="B414" t="str">
-        <v>Copia non riuscita — seleziona l’indirizzo e copialo.</v>
+        <v>Copiato</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Pixel ratio</v>
+        <v>Copy failed — select the address and copy it.</v>
       </c>
       <c r="B415" t="str">
-        <v>Rapporto pixel</v>
+        <v>Copia non riuscita — seleziona l’indirizzo e copialo.</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Current monitor</v>
+        <v>Pixel ratio</v>
       </c>
       <c r="B416" t="str">
-        <v>Monitor attuale</v>
+        <v>Rapporto pixel</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>unnamed</v>
+        <v>Current monitor</v>
       </c>
       <c r="B417" t="str">
-        <v>senza nome</v>
+        <v>Monitor attuale</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>primary</v>
+        <v>unnamed</v>
       </c>
       <c r="B418" t="str">
-        <v>principale</v>
+        <v>senza nome</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>built-in</v>
+        <v>primary</v>
       </c>
       <c r="B419" t="str">
-        <v>integrato</v>
+        <v>principale</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>HDR headroom</v>
+        <v>built-in</v>
       </c>
       <c r="B420" t="str">
-        <v>Margine HDR</v>
+        <v>integrato</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>not exposed by this browser</v>
+        <v>HDR headroom</v>
       </c>
       <c r="B421" t="str">
-        <v>non esposto da questo browser</v>
+        <v>Margine HDR</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
+        <v>not exposed by this browser</v>
       </c>
       <c r="B422" t="str">
-        <v>Chromium lo riporta in stop: log₂ della luminanza di picco del display ÷ il livello di bianco SDR. Su Windows si aggiorna solo quando Chrome rilegge il display — finestra spostata su un altro schermo o Chrome riattivato — non quando cambia la luminosità.</v>
+        <v>non esposto da questo browser</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>{stops} stops (≈{ratio}× SDR white)</v>
+        <v>Chromium reports this in stops: log₂ of the display’s peak brightness ÷ its SDR white level. On Windows it refreshes only when Chrome re-reads the display — the window moves to another screen, or Chrome becomes the active app again — not when brightness changes.</v>
       </c>
       <c r="B423" t="str">
-        <v>{stops} stop (≈{ratio}× il bianco SDR)</v>
+        <v>Chromium lo riporta in stop: log₂ della luminanza di picco del display ÷ il livello di bianco SDR. Su Windows si aggiorna solo quando Chrome rilegge il display — finestra spostata su un altro schermo o Chrome riattivato — non quando cambia la luminosità.</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>HDR</v>
+        <v>{stops} stops (≈{ratio}× SDR white)</v>
       </c>
       <c r="B424" t="str">
-        <v>HDR</v>
+        <v>{stops} stop (≈{ratio}× il bianco SDR)</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Gain at a display headroom</v>
+        <v>HDR</v>
       </c>
       <c r="B425" t="str">
-        <v>Guadagno a un margine del display</v>
+        <v>HDR</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
+        <v>Gain at a display headroom</v>
       </c>
       <c r="B426" t="str">
-        <v>Visualizza un’immagine HDR su questo display. I file che il browser sa decodificare sono mostrati dal browser stesso; OpenEXR e Radiance HDR sono decodificati e resi da profiletool.</v>
+        <v>Guadagno a un margine del display</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Drop an HDR image here, or click to choose one</v>
+        <v>View one HDR image on this display. Files the browser can decode are shown by the browser itself; OpenEXR and Radiance HDR are decoded and rendered by profiletool.</v>
       </c>
       <c r="B427" t="str">
-        <v>Trascina qui un’immagine HDR o fai clic per sceglierne una</v>
+        <v>Visualizza un’immagine HDR su questo display. I file che il browser sa decodificare sono mostrati dal browser stesso; OpenEXR e Radiance HDR sono decodificati e resi da profiletool.</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
+        <v>Drop an HDR image here, or click to choose one</v>
       </c>
       <c r="B428" t="str">
-        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (anche JPEG con gain map), PNG — e HEIC e JPEG XL su Safari.</v>
+        <v>Trascina qui un’immagine HDR o fai clic per sceglierne una</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Choose another</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (including gain-map JPEG), PNG — and HEIC and JPEG XL on Safari.</v>
       </c>
       <c r="B429" t="str">
-        <v>Scegli un’altra</v>
+        <v>OpenEXR, Radiance HDR (.hdr), AVIF, JPEG (anche JPEG con gain map), PNG — e HEIC e JPEG XL su Safari.</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Clear</v>
+        <v>Choose another</v>
       </c>
       <c r="B430" t="str">
-        <v>Svuota</v>
+        <v>Scegli un’altra</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Embedded ICC profile</v>
+        <v>Clear</v>
       </c>
       <c r="B431" t="str">
-        <v>Profilo ICC incorporato</v>
+        <v>Svuota</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>none — OpenEXR states colour through chromaticities</v>
+        <v>Embedded ICC profile</v>
       </c>
       <c r="B432" t="str">
-        <v>nessuno — OpenEXR indica il colore tramite le cromaticità</v>
+        <v>Profilo ICC incorporato</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
+        <v>none — OpenEXR states colour through chromaticities</v>
       </c>
       <c r="B433" t="str">
-        <v>nessuno — Radiance HDR indica il colore tramite l’intestazione PRIMARIES</v>
+        <v>nessuno — OpenEXR indica il colore tramite le cromaticità</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>checking…</v>
+        <v>none — Radiance HDR states colour through its PRIMARIES header</v>
       </c>
       <c r="B434" t="str">
-        <v>verifica…</v>
+        <v>nessuno — Radiance HDR indica il colore tramite l’intestazione PRIMARIES</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>none</v>
+        <v>checking…</v>
       </c>
       <c r="B435" t="str">
-        <v>nessuno</v>
+        <v>verifica…</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Open in Profile tab</v>
+        <v>none</v>
       </c>
       <c r="B436" t="str">
-        <v>Apri nella scheda Profilo</v>
+        <v>nessuno</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Gain map</v>
+        <v>Open in Profile tab</v>
       </c>
       <c r="B437" t="str">
-        <v>Mappa di guadagno</v>
+        <v>Apri nella scheda Profilo</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>detected, not decoded</v>
+        <v>Gain map</v>
       </c>
       <c r="B438" t="str">
-        <v>rilevata, non decodificata</v>
+        <v>Mappa di guadagno</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>That is not an image. Load profiles through the Profiles pane.</v>
+        <v>detected, not decoded</v>
       </c>
       <c r="B439" t="str">
-        <v>Non è un’immagine. Carica i profili dal pannello Profili.</v>
+        <v>rilevata, non decodificata</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Not an image format profiletool recognises.</v>
+        <v>That is not an image. Load profiles through the Profiles pane.</v>
       </c>
       <c r="B440" t="str">
-        <v>Formato immagine non riconosciuto da profiletool.</v>
+        <v>Non è un’immagine. Carica i profili dal pannello Profili.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
+        <v>Not an image format profiletool recognises.</v>
       </c>
       <c r="B441" t="str">
-        <v>I pixel TIFF non sono ancora mostrati qui: i browser non decodificano il TIFF e la codifica HDR in un TIFF a 16 bit non è ancora decisa (fase 4.3). Il profilo incorporato può essere esaminato.</v>
+        <v>Formato immagine non riconosciuto da profiletool.</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Cannot display this image here:</v>
+        <v>TIFF pixels are not shown here yet: browsers do not decode TIFF, and how HDR is encoded in a 16-bit TIFF is still undecided (Phase 4.3). Its embedded profile can be inspected.</v>
       </c>
       <c r="B442" t="str">
-        <v>Impossibile mostrare questa immagine qui:</v>
+        <v>I pixel TIFF non sono ancora mostrati qui: i browser non decodificano il TIFF e la codifica HDR in un TIFF a 16 bit non è ancora decisa (fase 4.3). Il profilo incorporato può essere esaminato.</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Its embedded profile can still be inspected.</v>
+        <v>Cannot display this image here:</v>
       </c>
       <c r="B443" t="str">
-        <v>Il profilo incorporato può comunque essere esaminato.</v>
+        <v>Impossibile mostrare questa immagine qui:</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Shown by</v>
+        <v>Its embedded profile can still be inspected.</v>
       </c>
       <c r="B444" t="str">
-        <v>Mostrato da</v>
+        <v>Il profilo incorporato può comunque essere esaminato.</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>the browser</v>
+        <v>Shown by</v>
       </c>
       <c r="B445" t="str">
-        <v>il browser</v>
+        <v>Mostrato da</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>profiletool</v>
+        <v>the browser</v>
       </c>
       <c r="B446" t="str">
-        <v>profiletool</v>
+        <v>il browser</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>HDR display</v>
+        <v>profiletool</v>
       </c>
       <c r="B447" t="str">
-        <v>Display HDR</v>
+        <v>profiletool</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
+        <v>HDR display</v>
       </c>
       <c r="B448" t="str">
-        <v>I browser ignorano l’HDR indicato solo da un profilo ICC incorporato, quindi questa immagine può apparire spenta e piatta.</v>
+        <v>Display HDR</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
+        <v>Browsers ignore HDR that is signalled only by an embedded ICC profile, so this image may look dim and flat.</v>
       </c>
       <c r="B449" t="str">
-        <v>Questo browser non può passare un’immagine tra SDR e HDR; è mostrata come il browser la rende.</v>
+        <v>I browser ignorano l’HDR indicato solo da un profilo ICC incorporato, quindi questa immagine può apparire spenta e piatta.</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>The browser could not decode this image.</v>
+        <v>This browser cannot switch an image between SDR and HDR, so it is shown as the browser renders it.</v>
       </c>
       <c r="B450" t="str">
-        <v>Il browser non è riuscito a decodificare questa immagine.</v>
+        <v>Questo browser non può passare un’immagine tra SDR e HDR; è mostrata come il browser la rende.</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Output</v>
+        <v>The browser could not decode this image.</v>
       </c>
       <c r="B451" t="str">
-        <v>Uscita</v>
+        <v>Il browser non è riuscito a decodificare questa immagine.</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>HDR canvas (float16)</v>
+        <v>Output</v>
       </c>
       <c r="B452" t="str">
-        <v>Canvas HDR (float16)</v>
+        <v>Uscita</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>WebGPU (extended range)</v>
+        <v>HDR canvas (float16)</v>
       </c>
       <c r="B453" t="str">
-        <v>WebGPU (gamma estesa)</v>
+        <v>Canvas HDR (float16)</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>SDR canvas (tone-mapped)</v>
+        <v>WebGPU (extended range)</v>
       </c>
       <c r="B454" t="str">
-        <v>Canvas SDR (tone mapping)</v>
+        <v>WebGPU (gamma estesa)</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Size</v>
+        <v>SDR canvas (tone-mapped)</v>
       </c>
       <c r="B455" t="str">
-        <v>Dimensioni</v>
+        <v>Canvas SDR (tone mapping)</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Brightest pixel</v>
+        <v>Size</v>
       </c>
       <c r="B456" t="str">
-        <v>Pixel più luminoso</v>
+        <v>Dimensioni</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>{n}× SDR white</v>
+        <v>Brightest pixel</v>
       </c>
       <c r="B457" t="str">
-        <v>{n}× il bianco SDR</v>
+        <v>Pixel più luminoso</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>Chromaticities</v>
+        <v>{n}× SDR white</v>
       </c>
       <c r="B458" t="str">
-        <v>Cromaticità</v>
+        <v>{n}× il bianco SDR</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>not stated — Rec. 709 assumed</v>
+        <v>Chromaticities</v>
       </c>
       <c r="B459" t="str">
-        <v>non indicate — si assume Rec. 709</v>
+        <v>Cromaticità</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>{from} was not available here ({why}); using the next output.</v>
+        <v>not stated — Rec. 709 assumed</v>
       </c>
       <c r="B460" t="str">
-        <v>{from} non è disponibile qui ({why}); si usa l’uscita successiva.</v>
+        <v>non indicate — si assume Rec. 709</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
+        <v>{from} was not available here ({why}); using the next output.</v>
       </c>
       <c r="B461" t="str">
-        <v>Questa uscita non può trasportare valori più luminosi del bianco; è mostrata la resa SDR con tone mapping.</v>
+        <v>{from} non è disponibile qui ({why}); si usa l’uscita successiva.</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Exposure</v>
+        <v>This output cannot carry brighter-than-white values, so the tone-mapped SDR rendering is shown.</v>
       </c>
       <c r="B462" t="str">
-        <v>Esposizione</v>
+        <v>Questa uscita non può trasportare valori più luminosi del bianco; è mostrata la resa SDR con tone mapping.</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>{n} stops</v>
+        <v>Exposure</v>
       </c>
       <c r="B463" t="str">
-        <v>{n} stop</v>
+        <v>Esposizione</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>Could not decode:</v>
+        <v>{n} stops</v>
       </c>
       <c r="B464" t="str">
-        <v>Decodifica non riuscita:</v>
+        <v>{n} stop</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
+        <v>Could not decode:</v>
       </c>
       <c r="B465" t="str">
-        <v>Questo file è di {size} MB; la scheda HDR apre immagini fino a {max} MB.</v>
+        <v>Decodifica non riuscita:</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>Could not apply the profile:</v>
+        <v>This file is {size} MB; the HDR tab opens images up to {max} MB.</v>
       </c>
       <c r="B466" t="str">
-        <v>Impossibile applicare il profilo:</v>
+        <v>Questo file è di {size} MB; la scheda HDR apre immagini fino a {max} MB.</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>Could not draw the image:</v>
+        <v>Could not apply the profile:</v>
       </c>
       <c r="B467" t="str">
-        <v>Impossibile disegnare l’immagine:</v>
+        <v>Impossibile applicare il profilo:</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
+        <v>Could not draw the image:</v>
       </c>
       <c r="B468" t="str">
-        <v>(questi primari non definiscono uno spazio colore — ignorati, si usa Rec. 709)</v>
+        <v>Impossibile disegnare l’immagine:</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
+        <v>(these primaries do not define a colour space — ignored, Rec. 709 used)</v>
       </c>
       <c r="B469" t="str">
-        <v>il profilo di un JPEG XL è compresso nel codestream, che profiletool non decomprime ancora</v>
+        <v>(questi primari non definiscono uno spazio colore — ignorati, si usa Rec. 709)</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>Decoding…</v>
+        <v>a JPEG XL profile is compressed inside the codestream, which profiletool does not decompress yet</v>
       </c>
       <c r="B470" t="str">
-        <v>Decodifica…</v>
+        <v>il profilo di un JPEG XL è compresso nel codestream, che profiletool non decomprime ancora</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>Dynamic range</v>
+        <v>Decoding…</v>
       </c>
       <c r="B471" t="str">
-        <v>Gamma dinamica</v>
+        <v>Decodifica…</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>This browser offers only the two ends, not a blend.</v>
+        <v>Dynamic range</v>
       </c>
       <c r="B472" t="str">
-        <v>Questo browser offre solo i due estremi, non una miscela.</v>
+        <v>Gamma dinamica</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>decoded by profiletool itself, so browser-independent</v>
+        <v>This browser offers only the two ends, not a blend.</v>
       </c>
       <c r="B473" t="str">
-        <v>decodificato da profiletool stesso, quindi indipendente dal browser</v>
+        <v>Questo browser offre solo i due estremi, non una miscela.</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>this browser decodes it</v>
+        <v>decoded by profiletool itself, so browser-independent</v>
       </c>
       <c r="B474" t="str">
-        <v>questo browser lo decodifica</v>
+        <v>decodificato da profiletool stesso, quindi indipendente dal browser</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>this browser does not decode it</v>
+        <v>this browser decodes it</v>
       </c>
       <c r="B475" t="str">
-        <v>questo browser non lo decodifica</v>
+        <v>questo browser lo decodifica</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
+        <v>this browser does not decode it</v>
       </c>
       <c r="B476" t="str">
-        <v>la visualizzazione HEIC richiede Safari o un altro browser WebKit — Chrome e Firefox non decodificano HEIC su nessuna piattaforma, macOS compreso</v>
+        <v>questo browser non lo decodifica</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
+        <v>HEIC display needs Safari or another WebKit browser — Chrome and Firefox decode HEIC on no platform, macOS included</v>
       </c>
       <c r="B477" t="str">
-        <v>la visualizzazione JPEG XL richiede Safari; gli altri browser non lo supportano ancora</v>
+        <v>la visualizzazione HEIC richiede Safari o un altro browser WebKit — Chrome e Firefox non decodificano HEIC su nessuna piattaforma, macOS compreso</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>deferred to a later release</v>
+        <v>JPEG XL display needs Safari; other browsers have not shipped it</v>
       </c>
       <c r="B478" t="str">
-        <v>rinviato a una versione successiva</v>
+        <v>la visualizzazione JPEG XL richiede Safari; gli altri browser non lo supportano ancora</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
+        <v>deferred to a later release</v>
       </c>
       <c r="B479" t="str">
-        <v>questo display non segnala alcun percorso HDR, quindi l’HDR è reso in SDR con tone mapping</v>
+        <v>rinviato a una versione successiva</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
+        <v>this display reports no HDR path, so HDR renders tone-mapped to SDR</v>
       </c>
       <c r="B480" t="str">
-        <v>questo browser non offre un canvas HDR (serve canvas float16 o WebGPU)</v>
+        <v>questo display non segnala alcun percorso HDR, quindi l’HDR è reso in SDR con tone mapping</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
+        <v>this browser exposes no HDR canvas path (needs float16 canvas or WebGPU)</v>
       </c>
       <c r="B481" t="str">
-        <v>Firefox non mostra immagini HDR e non legge gain map; i contenuti HDR sono mostrati in SDR</v>
+        <v>questo browser non offre un canvas HDR (serve canvas float16 o WebGPU)</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>inspection needs a container parse, not a codec</v>
+        <v>Firefox renders no HDR images and reads no gain maps; HDR content is shown as SDR</v>
       </c>
       <c r="B482" t="str">
-        <v>l’ispezione richiede solo l’analisi del contenitore, non un codec</v>
+        <v>Firefox non mostra immagini HDR e non legge gain map; i contenuti HDR sono mostrati in SDR</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>HDR display and an HDR canvas path are both available</v>
+        <v>inspection needs a container parse, not a codec</v>
       </c>
       <c r="B483" t="str">
-        <v>display HDR e canvas HDR sono entrambi disponibili</v>
+        <v>l’ispezione richiede solo l’analisi del contenitore, non un codec</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>unknown format</v>
+        <v>HDR display and an HDR canvas path are both available</v>
       </c>
       <c r="B484" t="str">
-        <v>formato sconosciuto</v>
+        <v>display HDR e canvas HDR sono entrambi disponibili</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>{browser} on {os}</v>
+        <v>unknown format</v>
       </c>
       <c r="B485" t="str">
-        <v>{browser} su {os}</v>
+        <v>formato sconosciuto</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>{name} · HDR display detected</v>
+        <v>{browser} on {os}</v>
       </c>
       <c r="B486" t="str">
-        <v>{name} · display HDR rilevato</v>
+        <v>{browser} su {os}</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>{name} · SDR display</v>
+        <v>{name} · HDR display detected</v>
       </c>
       <c r="B487" t="str">
-        <v>{name} · display SDR</v>
+        <v>{name} · display HDR rilevato</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
+        <v>{name} · SDR display</v>
       </c>
       <c r="B488" t="str">
-        <v>WebGPU ha applicato il tone mapping «{mode}», quindi l’uscita è limitata a SDR</v>
+        <v>{name} · display SDR</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
+        <v>WebGPU applied tone mapping “{mode}”, so output is clamped to SDR</v>
       </c>
       <c r="B489" t="str">
-        <v>Questo browser non indica il tone mapping WebGPU applicato, quindi l’uscita HDR non è confermata</v>
+        <v>WebGPU ha applicato il tone mapping «{mode}», quindi l’uscita è limitata a SDR</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>Display peak</v>
+        <v>This browser does not report the WebGPU tone mapping it applied, so HDR output is unconfirmed</v>
       </c>
       <c r="B490" t="str">
-        <v>Picco del display</v>
+        <v>Questo browser non indica il tone mapping WebGPU applicato, quindi l’uscita HDR non è confermata</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>{r}× SDR white ({n} stops)</v>
+        <v>Display peak</v>
       </c>
       <c r="B491" t="str">
-        <v>{r}× il bianco SDR ({n} stop)</v>
+        <v>Picco del display</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>1× — SDR display</v>
+        <v>{r}× SDR white ({n} stops)</v>
       </c>
       <c r="B492" t="str">
-        <v>1× — display SDR</v>
+        <v>{r}× il bianco SDR ({n} stop)</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>not known</v>
+        <v>1× — SDR display</v>
       </c>
       <c r="B493" t="str">
-        <v>non noto</v>
+        <v>1× — display SDR</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
+        <v>not known</v>
       </c>
       <c r="B494" t="str">
-        <v>Questo display non segnala HDR, quindi il browser mostra l’immagine in SDR a entrambi gli estremi.</v>
+        <v>non noto</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
+        <v>This display reports no HDR, so the browser shows this image in SDR at either end.</v>
       </c>
       <c r="B495" t="str">
-        <v>Questo display non segnala HDR, quindi tutto ciò che supera il bianco SDR viene tagliato. «Adatta al display» mostra invece la resa con tone mapping.</v>
+        <v>Questo display non segnala HDR, quindi il browser mostra l’immagine in SDR a entrambi gli estremi.</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
+        <v>This display reports no HDR, so everything brighter than SDR white clips. Fit to display shows the tone-mapped rendering instead.</v>
       </c>
       <c r="B496" t="str">
-        <v>Questa immagine richiede {img}× il bianco SDR, ma questo display arriva solo a {disp}×, quindi i valori più luminosi vengono tagliati. «Adatta al display» li attenua verso il picco del display.</v>
+        <v>Questo display non segnala HDR, quindi tutto ciò che supera il bianco SDR viene tagliato. «Adatta al display» mostra invece la resa con tone mapping.</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>Fit to display</v>
+        <v>This image asks for {img}× SDR white, but this display shows up to {disp}×, so brighter values clip. Fit to display rolls them off into the display’s peak instead.</v>
       </c>
       <c r="B497" t="str">
-        <v>Adatta al display</v>
+        <v>Questa immagine richiede {img}× il bianco SDR, ma questo display arriva solo a {disp}×, quindi i valori più luminosi vengono tagliati. «Adatta al display» li attenua verso il picco del display.</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>Image details</v>
+        <v>Fit to display</v>
       </c>
       <c r="B498" t="str">
-        <v>Dettagli immagine</v>
+        <v>Adatta al display</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
+        <v>Image details</v>
       </c>
       <c r="B499" t="str">
-        <v>non disponibile — il browser rende questa immagine e non può limitarla a un picco dato</v>
+        <v>Dettagli immagine</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>not available — this output shows nothing above SDR white</v>
+        <v>not available — the browser renders this image and cannot cap it at a set peak</v>
       </c>
       <c r="B500" t="str">
-        <v>non disponibile — questa uscita non mostra nulla sopra il bianco SDR</v>
+        <v>non disponibile — il browser rende questa immagine e non può limitarla a un picco dato</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>not available — this display’s peak is not known</v>
+        <v>not available — this output shows nothing above SDR white</v>
       </c>
       <c r="B501" t="str">
-        <v>non disponibile — il picco di questo display non è noto</v>
+        <v>non disponibile — questa uscita non mostra nulla sopra il bianco SDR</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>Zoom in</v>
+        <v>not available — this display’s peak is not known</v>
       </c>
       <c r="B502" t="str">
-        <v>Ingrandisci</v>
+        <v>non disponibile — il picco di questo display non è noto</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>Zoom out</v>
+        <v>Zoom in</v>
       </c>
       <c r="B503" t="str">
-        <v>Riduci</v>
+        <v>Ingrandisci</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>Fit image</v>
+        <v>Zoom out</v>
       </c>
       <c r="B504" t="str">
-        <v>Adatta immagine</v>
+        <v>Riduci</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>Actual pixels (1:1)</v>
+        <v>Fit image</v>
       </c>
       <c r="B505" t="str">
-        <v>Pixel reali (1:1)</v>
+        <v>Adatta immagine</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
+        <v>Actual pixels (1:1)</v>
       </c>
       <c r="B506" t="str">
-        <v>Trascina per spostare · Ctrl+rotellina per lo zoom · doppio clic per ripristinare</v>
+        <v>Pixel reali (1:1)</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>Drag to resize the image area; double-click to restore the default size</v>
+        <v>Drag to pan · Ctrl+wheel to zoom · double-click to reset</v>
       </c>
       <c r="B507" t="str">
-        <v>Trascina per ridimensionare l’area immagine; doppio clic per tornare alla dimensione predefinita</v>
+        <v>Trascina per spostare · Ctrl+rotellina per lo zoom · doppio clic per ripristinare</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>Image view</v>
+        <v>Drag to resize the image area; double-click to restore the default size</v>
       </c>
       <c r="B508" t="str">
-        <v>Vista immagine</v>
+        <v>Trascina per ridimensionare l’area immagine; doppio clic per tornare alla dimensione predefinita</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
+        <v>Image view</v>
       </c>
       <c r="B509" t="str">
-        <v>Limita la luminosità al picco segnalato dal display. Su Windows questo valore può restare indietro rispetto ai cambi di luminosità.</v>
+        <v>Vista immagine</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>no limit</v>
+        <v>Caps brightness at the peak this display reports. On Windows that figure can lag behind brightness changes.</v>
       </c>
       <c r="B510" t="str">
-        <v>nessun limite</v>
+        <v>Limita la luminosità al picco segnalato dal display. Su Windows questo valore può restare indietro rispetto ai cambi di luminosità.</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>limit {n} stops ({r}×)</v>
+        <v>no limit</v>
       </c>
       <c r="B511" t="str">
-        <v>limite {n} stop ({r}×)</v>
+        <v>nessun limite</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>SDR white</v>
+        <v>limit {n} stops ({r}×)</v>
       </c>
       <c r="B512" t="str">
-        <v>Bianco SDR</v>
+        <v>limite {n} stop ({r}×)</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
+        <v>SDR white</v>
       </c>
       <c r="B513" t="str">
-        <v>Bianco SDR semplice, per confronto. Su un display HDR le alte luci HDR appaiono più luminose di questo.</v>
+        <v>Bianco SDR</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>SDR white patch</v>
+        <v>Plain SDR white, for comparison. On an HDR display, HDR highlights look brighter than this.</v>
       </c>
       <c r="B514" t="str">
-        <v>Riquadro bianco SDR</v>
+        <v>Bianco SDR semplice, per confronto. Su un display HDR le alte luci HDR appaiono più luminose di questo.</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>Drag to move it; double-click to put it back beside the image.</v>
+        <v>SDR white patch</v>
       </c>
       <c r="B515" t="str">
-        <v>Trascinalo per spostarlo; doppio clic per rimetterlo accanto all’immagine.</v>
+        <v>Riquadro bianco SDR</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>Assign profile</v>
+        <v>Drag to move it; double-click to put it back beside the image.</v>
       </c>
       <c r="B516" t="str">
-        <v>Assegna profilo</v>
+        <v>Trascinalo per spostarlo; doppio clic per rimetterlo accanto all’immagine.</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>None — use what the file signals</v>
+        <v>Assign profile</v>
       </c>
       <c r="B517" t="str">
-        <v>Nessuno — secondo il file</v>
+        <v>Assegna profilo</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>Embedded profile ({n} B)</v>
+        <v>None — use what the file signals</v>
       </c>
       <c r="B518" t="str">
-        <v>Profilo incorporato ({n} B)</v>
+        <v>Nessuno — secondo il file</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>HDR Profiles in the pool</v>
+        <v>Embedded profile ({n} B)</v>
       </c>
       <c r="B519" t="str">
-        <v>Profili HDR nel pool</v>
+        <v>Profilo incorporato ({n} B)</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>Profile</v>
+        <v>HDR Profiles in the pool</v>
       </c>
       <c r="B520" t="str">
-        <v>Profilo</v>
+        <v>Profili HDR nel pool</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>embedded profile</v>
+        <v>Profile</v>
       </c>
       <c r="B521" t="str">
-        <v>profilo incorporato</v>
+        <v>Profilo</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>Colour engine path</v>
+        <v>embedded profile</v>
       </c>
       <c r="B522" t="str">
-        <v>Percorso del motore colore</v>
+        <v>profilo incorporato</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>HDR path, gain curve applied</v>
+        <v>Colour engine path</v>
       </c>
       <c r="B523" t="str">
-        <v>Percorso HDR, curva di guadagno applicata</v>
+        <v>Percorso del motore colore</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>HDR path, no gain curve</v>
+        <v>HDR path, gain curve applied</v>
       </c>
       <c r="B524" t="str">
-        <v>Percorso HDR, nessuna curva di guadagno</v>
+        <v>Percorso HDR, curva di guadagno applicata</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>Baked AToB0 — not the HDR path</v>
+        <v>HDR path, no gain curve</v>
       </c>
       <c r="B525" t="str">
-        <v>AToB0 precalcolato — non il percorso HDR</v>
+        <v>Percorso HDR, nessuna curva di guadagno</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>Transfer</v>
+        <v>Baked AToB0 — not the HDR path</v>
       </c>
       <c r="B526" t="str">
-        <v>Trasferimento</v>
+        <v>AToB0 precalcolato — non il percorso HDR</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>HDR reference white</v>
+        <v>Transfer</v>
       </c>
       <c r="B527" t="str">
-        <v>Bianco di riferimento HDR</v>
+        <v>Trasferimento</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>Linear values</v>
+        <v>HDR reference white</v>
       </c>
       <c r="B528" t="str">
-        <v>Valori lineari</v>
+        <v>Bianco di riferimento HDR</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>File 1.0 = HDR reference white</v>
+        <v>Linear values</v>
       </c>
       <c r="B529" t="str">
-        <v>File 1,0 = bianco di riferimento HDR</v>
+        <v>Valori lineari</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>File 1.0 = HDR reference white</v>
       </c>
       <c r="B530" t="str">
-        <v>File 1,0 = 1 cd/m² (ICC.1 clausola 8.10.2 a)</v>
+        <v>File 1,0 = bianco di riferimento HDR</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
       </c>
       <c r="B531" t="str">
-        <v>I file OpenEXR e Radiance HDR pongono per convenzione il bianco SDR a 1,0, mentre un trasferimento ICC lineare legge 1,0 come 1 cd/m². Per impostazione predefinita il file viene scalato in modo che il suo 1,0 cada sul bianco di riferimento HDR del profilo.</v>
+        <v>File 1,0 = 1 cd/m² (ICC.1 clausola 8.10.2 a)</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>Input scale</v>
+        <v>OpenEXR and Radiance HDR files conventionally put SDR white at 1.0, while an ICC Linear transfer reads 1.0 as 1 cd/m². The default scales the file so its 1.0 lands on the profile’s HDR reference white.</v>
       </c>
       <c r="B532" t="str">
-        <v>Scala di ingresso</v>
+        <v>I file OpenEXR e Radiance HDR pongono per convenzione il bianco SDR a 1,0, mentre un trasferimento ICC lineare legge 1,0 come 1 cd/m². Per impostazione predefinita il file viene scalato in modo che il suo 1,0 cada sul bianco di riferimento HDR del profilo.</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>×{w} — file 1.0 = reference white</v>
+        <v>Input scale</v>
       </c>
       <c r="B533" t="str">
-        <v>×{w} — file 1,0 = bianco di riferimento</v>
+        <v>Scala di ingresso</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>none — file 1.0 = 1 cd/m²</v>
+        <v>×{w} — file 1.0 = reference white</v>
       </c>
       <c r="B534" t="str">
-        <v>nessuna — file 1,0 = 1 cd/m²</v>
+        <v>×{w} — file 1,0 = bianco di riferimento</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>Target headroom</v>
+        <v>none — file 1.0 = 1 cd/m²</v>
       </c>
       <c r="B535" t="str">
-        <v>Margine di destinazione</v>
+        <v>nessuna — file 1,0 = 1 cd/m²</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>{r}× reference white ({n} stops)</v>
+        <v>Target headroom</v>
       </c>
       <c r="B536" t="str">
-        <v>{r}× il bianco di riferimento ({n} stop)</v>
+        <v>Margine di destinazione</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>Tone mapping</v>
+        <v>{r}× reference white ({n} stops)</v>
       </c>
       <c r="B537" t="str">
-        <v>Mappatura dei toni</v>
+        <v>{r}× il bianco di riferimento ({n} stop)</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Tone mapping</v>
       </c>
       <c r="B538" t="str">
-        <v>Auto (classifica della clausola 8.10.3)</v>
+        <v>Mappatura dei toni</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Gain curve (HAGC)</v>
+        <v>Auto (clause 8.10.3 ranking)</v>
       </c>
       <c r="B539" t="str">
-        <v>Curva di guadagno (HAGC)</v>
+        <v>Auto (classifica della clausola 8.10.3)</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>Baked SDR fallback (AToB0)</v>
+        <v>Gain curve (HAGC)</v>
       </c>
       <c r="B540" t="str">
-        <v>Ripiego SDR precalcolato (AToB0)</v>
+        <v>Curva di guadagno (HAGC)</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>Off — as a pre-amendment CMM</v>
+        <v>Baked SDR fallback (AToB0)</v>
       </c>
       <c r="B541" t="str">
-        <v>Disattivato — come un CMM precedente all’emendamento</v>
+        <v>Ripiego SDR precalcolato (AToB0)</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>Applying the profile…</v>
+        <v>Off — as a pre-amendment CMM</v>
       </c>
       <c r="B542" t="str">
-        <v>Applicazione del profilo…</v>
+        <v>Disattivato — come un CMM precedente all’emendamento</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
+        <v>Applying the profile…</v>
       </c>
       <c r="B543" t="str">
-        <v>{format} contiene luce lineare, quindi serve un profilo con trasferimento Linear (8).</v>
+        <v>Applicazione del profilo…</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>Assigning a profile needs a 3-channel RGB image.</v>
+        <v>{format} holds linear light, so it needs a profile whose transfer is Linear (8).</v>
       </c>
       <c r="B544" t="str">
-        <v>Per assegnare un profilo serve un’immagine RGB a 3 canali.</v>
+        <v>{format} contiene luce lineare, quindi serve un profilo con trasferimento Linear (8).</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>To interpret its values, assign a profile above.</v>
+        <v>Assigning a profile needs a 3-channel RGB image.</v>
       </c>
       <c r="B545" t="str">
-        <v>Per interpretarne i valori, assegna un profilo qui sopra.</v>
+        <v>Per assegnare un profilo serve un’immagine RGB a 3 canali.</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>HDR Profiles</v>
+        <v>To interpret its values, assign a profile above.</v>
       </c>
       <c r="B546" t="str">
-        <v>Profili HDR</v>
+        <v>Per interpretarne i valori, assegna un profilo qui sopra.</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>Linear transfer</v>
+        <v>HDR Profiles</v>
       </c>
       <c r="B547" t="str">
-        <v>Trasferimento lineare</v>
+        <v>Profili HDR</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>Non-linear transfer (PQ, HLG)</v>
+        <v>Linear transfer</v>
       </c>
       <c r="B548" t="str">
-        <v>Trasferimento non lineare (PQ, HLG)</v>
+        <v>Trasferimento lineare</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>Non-linear transfer (PQ, HLG)</v>
       </c>
       <c r="B549" t="str">
-        <v>Profili HDR — trasferimento lineare</v>
+        <v>Trasferimento non lineare (PQ, HLG)</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR Profiles — Linear transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>Profili HDR — trasferimento PQ / HLG</v>
+        <v>Profili HDR — trasferimento lineare</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>HDR Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B551" t="str">
-        <v>{format} contiene luce lineare, quindi si possono assegnare solo profili HDR con trasferimento lineare.</v>
+        <v>Profili HDR — trasferimento PQ / HLG</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B552" t="str">
-        <v>{n} profilo/i HDR PQ/HLG nel pool non sono proposti — il pannello Profili li elenca sotto Profili HDR › Trasferimento non lineare.</v>
+        <v>{format} contiene luce lineare, quindi si possono assegnare solo profili HDR con trasferimento lineare.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>Nel pool non c’è ancora un profilo HDR con trasferimento lineare; il pannello Profili raggruppa i profili HDR per trasferimento.</v>
+        <v>{n} profilo/i HDR PQ/HLG nel pool non sono proposti — il pannello Profili li elenca sotto Profili HDR › Trasferimento non lineare.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
       </c>
       <c r="B554" t="str">
-        <v>IccProfLib non applica questa curva di guadagno: {why}. Un CMM passa al descrittore di tone mapping successivo (clausola 8.10.3).</v>
+        <v>Nel pool non c’è ancora un profilo HDR con trasferimento lineare; il pannello Profili raggruppa i profili HDR per trasferimento.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
       </c>
       <c r="B555" t="str">
-        <v>Margine del display</v>
+        <v>IccProfLib non applica questa curva di guadagno: {why}. Un CMM passa al descrittore di tone mapping successivo (clausola 8.10.3).</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B556" t="str">
-        <v>{n} stop (≈{r}× il bianco di riferimento)</v>
+        <v>Margine del display</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B557" t="str">
-        <v>Base</v>
+        <v>{n} stop (≈{r}× il bianco di riferimento)</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Preview through the colour engine</v>
+        <v>Baseline</v>
       </c>
       <c r="B558" t="str">
-        <v>Anteprima tramite il motore colore</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B559" t="str">
-        <v>Come creata (base {h} stop, senza guadagno)</v>
+        <v>Anteprima tramite il motore colore</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B560" t="str">
-        <v>Mappata per {h} stop</v>
+        <v>Come creata (base {h} stop, senza guadagno)</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B561" t="str">
-        <v>Gli stessi pixel di prova (segnale {transfer} crescente da sinistra a destra: grigio, poi R, G, B, Y, C, M) attraverso la trasformazione HDR di IccProfLib. Entrambe le strisce sono limitate a {r}× il bianco di riferimento HDR, come le mostrerebbe un display con {h} stop di headroom: dove la striscia superiore satura piatta, la curva di guadagno attenua le alte luci.</v>
+        <v>Mappata per {h} stop</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>reference white</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B562" t="str">
-        <v>bianco di riferimento</v>
+        <v>Gli stessi pixel di prova (segnale {transfer} crescente da sinistra a destra: grigio, poi R, G, B, Y, C, M) attraverso la trasformazione HDR di IccProfLib. Entrambe le strisce sono limitate a {r}× il bianco di riferimento HDR, come le mostrerebbe un display con {h} stop di headroom: dove la striscia superiore satura piatta, la curva di guadagno attenua le alte luci.</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>display peak</v>
+        <v>reference white</v>
       </c>
       <c r="B563" t="str">
-        <v>picco del display</v>
+        <v>bianco di riferimento</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>display peak</v>
       </c>
       <c r="B564" t="str">
-        <v>Anteprima non disponibile: {why}</v>
+        <v>picco del display</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B565" t="str">
-        <v>il motore colore non ha seguito il percorso HDR per questo profilo</v>
+        <v>Anteprima non disponibile: {why}</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>Gain across every headroom</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B566" t="str">
-        <v>Guadagno a ogni headroom</v>
+        <v>il motore colore non ha seguito il percorso HDR per questo profilo</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B567" t="str">
-        <v>Guadagno applicato a un ingresso grigio a ogni headroom del display: il blu comprime, il rosso espande, il bianco lo lascia invariato. Le linee punteggiate indicano le curve del tag, quella continua la base, quella ambra il cursore; la diagonale tratteggiata è dove l’ingresso raggiunge il picco del display. Fai clic per spostare il cursore.</v>
+        <v>Guadagno a ogni headroom</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B568" t="str">
-        <v>Ingresso (stop rispetto al bianco di riferimento HDR)</v>
+        <v>Guadagno applicato a un ingresso grigio a ogni headroom del display: il blu comprime, il rosso espande, il bianco lo lascia invariato. Le linee punteggiate indicano le curve del tag, quella continua la base, quella ambra il cursore; la diagonale tratteggiata è dove l’ingresso raggiunge il picco del display. Fai clic per spostare il cursore.</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B569" t="str">
-        <v>Headroom del display (stop)</v>
+        <v>Ingresso (stop rispetto al bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Gain (stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B570" t="str">
-        <v>Guadagno (stop)</v>
+        <v>Headroom del display (stop)</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B571" t="str">
-        <v>Curva nel tag</v>
+        <v>Guadagno (stop)</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Baseline</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B572" t="str">
-        <v>Base</v>
+        <v>Curva nel tag</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Slider</v>
+        <v>Baseline</v>
       </c>
       <c r="B573" t="str">
-        <v>Cursore</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Input = display peak</v>
+        <v>Slider</v>
       </c>
       <c r="B574" t="str">
-        <v>Ingresso = picco del display</v>
+        <v>Cursore</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B575" t="str">
-        <v>Curve tonali del grigio per headroom</v>
+        <v>Ingresso = picco del display</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B576" t="str">
-        <v>La curva tonale del grigio a ogni headroom memorizzato nel tag, colorata dal basso (blu) all’alto (rosso), con la curva del cursore in ambra. Entrambi gli assi sono in stop, quindi la diagonale indica nessuna modifica.</v>
+        <v>Curve tonali del grigio per headroom</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B577" t="str">
-        <v>Uscita (stop rispetto al bianco di riferimento HDR)</v>
+        <v>La curva tonale del grigio a ogni headroom memorizzato nel tag, colorata dal basso (blu) all’alto (rosso), con la curva del cursore in ambra. Entrambi gli assi sono in stop, quindi la diagonale indica nessuna modifica.</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>{h} stops</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B578" t="str">
-        <v>{h} stop</v>
+        <v>Uscita (stop rispetto al bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>{h} stops</v>
       </c>
       <c r="B579" t="str">
-        <v>{h} stop (base)</v>
+        <v>{h} stop</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B580" t="str">
-        <v>A {h} stop (cursore)</v>
+        <v>{h} stop (base)</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B581" t="str">
-        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
+        <v>A {h} stop (cursore)</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B582" t="str">
-        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
+        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B583" t="str">
-        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
+        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B584" t="str">
-        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
+        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B585" t="str">
-        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
+        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B586" t="str">
-        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
+        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B587" t="str">
-        <v>Curva a {h} stop (nessun guadagno)</v>
+        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B588" t="str">
-        <v>Curva a {h} stop</v>
+        <v>Curva a {h} stop (nessun guadagno)</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B589" t="str">
-        <v>Applicato a {h} stop</v>
+        <v>Curva a {h} stop</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B590" t="str">
-        <v>Guadagno applicato a questo margine</v>
+        <v>Applicato a {h} stop</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B591" t="str">
-        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
+        <v>Guadagno applicato a questo margine</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B592" t="str">
-        <v>Guadagno (stop log2)</v>
+        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B593" t="str">
-        <v>Curva tonale dei grigi a questo margine</v>
+        <v>Guadagno (stop log2)</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B594" t="str">
-        <v>Ingresso (× bianco di riferimento HDR)</v>
+        <v>Curva tonale dei grigi a questo margine</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B595" t="str">
-        <v>Uscita (× bianco di riferimento HDR)</v>
+        <v>Ingresso (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B596" t="str">
-        <v>Nessuna modifica</v>
+        <v>Uscita (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B597" t="str">
-        <v>Picco del display a {h} stop</v>
+        <v>Nessuna modifica</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B598" t="str">
-        <v>Uscita a {h} stop</v>
+        <v>Picco del display a {h} stop</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B599" t="str">
-        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
+        <v>Uscita a {h} stop</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B600" t="str">
-        <v>Identifica i display</v>
+        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B601" t="str">
-        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
+        <v>Identifica i display</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B602" t="str">
-        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
+        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B603" t="str">
-        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
+        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B604" t="str">
-        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
+        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B605" t="str">
-        <v>Impossibile identificare i display.</v>
+        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B606" t="str">
-        <v>Eventi del display</v>
+        <v>Impossibile identificare i display.</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B607" t="str">
-        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
+        <v>Eventi del display</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B608" t="str">
-        <v>Primari di colore</v>
+        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B609" t="str">
-        <v>Caratteristiche di trasferimento</v>
+        <v>Primari di colore</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B610" t="str">
-        <v>Coefficienti di matrice</v>
+        <v>Caratteristiche di trasferimento</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B611" t="str">
-        <v>Flag intervallo video completo</v>
+        <v>Coefficienti di matrice</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B612" t="str">
-        <v>Intervallo completo</v>
+        <v>Flag intervallo video completo</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B613" t="str">
-        <v>Intervallo ridotto</v>
+        <v>Intervallo completo</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B614" t="str">
-        <v>non assegnato da ITU-T H.273</v>
+        <v>Intervallo ridotto</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B615" t="str">
-        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
+        <v>non assegnato da ITU-T H.273</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B616" t="str">
-        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
+        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B617" t="str">
-        <v>RAPPORTO</v>
+        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B618" t="str">
-        <v>NON SUPERATO</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B619" t="str">
-        <v>controlli</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B620" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B621" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B622" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B623" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B624" t="str">
-        <v>Iscriviti</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B625" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B626" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B627" t="str">
-        <v>Chiudi</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B628" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B629" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B630" t="str">
-        <v>tu@esempio.com</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B631" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B632" t="str">
-        <v>(opzionale)</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B633" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B634" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B635" t="str">
-        <v>Annulla</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B636" t="str">
-        <v>Iscriviti</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B637" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B638" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B639" t="str">
-        <v>Chiudi</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B640" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B641" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B642" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B643" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B644" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B646" t="str">
-        <v>Errore:</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B647" t="str">
-        <v>Converti in XML</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B648" t="str">
-        <v>Converti in JSON</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B649" t="str">
-        <v>Converti in ICC</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B650" t="str">
-        <v>Conversione in XML…</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B651" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B652" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B653" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B654" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B655" t="str">
-        <v>ID profilo</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B656" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B657" t="str">
-        <v>Nome tag</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B658" t="str">
-        <v>ID</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B659" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B660" t="str">
-        <v>Dimensione</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B661" t="str">
-        <v>Riempimento</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B662" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B663" t="str">
-        <v>Tipo</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B664" t="str">
-        <v>Array di {type}</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B665" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B666" t="str">
-        <v>byte</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B667" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B668" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B669" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B670" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B671" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B672" t="str">
-        <v>Il profilo è valido</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B673" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B674" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B675" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B676" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B677" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B678" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B679" t="str">
-        <v>Valido</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B680" t="str">
-        <v>Avviso</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B681" t="str">
-        <v>Errore</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B682" t="str">
-        <v>Sconosciuto</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B683" t="str">
-        <v>Superato</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B684" t="str">
-        <v>Non superato</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B685" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B686" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B687" t="str">
-        <v>Attivato da</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B688" t="str">
-        <v>Campo</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B689" t="str">
-        <v>Valore attuale</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B690" t="str">
-        <v>Richiesto: 0</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B691" t="str">
-        <v>Atteso: {value}</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B692" t="str">
-        <v>Non valido</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B693" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B694" t="str">
-        <v>Chiudi</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B695" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B696" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Caricamento editor XML…</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B697" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Caricamento editor JSON…</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B698" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B699" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B700" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>● modifiche XML non salvate</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B701" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● modifiche JSON non salvate</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B702" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B703" t="str">
-        <v>rientro</v>
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B704" t="str">
-        <v>ordina chiavi</v>
+        <v>rientro</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B705" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B705" t="str">
+      <c r="B706" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B705"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B706"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B466"/>
+  <dimension ref="A1:B467"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1197,2949 +1197,2957 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sort by name</v>
+        <v>Tap to select, then tap a tab to send.</v>
       </c>
       <c r="B100" t="str">
-        <v>Ordina per nome</v>
+        <v>Tocca per selezionare, poi tocca una scheda per inviare.</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B101" t="str">
-        <v>A–Z</v>
+        <v>Ordina per nome</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B102" t="str">
-        <v>Nuovo profilo da .cube</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B103" t="str">
-        <v>Crea un DeviceLink ICC da una LUT 3D .cube di Adobe/Resolve. Il risultato viene aggiunto al tuo pool e aperto; nulla viene scaricato finché non fai clic su Salva profilo ICC.</v>
+        <v>Nuovo profilo da .cube</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and opened; nothing is downloaded until you click Save ICC profile.</v>
       </c>
       <c r="B104" t="str">
-        <v>Scegli file .cube</v>
+        <v>Crea un DeviceLink ICC da una LUT 3D .cube di Adobe/Resolve. Il risultato viene aggiunto al tuo pool e aperto; nulla viene scaricato finché non fai clic su Salva profilo ICC.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Scegli file .cube</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B105" t="str">
+      <c r="B106" t="str">
         <v>oppure trascinalo qui o incolla sotto</v>
       </c>
     </row>
-    <row r="106" xml:space="preserve">
-      <c r="A106" t="str" xml:space="preserve">
+    <row r="107" xml:space="preserve">
+      <c r="A107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B106" t="str" xml:space="preserve">
+      <c r="B107" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B107" t="str">
-        <v>Annulla</v>
-      </c>
-    </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B108" t="str">
-        <v>Crea DeviceLink</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B109" t="str">
-        <v>Creazione…</v>
+        <v>Crea DeviceLink</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B110" t="str">
-        <v>Impossibile leggere questo file.</v>
+        <v>Creazione…</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B111" t="str">
-        <v>Profilo</v>
+        <v>Impossibile leggere questo file.</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B112" t="str">
-        <v>Confronta</v>
+        <v>Profilo</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B113" t="str">
-        <v>Collega</v>
+        <v>Confronta</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B114" t="str">
-        <v>Spettrale</v>
+        <v>Collega</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B115" t="str">
-        <v>Trascina i profili dal pool su questa scheda</v>
+        <v>Spettrale</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B116" t="str">
-        <v>Rimuovi</v>
+        <v>Trascina i profili dal pool su questa scheda</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B117" t="str">
-        <v>Nessun profilo selezionato</v>
+        <v>Rimuovi</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B118" t="str">
-        <v>Trascina un profilo dal pool sulla scheda Profilo per ispezionarlo.</v>
+        <v>Nessun profilo selezionato</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B119" t="str">
-        <v>Ancora niente da confrontare</v>
+        <v>Trascina un profilo dal pool sulla scheda Profilo per ispezionarlo.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B120" t="str">
-        <v>Trascina uno o più profili sulla scheda Confronta.</v>
+        <v>Ancora niente da confrontare</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B121" t="str">
-        <v>Confronto di gamut</v>
+        <v>Trascina uno o più profili sulla scheda Confronta.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B122" t="str">
-        <v>Le viste gamut 3D e sezione 2D arriveranno qui. Accumulati:</v>
+        <v>Confronto di gamut</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B123" t="str">
-        <v>Intento di rendering</v>
+        <v>Le viste gamut 3D e sezione 2D arriveranno qui. Accumulati:</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B124" t="str">
-        <v>Guscio</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B125" t="str">
-        <v>Wireframe</v>
+        <v>Guscio</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B126" t="str">
-        <v>Numeri degli assi</v>
+        <v>Wireframe</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B127" t="str">
-        <v>Opacità</v>
+        <v>Numeri degli assi</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B128" t="str">
-        <v>Colore</v>
+        <v>Opacità</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B129" t="str">
-        <v>Pieno</v>
+        <v>Colore</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B130" t="str">
-        <v>Per valore</v>
+        <v>Pieno</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B131" t="str">
-        <v>Per tonalità</v>
+        <v>Per valore</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B132" t="str">
-        <v>Rotazione</v>
+        <v>Per tonalità</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B133" t="str">
-        <v>Piattaforma girevole</v>
+        <v>Rotazione</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B134" t="str">
-        <v>Orbita</v>
+        <v>Piattaforma girevole</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B135" t="str">
-        <v>Velocità di trascinamento</v>
+        <v>Orbita</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B136" t="str">
-        <v>Rollio</v>
+        <v>Velocità di trascinamento</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B137" t="str">
-        <v>Velocità di rollio</v>
+        <v>Rollio</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B138" t="str">
-        <v>Creazione del gamut…</v>
+        <v>Velocità di rollio</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B139" t="str">
-        <v>nessun gamut</v>
+        <v>Creazione del gamut…</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B140" t="str">
-        <v>Mostra / nascondi</v>
+        <v>nessun gamut</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B141" t="str">
-        <v>Guscio del gamut 3D</v>
+        <v>Mostra / nascondi</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B142" t="str">
-        <v>Sezione del gamut 2D</v>
+        <v>Guscio del gamut 3D</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B143" t="str">
-        <v>Piano</v>
+        <v>Sezione del gamut 2D</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B144" t="str">
-        <v>L*</v>
+        <v>Piano</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B145" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B146" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B147" t="str">
-        <v>Nessuno dei profili selezionati ha una trasformazione dispositivo→PCS da cui derivare un gamut.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B148" t="str">
-        <v>Collegamento</v>
+        <v>Nessuno dei profili selezionati ha una trasformazione dispositivo→PCS da cui derivare un gamut.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B149" t="str">
-        <v>La produzione di DeviceLink e le trasformazioni multi-profilo arriveranno in una fase successiva.</v>
+        <v>Collegamento</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B150" t="str">
-        <v>Altri strumenti di collegamento (DeviceLink, …) arriveranno qui.</v>
+        <v>La produzione di DeviceLink e le trasformazioni multi-profilo arriveranno in una fase successiva.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B151" t="str">
-        <v>Generatore di display V4</v>
+        <v>Altri strumenti di collegamento (DeviceLink, …) arriveranno qui.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B152" t="str">
-        <v>Trascina qui un profilo display RGB V5 e un profilo osservatore V5 per creare un profilo display V4.</v>
+        <v>Generatore di display V4</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B153" t="str">
-        <v>Display RGB V5</v>
+        <v>Trascina qui un profilo display RGB V5 e un profilo osservatore V5 per creare un profilo display V4.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B154" t="str">
-        <v>rilascia un profilo display</v>
+        <v>Display RGB V5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B155" t="str">
-        <v>Osservatore V5 (PCC)</v>
+        <v>rilascia un profilo display</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B156" t="str">
-        <v>rilascia un profilo osservatore</v>
+        <v>Osservatore V5 (PCC)</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B157" t="str">
-        <v>Ignorato un profilo che non è né un display RGB V5 né un osservatore.</v>
+        <v>rilascia un profilo osservatore</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B158" t="str">
-        <v>Crea profilo display V4</v>
+        <v>Ignorato un profilo che non è né un display RGB V5 né un osservatore.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B159" t="str">
-        <v>Nome del profilo</v>
+        <v>Crea profilo display V4</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B160" t="str">
-        <v>Crea</v>
+        <v>Nome del profilo</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B161" t="str">
-        <v>Creazione…</v>
+        <v>Crea</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B162" t="str">
-        <v>«{name}» creato — aggiunto al pool e a questa scheda.</v>
+        <v>Creazione…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B163" t="str">
-        <v>Pipeline di collegamento</v>
+        <v>«{name}» creato — aggiunto al pool e a questa scheda.</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B164" t="str">
-        <v>Crea una catena di profili, quindi genera un DeviceLink, trasforma un'immagine o trasforma un set di dati colore attraverso di essa.</v>
+        <v>Pipeline di collegamento</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B165" t="str">
-        <v>Fatto</v>
+        <v>Crea una catena di profili, quindi genera un DeviceLink, trasforma un'immagine o trasforma un set di dati colore attraverso di essa.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B166" t="str">
-        <v>Trascina un'immagine da trasformare (TIFF/PNG/JPEG)</v>
+        <v>Fatto</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B167" t="str">
-        <v>Controllo immagine…</v>
+        <v>Trascina un'immagine da trasformare (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B168" t="str">
-        <v>Immagine non supportata (TIFF, PNG o JPEG).</v>
+        <v>Controllo immagine…</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B169" t="str">
-        <v>Immagine troppo grande ({mp} MP; limite {max} MP).</v>
+        <v>Immagine non supportata (TIFF, PNG o JPEG).</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B170" t="str">
-        <v>Trasforma immagine</v>
+        <v>Immagine troppo grande ({mp} MP; limite {max} MP).</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B171" t="str">
-        <v>Trasformazione…</v>
+        <v>Trasforma immagine</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B172" t="str">
-        <v>Trascina i profili per avviare la catena</v>
+        <v>Trasformazione…</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B173" t="str">
-        <v>rimosso</v>
+        <v>Trascina i profili per avviare la catena</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B174" t="str">
-        <v>Sposta prima</v>
+        <v>rimosso</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B175" t="str">
-        <v>Sposta dopo</v>
+        <v>Sposta prima</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B176" t="str">
-        <v>Sposta su</v>
+        <v>Sposta dopo</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B177" t="str">
-        <v>Sposta giù</v>
+        <v>Sposta su</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B178" t="str">
-        <v>Intento di rendering (tutti)</v>
+        <v>Sposta giù</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B179" t="str">
-        <v>Intento di rendering per questa trasformazione</v>
+        <v>Intento di rendering (tutti)</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B180" t="str">
-        <v>Le trasformazioni usano intenti di rendering diversi</v>
+        <v>Intento di rendering per questa trasformazione</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B181" t="str">
-        <v>Inverti la direzione della catena (inverte la trasformazione iniziale, propagandosi lungo la catena)</v>
+        <v>Le trasformazioni usano intenti di rendering diversi</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B182" t="str">
-        <v>Un profilo della catena è stato rimosso dal pool — rimuovilo per continuare.</v>
+        <v>Inverti la direzione della catena (inverte la trasformazione iniziale, propagandosi lungo la catena)</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B183" t="str">
-        <v>Catena</v>
+        <v>Un profilo della catena è stato rimosso dal pool — rimuovilo per continuare.</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B184" t="str">
-        <v>Non è stato possibile analizzare la catena.</v>
+        <v>Catena</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B185" t="str">
-        <v>Controllo della catena…</v>
+        <v>Non è stato possibile analizzare la catena.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B186" t="str">
-        <v>La catena non si collega ({detail}).</v>
+        <v>Controllo della catena…</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>Il profilo {n} non si collega alla fase precedente ({detail}).</v>
+        <v>La catena non si collega ({detail}).</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B188" t="str">
-        <v>Correggi la catena prima di elaborare le immagini</v>
+        <v>Il profilo {n} non si collega alla fase precedente ({detail}).</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B189" t="str">
-        <v>Svuota</v>
+        <v>Correggi la catena prima di elaborare le immagini</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B190" t="str">
-        <v>Crea DeviceLink</v>
+        <v>Svuota</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B191" t="str">
-        <v>Nome del DeviceLink</v>
+        <v>Crea DeviceLink</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B192" t="str">
-        <v>Creazione…</v>
+        <v>Nome del DeviceLink</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B193" t="str">
-        <v>Creato «{name}» — aggiunto al pool e a questa scheda.</v>
+        <v>Creazione…</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B194" t="str">
-        <v>Trascina immagini {src} da convertire in {dst} — i risultati si scaricano, nulla viene memorizzato.</v>
+        <v>Creato «{name}» — aggiunto al pool e a questa scheda.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B195" t="str">
-        <v>Crea una catena per elaborare le immagini</v>
+        <v>Trascina immagini {src} da convertire in {dst} — i risultati si scaricano, nulla viene memorizzato.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B196" t="str">
-        <v>Questa catena non inizia e non termina in uno spazio colore per immagini</v>
+        <v>Crea una catena per elaborare le immagini</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B197" t="str">
-        <v>Immagine trasformata salvata.</v>
+        <v>Questa catena non inizia e non termina in uno spazio colore per immagini</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B198" t="str">
-        <v>Trascina un set di dati colore (CGATS/CSV/CxF/JSON)</v>
+        <v>Immagine trasformata salvata.</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B199" t="str">
-        <v>Impossibile leggere il file.</v>
+        <v>Trascina un set di dati colore (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B200" t="str">
-        <v>File di dati troppo grande.</v>
+        <v>Impossibile leggere il file.</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B201" t="str">
-        <v>Trasforma dati</v>
+        <v>File di dati troppo grande.</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B202" t="str">
-        <v>Trasformazione…</v>
+        <v>Trasforma dati</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B203" t="str">
-        <v>Preferisci</v>
+        <v>Trasformazione…</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B204" t="str">
-        <v>Osservatore</v>
+        <v>Preferisci</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B205" t="str">
-        <v>Illuminante</v>
+        <v>Osservatore</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B206" t="str">
-        <v>Condizione</v>
+        <v>Illuminante</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B207" t="str">
-        <v>Filtra {n} duplicato/i</v>
+        <v>Condizione</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B208" t="str">
-        <v>mediana</v>
+        <v>Filtra {n} duplicato/i</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B209" t="str">
-        <v>media</v>
+        <v>mediana</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B210" t="str">
-        <v>patch</v>
+        <v>media</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B211" t="str">
-        <v>{n} duplicati</v>
+        <v>patch</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B212" t="str">
-        <v>Risultato della trasformazione</v>
+        <v>{n} duplicati</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B213" t="str">
-        <v>{src} → {dst} · {n} patch</v>
+        <v>Risultato della trasformazione</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B214" t="str">
-        <v>Visualizzati i primi {shown} di {total} — Salva li scrive tutti.</v>
+        <v>{src} → {dst} · {n} patch</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B215" t="str">
-        <v>Salva con nome</v>
+        <v>Visualizzati i primi {shown} di {total} — Salva li scrive tutti.</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B216" t="str">
-        <v>Salva</v>
+        <v>Salva con nome</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B217" t="str">
-        <v>Inverti trasformazione</v>
+        <v>Salva</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B218" t="str">
-        <v>Inversione…</v>
+        <v>Inverti trasformazione</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B219" t="str">
-        <v>Inverti</v>
+        <v>Inversione…</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B220" t="str">
-        <v>ultima fase</v>
+        <v>Inverti</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B221" t="str">
-        <v>prima fase</v>
+        <v>ultima fase</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B222" t="str">
-        <v>Dati in {in} → ricerca {out}</v>
+        <v>prima fase</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B223" t="str">
-        <v>L'inversione richiede una catena di 2–3 profili</v>
+        <v>Dati in {in} → ricerca {out}</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B224" t="str">
-        <v>Il set di dati deve essere in {in}; la ricerca inversa produce {out} più un costo di invertibilità per patch.</v>
+        <v>L'inversione richiede una catena di 2–3 profili</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B225" t="str">
-        <v>Costo ΔE</v>
+        <v>Il set di dati deve essere in {in}; la ricerca inversa produce {out} più un costo di invertibilità per patch.</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B226" t="str">
-        <v>Questa immagine contiene un profilo ICC incorporato.</v>
+        <v>Costo ΔE</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B227" t="str">
-        <v>Estrai e aggiungi alla catena</v>
+        <v>Questa immagine contiene un profilo ICC incorporato.</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B228" t="str">
-        <v>Estrazione…</v>
+        <v>Estrai e aggiungi alla catena</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B229" t="str">
-        <v>Ignora</v>
+        <v>Estrazione…</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B230" t="str">
-        <v>Profilo incorporato estratto — aggiunto al pool e posizionato all'inizio della catena.</v>
+        <v>Ignora</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B231" t="str">
-        <v>Opzioni di output dell'immagine</v>
+        <v>Profilo incorporato estratto — aggiunto al pool e posizionato all'inizio della catena.</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B232" t="str">
-        <v>Codifica</v>
+        <v>Opzioni di output dell'immagine</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B233" t="str">
-        <v>Come l'origine</v>
+        <v>Codifica</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B234" t="str">
-        <v>8 bit</v>
+        <v>Come l'origine</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>16 bit</v>
+        <v>8 bit</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B236" t="str">
-        <v>Virgola mobile (32 bit)</v>
+        <v>16 bit</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B237" t="str">
-        <v>Compressione</v>
+        <v>Virgola mobile (32 bit)</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B238" t="str">
-        <v>Nessuna</v>
+        <v>Compressione</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B239" t="str">
-        <v>Planare</v>
+        <v>Nessuna</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B240" t="str">
-        <v>Interlacciato</v>
+        <v>Planare</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B241" t="str">
-        <v>Separato</v>
+        <v>Interlacciato</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B242" t="str">
-        <v>Interpolazione CMM</v>
+        <v>Separato</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B243" t="str">
-        <v>Tetraedrica</v>
+        <v>Interpolazione CMM</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B244" t="str">
-        <v>Lineare</v>
+        <v>Tetraedrica</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B245" t="str">
-        <v>Incorpora profilo ICC</v>
+        <v>Lineare</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B246" t="str">
-        <v>Codifica, compressione e disposizione planare determinano il TIFF salvato. L'output RGB/Gray resta PNG a meno che non sia impostata un'opzione esclusiva del TIFF (virgola mobile, LZW/ZIP, separato).</v>
+        <v>Incorpora profilo ICC</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B247" t="str">
-        <v>Assembla TIFF spettrale</v>
+        <v>Codifica, compressione e disposizione planare determinano il TIFF salvato. L'output RGB/Gray resta PNG a meno che non sia impostata un'opzione esclusiva del TIFF (virgola mobile, LZW/ZIP, separato).</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B248" t="str">
-        <v>Trascina immagini spettrali monocanale nell'ordine dei canali, quindi assemblale in un unico TIFF multicanale.</v>
+        <v>Assembla TIFF spettrale</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B249" t="str">
-        <v>Trascina qui le immagini spettrali (o clicca per selezionarle)</v>
+        <v>Trascina immagini spettrali monocanale nell'ordine dei canali, quindi assemblale in un unico TIFF multicanale.</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B250" t="str">
-        <v>can</v>
+        <v>Trascina qui le immagini spettrali (o clicca per selezionarle)</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B251" t="str">
-        <v>Assembla e salva</v>
+        <v>can</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B252" t="str">
-        <v>Assemblaggio…</v>
+        <v>Assembla e salva</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B253" t="str">
-        <v>Assemblati {n} canali.</v>
+        <v>Assemblaggio…</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B254" t="str">
-        <v>Nessuno di questi sembra un'immagine (TIFF, PNG o JPEG).</v>
+        <v>Assemblati {n} canali.</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B255" t="str">
-        <v>Annulla</v>
+        <v>Nessuno di questi sembra un'immagine (TIFF, PNG o JPEG).</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B256" t="str">
-        <v>{n} file non caricati</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B257" t="str">
-        <v>Questi file non sono profili ICC, quindi non sono stati aggiunti al pool:</v>
+        <v>{n} file non caricati</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B258" t="str">
-        <v>OK</v>
+        <v>Questi file non sono profili ICC, quindi non sono stati aggiunti al pool:</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B259" t="str">
-        <v>Trascina qui un profilo ICC</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B260" t="str">
-        <v>oppure</v>
+        <v>Trascina qui un profilo ICC</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B261" t="str">
-        <v>Scegli file</v>
+        <v>oppure</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B262" t="str">
-        <v>File .icc e .icm</v>
+        <v>Scegli file</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B263" t="str">
-        <v>Intestazione</v>
+        <v>File .icc e .icm</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B264" t="str">
-        <v>Tag</v>
+        <v>Intestazione</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B265" t="str">
-        <v>Convalida</v>
+        <v>Tag</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B266" t="str">
-        <v>Analisi</v>
+        <v>Convalida</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B267" t="str">
-        <v>Inchiostrazione dell’asse neutro</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B268" t="str">
-        <v>Colorante depositato lungo l’asse neutro (a*=b*=0) mentre la luminosità passa dal bianco (L*=100) al nero (L*=0).</v>
+        <v>Inchiostrazione dell’asse neutro</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B269" t="str">
-        <v>L’inchiostrazione dell’asse neutro è disponibile solo per i profili di output (stampante).</v>
+        <v>Colorante depositato lungo l’asse neutro (a*=b*=0) mentre la luminosità passa dal bianco (L*=100) al nero (L*=0).</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B270" t="str">
-        <v>Questo profilo non ha una tabella B2A (PCS→dispositivo) da campionare.</v>
+        <v>L’inchiostrazione dell’asse neutro è disponibile solo per i profili di output (stampante).</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B271" t="str">
-        <v>Intento di rendering</v>
+        <v>Questo profilo non ha una tabella B2A (PCS→dispositivo) da campionare.</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B272" t="str">
-        <v>% inchiostro</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>L* out (tone)</v>
+        <v>% ink</v>
       </c>
       <c r="B273" t="str">
-        <v>L* in uscita (tono)</v>
+        <v>% inchiostro</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Δa*b*</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B274" t="str">
-        <v>Δa*b*</v>
+        <v>L* in uscita (tono)</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B275" t="str">
-        <v>Colorimetria degli estremi</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B276" t="str">
-        <v>Gli estremi dell’intervallo di riproduzione del profilo: il bianco del supporto, il nero più scuro che stamperà, l’inchiostro che quel nero costa e il punto in cui ogni tinta raggiunge la massima saturazione.</v>
+        <v>Colorimetria degli estremi</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B277" t="str">
-        <v>Il punto di bianco è il colore con colorante nullo — il supporto nudo. Il punto di nero si ottiene facendo passare il nero PCS (L*=0, a*=b*=0) attraverso la tabella B2A selezionata per ricavare l’inchiostrazione che il profilo sceglie per il nero, e rileggendo poi tale inchiostrazione tramite A2B1. La copertura totale d’inchiostro (TAC) è la somma di tale inchiostrazione. La colorimetria assoluta mostra il colore proprio del supporto; quella relativa lo riferisce a un bianco perfetto.</v>
+        <v>Gli estremi dell’intervallo di riproduzione del profilo: il bianco del supporto, il nero più scuro che stamperà, l’inchiostro che quel nero costa e il punto in cui ogni tinta raggiunge la massima saturazione.</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Relative</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B278" t="str">
-        <v>Relativa</v>
+        <v>Il punto di bianco è il colore con colorante nullo — il supporto nudo. Il punto di nero si ottiene facendo passare il nero PCS (L*=0, a*=b*=0) attraverso la tabella B2A selezionata per ricavare l’inchiostrazione che il profilo sceglie per il nero, e rileggendo poi tale inchiostrazione tramite A2B1. La copertura totale d’inchiostro (TAC) è la somma di tale inchiostrazione. La colorimetria assoluta mostra il colore proprio del supporto; quella relativa lo riferisce a un bianco perfetto.</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Absolute</v>
+        <v>Relative</v>
       </c>
       <c r="B279" t="str">
-        <v>Assoluta</v>
+        <v>Relativa</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>White point</v>
+        <v>Absolute</v>
       </c>
       <c r="B280" t="str">
-        <v>Punto di bianco</v>
+        <v>Assoluta</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Black point</v>
+        <v>White point</v>
       </c>
       <c r="B281" t="str">
-        <v>Punto di nero</v>
+        <v>Punto di bianco</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Inking at black point</v>
+        <v>Black point</v>
       </c>
       <c r="B282" t="str">
-        <v>Inchiostrazione al punto di nero</v>
+        <v>Punto di nero</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>TAC</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B283" t="str">
-        <v>TAC</v>
+        <v>Inchiostrazione al punto di nero</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>TAC</v>
       </c>
       <c r="B284" t="str">
-        <v>Questo profilo non ha il tag del punto di bianco del supporto, quindi la colorimetria assoluta non è disponibile.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B285" t="str">
-        <v>La colorimetria degli estremi è disponibile solo per i profili di output (stampante) — presuppone che colorante nullo significhi supporto nudo.</v>
+        <v>Questo profilo non ha il tag del punto di bianco del supporto, quindi la colorimetria assoluta non è disponibile.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B286" t="str">
-        <v>Pieno e croma massima</v>
+        <v>La colorimetria degli estremi è disponibile solo per i profili di output (stampante) — presuppone che colorante nullo significhi supporto nudo.</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B287" t="str">
-        <v>Dove si colloca ogni vertice d’inchiostro e il punto più cromatico lungo il percorso. Misurato tramite A2B1, quindi queste righe non cambiano con l’intento di rendering sopra. In un profilo ben formato le due righe coincidono; se la croma massima arriva prima del pieno, l’inchiostro oltre quel punto si limita a scurire.</v>
+        <v>Pieno e croma massima</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Hue</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B288" t="str">
-        <v>Tinta</v>
+        <v>Dove si colloca ogni vertice d’inchiostro e il punto più cromatico lungo il percorso. Misurato tramite A2B1, quindi queste righe non cambiano con l’intento di rendering sopra. In un profilo ben formato le due righe coincidono; se la croma massima arriva prima del pieno, l’inchiostro oltre quel punto si limita a scurire.</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Full tone</v>
+        <v>Hue</v>
       </c>
       <c r="B289" t="str">
-        <v>Pieno</v>
+        <v>Tinta</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Max C*</v>
+        <v>Full tone</v>
       </c>
       <c r="B290" t="str">
-        <v>C* max</v>
+        <v>Pieno</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>At ink</v>
+        <v>Max C*</v>
       </c>
       <c r="B291" t="str">
-        <v>All’inchiostrazione</v>
+        <v>C* max</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>At ink</v>
       </c>
       <c r="B292" t="str">
-        <v>La croma massima viene raggiunta prima del pieno — oltre questo punto l’inchiostro si limita a scurire.</v>
+        <v>All’inchiostrazione</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B293" t="str">
-        <v>Uso dell’inchiostro nelle ombre</v>
+        <v>La croma massima viene raggiunta prima del pieno — oltre questo punto l’inchiostro si limita a scurire.</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B294" t="str">
-        <v>Quattro percorsi rettilinei sul piano a*b* a una luminosità costante e deliberatamente scura, passati attraverso la tabella B2A selezionata. Tutti i campioni condividono la stessa L*, perciò ogni scalino brusco o inversione di un colorante deriva unicamente dalla gestione di tinta e croma — la firma di un artefatto di mappatura del gamut nelle ombre.</v>
+        <v>Uso dell’inchiostro nelle ombre</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B295" t="str">
-        <v>L’uso dell’inchiostro nelle ombre è disponibile solo per i profili di output (stampante).</v>
+        <v>Quattro percorsi rettilinei sul piano a*b* a una luminosità costante e deliberatamente scura, passati attraverso la tabella B2A selezionata. Tutti i campioni condividono la stessa L*, perciò ogni scalino brusco o inversione di un colorante deriva unicamente dalla gestione di tinta e croma — la firma di un artefatto di mappatura del gamut nelle ombre.</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Constant L* plane</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B296" t="str">
-        <v>Piano a L* costante</v>
+        <v>L’uso dell’inchiostro nelle ombre è disponibile solo per i profili di output (stampante).</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>black-point compensated from</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B297" t="str">
-        <v>con compensazione del punto di nero da</v>
+        <v>Piano a L* costante</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Position along path</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B298" t="str">
-        <v>Posizione lungo il percorso</v>
+        <v>con compensazione del punto di nero da</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Path</v>
+        <v>Position along path</v>
       </c>
       <c r="B299" t="str">
-        <v>Percorso</v>
+        <v>Posizione lungo il percorso</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Primary-Inking Paths through Neutral</v>
+        <v>Path</v>
       </c>
       <c r="B300" t="str">
-        <v>Percorsi d’inchiostrazione primaria attraverso il neutro</v>
+        <v>Percorso</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B301" t="str">
-        <v>Tre percorsi nel gamut — ciano→rosso, magenta→verde, giallo→blu — ciascuno attraverso l’asse neutro alla chiarezza mediana dei suoi estremi, attraverso la tabella B2A selezionata. Ogni campione è nel gamut, quindi a differenza dei percorsi in ombra qualsiasi salto o inversione di un colorante è un difetto di regolarità della CLUT e non un artefatto di mappatura del gamut.</v>
+        <v>Percorsi d’inchiostrazione primaria attraverso il neutro</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Primary-inking paths are only available for output (printer) profiles.</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B302" t="str">
-        <v>I percorsi d’inchiostrazione primaria sono disponibili solo per i profili di output (stampante).</v>
+        <v>Tre percorsi nel gamut — ciano→rosso, magenta→verde, giallo→blu — ciascuno attraverso l’asse neutro alla chiarezza mediana dei suoi estremi, attraverso la tabella B2A selezionata. Ogni campione è nel gamut, quindi a differenza dei percorsi in ombra qualsiasi salto o inversione di un colorante è un difetto di regolarità della CLUT e non un artefatto di mappatura del gamut.</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Position along path (neutral at midpoint)</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B303" t="str">
-        <v>Posizione lungo il percorso (neutro al centro)</v>
+        <v>I percorsi d’inchiostrazione primaria sono disponibili solo per i profili di output (stampante).</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Black-point compensated for this intent.</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B304" t="str">
-        <v>Compensazione del punto nero applicata per questo intento.</v>
+        <v>Posizione lungo il percorso (neutro al centro)</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Ink Usage Statistics</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B305" t="str">
-        <v>Statistiche di utilizzo dell’inchiostro</v>
+        <v>Compensazione del punto nero applicata per questo intento.</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B306" t="str">
-        <v>Quanto di ogni colorante il profilo deposita, come somma e come quota del totale — la firma di consumo d’inchiostro della separazione.</v>
+        <v>Statistiche di utilizzo dell’inchiostro</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Ink usage statistics are only available for output (printer) profiles.</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B307" t="str">
-        <v>Le statistiche di utilizzo dell’inchiostro sono disponibili solo per i profili di output (stampante).</v>
+        <v>Quanto di ogni colorante il profilo deposita, come somma e come quota del totale — la firma di consumo d’inchiostro della separazione.</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Neutral axis</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B308" t="str">
-        <v>Asse neutro</v>
+        <v>Le statistiche di utilizzo dell’inchiostro sono disponibili solo per i profili di output (stampante).</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Mean coverage</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B309" t="str">
-        <v>Copertura media</v>
+        <v>Asse neutro</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Share of ink</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B310" t="str">
-        <v>Quota d’inchiostro</v>
+        <v>Copertura media</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
+        <v>Share of ink</v>
       </c>
       <c r="B311" t="str">
-        <v>La quota d’inchiostro è l’impronta della costruzione del neutro — la frazione di ogni colorante sul totale d’inchiostro depositato, indipendentemente dal numero di campioni.</v>
+        <v>Quota d’inchiostro</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>On &amp; in-gamut points</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B312" t="str">
-        <v>Punti nel gamut</v>
+        <v>La quota d’inchiostro è l’impronta della costruzione del neutro — la frazione di ogni colorante sul totale d’inchiostro depositato, indipendentemente dal numero di campioni.</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B313" t="str">
-        <v>L’utilizzo d’inchiostro su tutti i colori nel gamut richiede il confine del gamut lato B2A, non ancora implementato — in arrivo.</v>
+        <v>Punti nel gamut</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>No colorant data to summarize.</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B314" t="str">
-        <v>Nessun dato di colorante da riepilogare.</v>
+        <v>L’utilizzo d’inchiostro su tutti i colori nel gamut richiede il confine del gamut lato B2A, non ancora implementato — in arrivo.</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B315" t="str">
-        <v>Seleziona una tabella B2A (PCS→dispositivo) qui sotto per visualizzare anche un’immagine in scala di grigi della copertura d’inchiostro per ogni colorante.</v>
+        <v>Nessun dato di colorante da riepilogare.</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B316" t="str">
-        <v>Copertura d’inchiostro di ogni colorante sullo stesso reticolo (più scuro = più inchiostro).</v>
+        <v>Seleziona una tabella B2A (PCS→dispositivo) qui sotto per visualizzare anche un’immagine in scala di grigi della copertura d’inchiostro per ogni colorante.</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Cyan</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B317" t="str">
-        <v>Ciano</v>
+        <v>Copertura d’inchiostro di ogni colorante sullo stesso reticolo (più scuro = più inchiostro).</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Magenta</v>
+        <v>Cyan</v>
       </c>
       <c r="B318" t="str">
-        <v>Magenta</v>
+        <v>Ciano</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Yellow</v>
+        <v>Magenta</v>
       </c>
       <c r="B319" t="str">
-        <v>Giallo</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Red</v>
+        <v>Yellow</v>
       </c>
       <c r="B320" t="str">
-        <v>Rosso</v>
+        <v>Giallo</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Green</v>
+        <v>Red</v>
       </c>
       <c r="B321" t="str">
-        <v>Verde</v>
+        <v>Rosso</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Blue</v>
+        <v>Green</v>
       </c>
       <c r="B322" t="str">
-        <v>Blu</v>
+        <v>Verde</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Black</v>
+        <v>Blue</v>
       </c>
       <c r="B323" t="str">
-        <v>Nero</v>
+        <v>Blu</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Perceptual</v>
+        <v>Black</v>
       </c>
       <c r="B324" t="str">
-        <v>Percettivo</v>
+        <v>Nero</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B325" t="str">
-        <v>Colorimetrico relativo</v>
+        <v>Percettivo</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B326" t="str">
-        <v>Saturazione</v>
+        <v>Colorimetrico relativo</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B327" t="str">
-        <v>Colorimetrico assoluto</v>
+        <v>Saturazione</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B328" t="str">
-        <v>Statistiche del profilo</v>
+        <v>Colorimetrico assoluto</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B329" t="str">
-        <v>Metriche dell’intero profilo per intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e l’accuratezza del round-trip B2A — ΔE*ab di un percorso Lab → dispositivo → Lab attraverso il profilo.</v>
+        <v>Statistiche del profilo</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B330" t="str">
-        <v>Nessuna CLUT dispositivo↔PCS in questo profilo — le statistiche del profilo non si applicano (ad es. un profilo monitor matrice/TRC).</v>
+        <v>Metriche dell’intero profilo per intento di rendering: il volume del gamut racchiuso dalla trasformazione dispositivo→PCS (ΔE*ab³) e l’accuratezza del round-trip B2A — ΔE*ab di un percorso Lab → dispositivo → Lab attraverso il profilo.</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B331" t="str">
-        <v>Intento di rendering</v>
+        <v>Nessuna CLUT dispositivo↔PCS in questo profilo — le statistiche del profilo non si applicano (ad es. un profilo monitor matrice/TRC).</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B332" t="str">
-        <v>Volume del gamut (ΔE³)</v>
+        <v>Intento di rendering</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B333" t="str">
-        <v>ΔE round-trip</v>
+        <v>Volume del gamut (ΔE³)</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B334" t="str">
-        <v>Il confine del gamut è collassato o era in gran parte indefinito; questo volume di gamut non è affidabile.</v>
+        <v>ΔE round-trip</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B335" t="str">
-        <v>media</v>
+        <v>Il confine del gamut è collassato o era in gran parte indefinito; questo volume di gamut non è affidabile.</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B336" t="str">
-        <v>P90</v>
+        <v>media</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B337" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B338" t="str">
-        <v>Analisi in corso…</v>
+        <v>max</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B339" t="str">
-        <v>Analisi</v>
+        <v>Analisi in corso…</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B340" t="str">
-        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
+        <v>Analisi</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B341" t="str">
-        <v>Grafico</v>
+        <v>Analisi di qualità sull’intero profilo, derivate dalla trasformazione dispositivo→PCS.</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B342" t="str">
-        <v>Output grezzo</v>
+        <v>Grafico</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B343" t="str">
-        <v>XML</v>
+        <v>Output grezzo</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B344" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B345" t="str">
-        <v>Curve</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B346" t="str">
-        <v>Curve di ingresso</v>
+        <v>Curve</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B347" t="str">
-        <v>Curve di uscita</v>
+        <v>Curve di ingresso</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B348" t="str">
-        <v>Immagine CLUT</v>
+        <v>Curve di uscita</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B349" t="str">
-        <v>Immagine gamut</v>
+        <v>Immagine CLUT</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B350" t="str">
-        <v>Cromaticità</v>
+        <v>Immagine gamut</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B351" t="str">
-        <v>Grafico a dispersione</v>
+        <v>Cromaticità</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B352" t="str">
-        <v>Curva di risposta tonale</v>
+        <v>Grafico a dispersione</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B353" t="str">
-        <v>Tabella della curva</v>
+        <v>Curva di risposta tonale</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B354" t="str">
-        <v>Tabelle</v>
+        <v>Tabella della curva</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B355" t="str">
-        <v>Dati</v>
+        <v>Tabelle</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B356" t="str">
-        <v>Valuta</v>
+        <v>Dati</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B357" t="str">
-        <v>Caricamento…</v>
+        <v>Valuta</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B358" t="str">
-        <v>Ingresso</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B359" t="str">
-        <v>Uscita</v>
+        <v>Ingresso</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B360" t="str">
-        <v>Virgola mobile</v>
+        <v>Uscita</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B361" t="str">
-        <v>Punto griglia</v>
+        <v>Virgola mobile</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B362" t="str">
-        <v>Normalizzato</v>
+        <v>Punto griglia</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B363" t="str">
-        <v>Leggibile</v>
+        <v>Normalizzato</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B364" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Leggibile</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B365" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B366" t="str">
-        <v>Nessuna griglia CLUT</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B367" t="str">
-        <v>Caricamento…</v>
+        <v>Nessuna griglia CLUT</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B368" t="str">
-        <v>Neutro = nel gamut · rosso = fuori gamut</v>
+        <v>Caricamento…</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B369" t="str">
-        <v>URL del profilo non valido:</v>
+        <v>Neutro = nel gamut · rosso = fuori gamut</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B370" t="str">
-        <v>Impossibile recuperare il profilo da</v>
+        <v>URL del profilo non valido:</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B371" t="str">
-        <v>Caricare un profilo ICC da questo sito esterno?</v>
+        <v>Impossibile recuperare il profilo da</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B372" t="str">
-        <v>Caricamento del rapporto Profile Assessment WG…</v>
+        <v>Caricare un profilo ICC da questo sito esterno?</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B373" t="str">
-        <v>Esecuzione dei controlli Profile Assessment WG…</v>
+        <v>Caricamento del rapporto Profile Assessment WG…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B374" t="str">
-        <v>Rapporto Profile Assessment WG</v>
+        <v>Esecuzione dei controlli Profile Assessment WG…</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B375" t="str">
-        <v>Sicurezza</v>
+        <v>Rapporto Profile Assessment WG</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B376" t="str">
-        <v>Conformità</v>
+        <v>Sicurezza</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B377" t="str">
-        <v>Qualità</v>
+        <v>Conformità</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B378" t="str">
-        <v>RAPPORTO</v>
+        <v>Qualità</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B379" t="str">
-        <v>NON SUPERATO</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B380" t="str">
-        <v>controlli</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B381" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B382" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B383" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B384" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B385" t="str">
-        <v>Iscriviti</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B386" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B387" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B388" t="str">
-        <v>Chiudi</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B389" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B390" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B391" t="str">
-        <v>tu@esempio.com</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B392" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B393" t="str">
-        <v>(opzionale)</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B394" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B395" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B396" t="str">
-        <v>Annulla</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B397" t="str">
-        <v>Iscriviti</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B398" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B399" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B400" t="str">
-        <v>Chiudi</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B401" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B402" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B403" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B404" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B405" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B406" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B407" t="str">
-        <v>Errore:</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B408" t="str">
-        <v>Converti in XML</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B409" t="str">
-        <v>Converti in JSON</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B410" t="str">
-        <v>Converti in ICC</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B411" t="str">
-        <v>Conversione in XML…</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B412" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B413" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B414" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B415" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B416" t="str">
-        <v>ID profilo</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B417" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B418" t="str">
-        <v>Nome tag</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B419" t="str">
-        <v>ID</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B420" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B421" t="str">
-        <v>Dimensione</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B422" t="str">
-        <v>Riempimento</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B423" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B424" t="str">
-        <v>Tipo</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B425" t="str">
-        <v>Array di {type}</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B426" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B427" t="str">
-        <v>byte</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B428" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B429" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B430" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B431" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B432" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B433" t="str">
-        <v>Il profilo è valido</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B434" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B435" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B436" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B437" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B438" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B439" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B440" t="str">
-        <v>Valido</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B441" t="str">
-        <v>Avviso</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B442" t="str">
-        <v>Errore</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B443" t="str">
-        <v>Sconosciuto</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B444" t="str">
-        <v>Superato</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B445" t="str">
-        <v>Non superato</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B446" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B447" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B448" t="str">
-        <v>Attivato da</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B449" t="str">
-        <v>Campo</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B450" t="str">
-        <v>Valore attuale</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B451" t="str">
-        <v>Richiesto: 0</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B452" t="str">
-        <v>Atteso: {value}</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B453" t="str">
-        <v>Non valido</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B454" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B455" t="str">
-        <v>Chiudi</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B456" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B457" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Caricamento editor XML…</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B458" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Caricamento editor JSON…</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B459" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B460" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B461" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>● modifiche XML non salvate</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B462" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● modifiche JSON non salvate</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B463" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B464" t="str">
-        <v>rientro</v>
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B465" t="str">
-        <v>ordina chiavi</v>
+        <v>rientro</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B466" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B466" t="str">
+      <c r="B467" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B466"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B467"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-It.xlsx
+++ b/translations/Eng-It.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B706"/>
+  <dimension ref="A1:B707"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3475,26 +3475,26 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>HDR Profile in the chain</v>
+        <v>HDR ColorSpace Profile in the chain</v>
       </c>
       <c r="B384" t="str">
-        <v>Profilo HDR nella catena</v>
+        <v>Profilo HDR ColorSpace nella catena</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Transforms through an HDR Profile use its AToB0Tag — the baked SDR rendering required by clause 8.10.6 — because clause 8.10.1 leaves it no TRC tags. The result is that fallback, not HDR behaviour.</v>
+        <v>Transforms through an HDR ColorSpace Profile use its AToB0Tag — the baked SDR rendering required by clause 8.7.1.5 — because a ColorSpace profile has no TRC tags. The result is that fallback, not HDR behaviour.</v>
       </c>
       <c r="B385" t="str">
-        <v>Le trasformazioni attraverso un profilo HDR usano il suo AToB0Tag — il rendering SDR fissato richiesto dalla clausola 8.10.6 — perché la clausola 8.10.1 non gli lascia tag TRC. Il risultato è quel ripiego, non comportamento HDR.</v>
+        <v>Le trasformazioni attraverso un profilo HDR ColorSpace usano il suo AToB0Tag — il rendering SDR fissato richiesto dalla clausola 8.7.1.5 — perché un profilo ColorSpace non ha tag TRC. Il risultato è quel ripiego, non comportamento HDR.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>These are HDR Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.10.6 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
+        <v>These are HDR ColorSpace Profiles, which carry no TRC tags, so the gamut is built from the AToB0Tag — the baked SDR rendering clause 8.7.1.5 requires for consumers without HDR processing. It is not the profile’s HDR gamut, which cannot be drawn in a bounded PCS.</v>
       </c>
       <c r="B386" t="str">
-        <v>Sono profili HDR, privi di tag TRC: il gamut è quindi costruito dall’AToB0Tag, il rendering SDR fissato che la clausola 8.10.6 richiede per i consumatori senza elaborazione HDR. Non è il gamut HDR del profilo, che non può essere tracciato in un PCS limitato.</v>
+        <v>Sono profili HDR, privi di tag TRC: il gamut è quindi costruito dall’AToB0Tag, il rendering SDR fissato che la clausola 8.7.1.5 richiede per i consumatori senza elaborazione HDR. Non è il gamut HDR del profilo, che non può essere tracciato in un PCS limitato.</v>
       </c>
     </row>
     <row r="387">
@@ -4651,10 +4651,10 @@
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.10.2 a)</v>
+        <v>File 1.0 = 1 cd/m² (ICC.1 clause 8.7.1.2 a)</v>
       </c>
       <c r="B531" t="str">
-        <v>File 1,0 = 1 cd/m² (ICC.1 clausola 8.10.2 a)</v>
+        <v>File 1,0 = 1 cd/m² (ICC.1 clausola 8.7.1.2 a)</v>
       </c>
     </row>
     <row r="532">
@@ -4715,10 +4715,10 @@
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>Auto (clause 8.10.3 ranking)</v>
+        <v>Auto (clause 8.7.1.3 ranking)</v>
       </c>
       <c r="B539" t="str">
-        <v>Auto (classifica della clausola 8.10.3)</v>
+        <v>Auto (classifica della clausola 8.7.1.3)</v>
       </c>
     </row>
     <row r="540">
@@ -4779,10 +4779,10 @@
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>HDR Profiles</v>
+        <v>HDR ColorSpace Profiles</v>
       </c>
       <c r="B547" t="str">
-        <v>Profili HDR</v>
+        <v>Profili HDR ColorSpace</v>
       </c>
     </row>
     <row r="548">
@@ -4803,1263 +4803,1271 @@
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>HDR Profiles — Linear transfer</v>
+        <v>HDR ColorSpace Profiles — Linear transfer</v>
       </c>
       <c r="B550" t="str">
-        <v>Profili HDR — trasferimento lineare</v>
+        <v>Profili HDR ColorSpace — trasferimento lineare</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>HDR Profiles — PQ / HLG transfer</v>
+        <v>HDR ColorSpace Profiles — PQ / HLG transfer</v>
       </c>
       <c r="B551" t="str">
-        <v>Profili HDR — trasferimento PQ / HLG</v>
+        <v>Profili HDR ColorSpace — trasferimento PQ / HLG</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>{format} holds linear light, so only HDR Profiles with a Linear transfer can be assigned.</v>
+        <v>{format} holds linear light, so only HDR ColorSpace Profiles with a Linear transfer can be assigned.</v>
       </c>
       <c r="B552" t="str">
-        <v>{format} contiene luce lineare, quindi si possono assegnare solo profili HDR con trasferimento lineare.</v>
+        <v>{format} contiene luce lineare, quindi si possono assegnare solo profili HDR ColorSpace con trasferimento lineare.</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>{n} PQ/HLG HDR Profile(s) in the pool are not offered — the Profiles pane lists them under HDR Profiles › Non-linear transfer.</v>
+        <v>{n} PQ/HLG HDR ColorSpace Profile(s) in the pool are not offered — the Profiles pane lists them under HDR ColorSpace Profiles › Non-linear transfer.</v>
       </c>
       <c r="B553" t="str">
-        <v>{n} profilo/i HDR PQ/HLG nel pool non sono proposti — il pannello Profili li elenca sotto Profili HDR › Trasferimento non lineare.</v>
+        <v>{n} profilo/i HDR PQ/HLG nel pool non sono proposti — il pannello Profili li elenca sotto Profili HDR ColorSpace › Trasferimento non lineare.</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>There is no Linear-transfer HDR Profile in the pool yet; the Profiles pane groups HDR Profiles by transfer.</v>
+        <v>There is no Linear-transfer HDR ColorSpace Profile in the pool yet; the Profiles pane groups HDR ColorSpace Profiles by transfer.</v>
       </c>
       <c r="B554" t="str">
-        <v>Nel pool non c’è ancora un profilo HDR con trasferimento lineare; il pannello Profili raggruppa i profili HDR per trasferimento.</v>
+        <v>Nel pool non c’è ancora un profilo HDR ColorSpace con trasferimento lineare; il pannello Profili raggruppa i profili HDR ColorSpace per trasferimento.</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.10.3).</v>
+        <v>Unspecified primaries: no HDR path in this build</v>
       </c>
       <c r="B555" t="str">
-        <v>IccProfLib non applica questa curva di guadagno: {why}. Un CMM passa al descrittore di tone mapping successivo (clausola 8.10.3).</v>
+        <v>Primari non specificati: nessun percorso HDR in questa build</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>Display headroom</v>
+        <v>IccProfLib declines to apply this gain curve: {why}. A CMM falls back to the next tone-mapping descriptor (clause 8.7.1.3).</v>
       </c>
       <c r="B556" t="str">
-        <v>Margine del display</v>
+        <v>IccProfLib non applica questa curva di guadagno: {why}. Un CMM passa al descrittore di tone mapping successivo (clausola 8.7.1.3).</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>{n} stops (≈{r}× reference white)</v>
+        <v>Display headroom</v>
       </c>
       <c r="B557" t="str">
-        <v>{n} stop (≈{r}× il bianco di riferimento)</v>
+        <v>Margine del display</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>Baseline</v>
+        <v>{n} stops (≈{r}× reference white)</v>
       </c>
       <c r="B558" t="str">
-        <v>Base</v>
+        <v>{n} stop (≈{r}× il bianco di riferimento)</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>Preview through the colour engine</v>
+        <v>Baseline</v>
       </c>
       <c r="B559" t="str">
-        <v>Anteprima tramite il motore colore</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>As authored (baseline {h} stops, no gain)</v>
+        <v>Preview through the colour engine</v>
       </c>
       <c r="B560" t="str">
-        <v>Come creata (base {h} stop, senza guadagno)</v>
+        <v>Anteprima tramite il motore colore</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>Tone-mapped for {h} stops</v>
+        <v>As authored (baseline {h} stops, no gain)</v>
       </c>
       <c r="B561" t="str">
-        <v>Mappata per {h} stop</v>
+        <v>Come creata (base {h} stop, senza guadagno)</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
+        <v>Tone-mapped for {h} stops</v>
       </c>
       <c r="B562" t="str">
-        <v>Gli stessi pixel di prova (segnale {transfer} crescente da sinistra a destra: grigio, poi R, G, B, Y, C, M) attraverso la trasformazione HDR di IccProfLib. Entrambe le strisce sono limitate a {r}× il bianco di riferimento HDR, come le mostrerebbe un display con {h} stop di headroom: dove la striscia superiore satura piatta, la curva di guadagno attenua le alte luci.</v>
+        <v>Mappata per {h} stop</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>reference white</v>
+        <v>The same test pixels ({transfer} signal rising left to right: grey, then R, G, B, Y, C, M) through IccProfLib’s HDR transform. Both strips are capped at {r}× HDR reference white, as a display with {h} stops of headroom would show them: where the top strip clips flat, the gain curve rolls highlights off.</v>
       </c>
       <c r="B563" t="str">
-        <v>bianco di riferimento</v>
+        <v>Gli stessi pixel di prova (segnale {transfer} crescente da sinistra a destra: grigio, poi R, G, B, Y, C, M) attraverso la trasformazione HDR di IccProfLib. Entrambe le strisce sono limitate a {r}× il bianco di riferimento HDR, come le mostrerebbe un display con {h} stop di headroom: dove la striscia superiore satura piatta, la curva di guadagno attenua le alte luci.</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>display peak</v>
+        <v>reference white</v>
       </c>
       <c r="B564" t="str">
-        <v>picco del display</v>
+        <v>bianco di riferimento</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>Preview unavailable: {why}</v>
+        <v>display peak</v>
       </c>
       <c r="B565" t="str">
-        <v>Anteprima non disponibile: {why}</v>
+        <v>picco del display</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>the colour engine did not take the HDR path for this profile</v>
+        <v>Preview unavailable: {why}</v>
       </c>
       <c r="B566" t="str">
-        <v>il motore colore non ha seguito il percorso HDR per questo profilo</v>
+        <v>Anteprima non disponibile: {why}</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>Gain across every headroom</v>
+        <v>the colour engine did not take the HDR path for this profile</v>
       </c>
       <c r="B567" t="str">
-        <v>Guadagno a ogni headroom</v>
+        <v>il motore colore non ha seguito il percorso HDR per questo profilo</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
+        <v>Gain across every headroom</v>
       </c>
       <c r="B568" t="str">
-        <v>Guadagno applicato a un ingresso grigio a ogni headroom del display: il blu comprime, il rosso espande, il bianco lo lascia invariato. Le linee punteggiate indicano le curve del tag, quella continua la base, quella ambra il cursore; la diagonale tratteggiata è dove l’ingresso raggiunge il picco del display. Fai clic per spostare il cursore.</v>
+        <v>Guadagno a ogni headroom</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>Input (stops relative to HDR reference white)</v>
+        <v>Gain applied to a grey input at each display headroom: blue compresses, red expands, white leaves it unchanged. Dotted lines mark the curves in the tag, the solid line the baseline, the amber line the slider; the dashed diagonal is where the input reaches the display peak. Click to move the slider.</v>
       </c>
       <c r="B569" t="str">
-        <v>Ingresso (stop rispetto al bianco di riferimento HDR)</v>
+        <v>Guadagno applicato a un ingresso grigio a ogni headroom del display: il blu comprime, il rosso espande, il bianco lo lascia invariato. Le linee punteggiate indicano le curve del tag, quella continua la base, quella ambra il cursore; la diagonale tratteggiata è dove l’ingresso raggiunge il picco del display. Fai clic per spostare il cursore.</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>Display headroom (stops)</v>
+        <v>Input (stops relative to HDR reference white)</v>
       </c>
       <c r="B570" t="str">
-        <v>Headroom del display (stop)</v>
+        <v>Ingresso (stop rispetto al bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>Gain (stops)</v>
+        <v>Display headroom (stops)</v>
       </c>
       <c r="B571" t="str">
-        <v>Guadagno (stop)</v>
+        <v>Headroom del display (stop)</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>Curve in the tag</v>
+        <v>Gain (stops)</v>
       </c>
       <c r="B572" t="str">
-        <v>Curva nel tag</v>
+        <v>Guadagno (stop)</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>Baseline</v>
+        <v>Curve in the tag</v>
       </c>
       <c r="B573" t="str">
-        <v>Base</v>
+        <v>Curva nel tag</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>Slider</v>
+        <v>Baseline</v>
       </c>
       <c r="B574" t="str">
-        <v>Cursore</v>
+        <v>Base</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>Input = display peak</v>
+        <v>Slider</v>
       </c>
       <c r="B575" t="str">
-        <v>Ingresso = picco del display</v>
+        <v>Cursore</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>Grey tone curves by headroom</v>
+        <v>Input = display peak</v>
       </c>
       <c r="B576" t="str">
-        <v>Curve tonali del grigio per headroom</v>
+        <v>Ingresso = picco del display</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
+        <v>Grey tone curves by headroom</v>
       </c>
       <c r="B577" t="str">
-        <v>La curva tonale del grigio a ogni headroom memorizzato nel tag, colorata dal basso (blu) all’alto (rosso), con la curva del cursore in ambra. Entrambi gli assi sono in stop, quindi la diagonale indica nessuna modifica.</v>
+        <v>Curve tonali del grigio per headroom</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>Output (stops relative to HDR reference white)</v>
+        <v>The grey tone curve at each headroom the tag stores, coloured from low (blue) to high (red), with the slider’s curve in amber. Both axes are in stops, so the diagonal is no change.</v>
       </c>
       <c r="B578" t="str">
-        <v>Uscita (stop rispetto al bianco di riferimento HDR)</v>
+        <v>La curva tonale del grigio a ogni headroom memorizzato nel tag, colorata dal basso (blu) all’alto (rosso), con la curva del cursore in ambra. Entrambi gli assi sono in stop, quindi la diagonale indica nessuna modifica.</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>{h} stops</v>
+        <v>Output (stops relative to HDR reference white)</v>
       </c>
       <c r="B579" t="str">
-        <v>{h} stop</v>
+        <v>Uscita (stop rispetto al bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>{h} stops (baseline)</v>
+        <v>{h} stops</v>
       </c>
       <c r="B580" t="str">
-        <v>{h} stop (base)</v>
+        <v>{h} stop</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>At {h} stops (slider)</v>
+        <v>{h} stops (baseline)</v>
       </c>
       <c r="B581" t="str">
-        <v>A {h} stop (cursore)</v>
+        <v>{h} stop (base)</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
+        <v>At {h} stops (slider)</v>
       </c>
       <c r="B582" t="str">
-        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
+        <v>A {h} stop (cursore)</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
+        <v>Curves in the tag, by headroom: {list} stops. Baseline {b} stops, HDR reference white {w} cd/m².</v>
       </c>
       <c r="B583" t="str">
-        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
+        <v>Curve nel tag, per margine: {list} stop. Base {b} stop, bianco di riferimento HDR {w} cd/m².</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
+        <v>This headroom is outside the range of curves in the tag, so the nearest curve is used unchanged — the library does not extrapolate beyond them.</v>
       </c>
       <c r="B584" t="str">
-        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
+        <v>Questo margine è fuori dall’intervallo delle curve del tag; la curva più vicina è usata invariata — la libreria non estrapola oltre.</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
+        <v>Some slopes are derived (PCHIP), not stored in the tag. That derivation reconstructs a SMPTE clause, so treat those curves’ shape as provisional.</v>
       </c>
       <c r="B585" t="str">
-        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
+        <v>Alcune pendenze sono derivate (PCHIP), non memorizzate nel tag. Questa derivazione ricostruisce una clausola SMPTE, quindi considera provvisoria la forma di quelle curve.</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
+        <v>The tag asks for reference-white tone mapping, so its curves are constructed by the library rather than read from the file (a committee-draft construction).</v>
       </c>
       <c r="B586" t="str">
-        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
+        <v>Il tag richiede il tone mapping sul bianco di riferimento, quindi le sue curve sono costruite dalla libreria anziché lette dal file (una costruzione da una bozza di comitato).</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
+        <v>No alternate images: the tag asks for no tone mapping, only a clamp to the display’s colour volume.</v>
       </c>
       <c r="B587" t="str">
-        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
+        <v>Nessuna immagine alternativa: il tag non richiede tone mapping, solo un limite al volume colore del display.</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>Curve at {h} stops (no gain)</v>
+        <v>The two curves blended at this headroom mix colour channels differently, so there is no single gain curve to draw. The tone curve below is still exact.</v>
       </c>
       <c r="B588" t="str">
-        <v>Curva a {h} stop (nessun guadagno)</v>
+        <v>Le due curve miscelate a questo margine combinano i canali in modo diverso, quindi non esiste un’unica curva di guadagno. La curva tonale sotto resta esatta.</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>Curve at {h} stops</v>
+        <v>Curve at {h} stops (no gain)</v>
       </c>
       <c r="B589" t="str">
-        <v>Curva a {h} stop</v>
+        <v>Curva a {h} stop (nessun guadagno)</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>Applied at {h} stops</v>
+        <v>Curve at {h} stops</v>
       </c>
       <c r="B590" t="str">
-        <v>Applicato a {h} stop</v>
+        <v>Curva a {h} stop</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>Gain applied at this headroom</v>
+        <v>Applied at {h} stops</v>
       </c>
       <c r="B591" t="str">
-        <v>Guadagno applicato a questo margine</v>
+        <v>Applicato a {h} stop</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
+        <v>Gain applied at this headroom</v>
       </c>
       <c r="B592" t="str">
-        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
+        <v>Guadagno applicato a questo margine</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>Gain (log2 stops)</v>
+        <v>Mixed input (linear, 1.0 = HDR reference white)</v>
       </c>
       <c r="B593" t="str">
-        <v>Guadagno (stop log2)</v>
+        <v>Ingresso miscelato (lineare, 1,0 = bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>Grey tone curve at this headroom</v>
+        <v>Gain (log2 stops)</v>
       </c>
       <c r="B594" t="str">
-        <v>Curva tonale dei grigi a questo margine</v>
+        <v>Guadagno (stop log2)</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>Input (× HDR reference white)</v>
+        <v>Grey tone curve at this headroom</v>
       </c>
       <c r="B595" t="str">
-        <v>Ingresso (× bianco di riferimento HDR)</v>
+        <v>Curva tonale dei grigi a questo margine</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>Output (× HDR reference white)</v>
+        <v>Input (× HDR reference white)</v>
       </c>
       <c r="B596" t="str">
-        <v>Uscita (× bianco di riferimento HDR)</v>
+        <v>Ingresso (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>No change</v>
+        <v>Output (× HDR reference white)</v>
       </c>
       <c r="B597" t="str">
-        <v>Nessuna modifica</v>
+        <v>Uscita (× bianco di riferimento HDR)</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>Display peak at {h} stops</v>
+        <v>No change</v>
       </c>
       <c r="B598" t="str">
-        <v>Picco del display a {h} stop</v>
+        <v>Nessuna modifica</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>Output at {h} stops</v>
+        <v>Display peak at {h} stops</v>
       </c>
       <c r="B599" t="str">
-        <v>Uscita a {h} stop</v>
+        <v>Picco del display a {h} stop</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
+        <v>Output at {h} stops</v>
       </c>
       <c r="B600" t="str">
-        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
+        <v>Uscita a {h} stop</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>Identify displays</v>
+        <v>HDR, gamut and pixel ratio refresh when the window moves to a screen where they differ.</v>
       </c>
       <c r="B601" t="str">
-        <v>Identifica i display</v>
+        <v>HDR, gamut e rapporto pixel si aggiornano quando la finestra passa a uno schermo dove differiscono.</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
+        <v>Identify displays</v>
       </c>
       <c r="B602" t="str">
-        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
+        <v>Identifica i display</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>Tracking which monitor this window is on.</v>
+        <v>Asks permission to see which monitor this window is on, so the panel also refreshes when two screens look alike, and shows HDR headroom where the browser exposes it.</v>
       </c>
       <c r="B603" t="str">
-        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
+        <v>Chiede il permesso di vedere su quale monitor si trova questa finestra, così il pannello si aggiorna anche tra schermi simili e mostra il margine HDR dove il browser lo espone.</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
+        <v>Tracking which monitor this window is on.</v>
       </c>
       <c r="B604" t="str">
-        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
+        <v>Rilevamento del monitor su cui si trova questa finestra.</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
+        <v>Permission to identify displays was refused. It can be changed in this site’s settings.</v>
       </c>
       <c r="B605" t="str">
-        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
+        <v>Il permesso di identificare i display è stato negato. Si può modificare nelle impostazioni di questo sito.</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>Could not identify displays.</v>
+        <v>This browser cannot identify displays; only the automatic refresh above applies.</v>
       </c>
       <c r="B606" t="str">
-        <v>Impossibile identificare i display.</v>
+        <v>Questo browser non può identificare i display; vale solo l’aggiornamento automatico sopra.</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>Display events</v>
+        <v>Could not identify displays.</v>
       </c>
       <c r="B607" t="str">
-        <v>Eventi del display</v>
+        <v>Impossibile identificare i display.</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>No events yet. Drag the window to another monitor.</v>
+        <v>Display events</v>
       </c>
       <c r="B608" t="str">
-        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
+        <v>Eventi del display</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>Colour primaries</v>
+        <v>No events yet. Drag the window to another monitor.</v>
       </c>
       <c r="B609" t="str">
-        <v>Primari di colore</v>
+        <v>Ancora nessun evento. Trascina la finestra su un altro monitor.</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>Transfer characteristics</v>
+        <v>Colour primaries</v>
       </c>
       <c r="B610" t="str">
-        <v>Caratteristiche di trasferimento</v>
+        <v>Primari di colore</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>Matrix coefficients</v>
+        <v>Transfer characteristics</v>
       </c>
       <c r="B611" t="str">
-        <v>Coefficienti di matrice</v>
+        <v>Caratteristiche di trasferimento</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>Video full-range flag</v>
+        <v>Matrix coefficients</v>
       </c>
       <c r="B612" t="str">
-        <v>Flag intervallo video completo</v>
+        <v>Coefficienti di matrice</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>Full range</v>
+        <v>Video full-range flag</v>
       </c>
       <c r="B613" t="str">
-        <v>Intervallo completo</v>
+        <v>Flag intervallo video completo</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>Narrow range</v>
+        <v>Full range</v>
       </c>
       <c r="B614" t="str">
-        <v>Intervallo ridotto</v>
+        <v>Intervallo completo</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>not assigned by ITU-T H.273</v>
+        <v>Narrow range</v>
       </c>
       <c r="B615" t="str">
-        <v>non assegnato da ITU-T H.273</v>
+        <v>Intervallo ridotto</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
+        <v>not assigned by ITU-T H.273</v>
       </c>
       <c r="B616" t="str">
-        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
+        <v>non assegnato da ITU-T H.273</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>The four reserved bytes of this tag are not all zero.</v>
+        <v>Colour primaries 2 (Unspecified) defers the primaries to the profile itself — they are taken from the colorant tags rather than from this tag.</v>
       </c>
       <c r="B617" t="str">
-        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
+        <v>I primari 2 (Non specificato) rimandano al profilo stesso: i primari provengono dai tag dei coloranti e non da questo tag.</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>REPORT</v>
+        <v>The four reserved bytes of this tag are not all zero.</v>
       </c>
       <c r="B618" t="str">
-        <v>RAPPORTO</v>
+        <v>I quattro byte riservati di questo tag non sono tutti zero.</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B619" t="str">
-        <v>NON SUPERATO</v>
+        <v>RAPPORTO</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B620" t="str">
-        <v>controlli</v>
+        <v>NON SUPERATO</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B621" t="str">
-        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
+        <v>controlli</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B622" t="str">
-        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
+        <v>Generato da iccPawgReport (iccDEV) · checklist dell’ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B623" t="str">
-        <v>Strumento per profili ICC</v>
+        <v>Strumento per profili ICC · realizzato con IccProfLib</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B624" t="str">
-        <v>Realizzato con {lib}</v>
+        <v>Strumento per profili ICC</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B625" t="str">
-        <v>Iscriviti</v>
+        <v>Realizzato con {lib}</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B626" t="str">
-        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B627" t="str">
-        <v>Ricevi notifiche sulle nuove versioni</v>
+        <v>Ricevi notifiche sulle nuove versioni di profiletool</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B628" t="str">
-        <v>Chiudi</v>
+        <v>Ricevi notifiche sulle nuove versioni</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B629" t="str">
-        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B630" t="str">
-        <v>Indirizzo e-mail</v>
+        <v>Ti invieremo un’e-mail quando esce una nuova versione maggiore o minore di profiletool. Le versioni patch sono escluse. Il tuo indirizzo viene verificato manualmente prima di essere aggiunto.</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B631" t="str">
-        <v>tu@esempio.com</v>
+        <v>Indirizzo e-mail</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B632" t="str">
-        <v>Come utilizzerai profiletool?</v>
+        <v>tu@esempio.com</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B633" t="str">
-        <v>(opzionale)</v>
+        <v>Come utilizzerai profiletool?</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B634" t="str">
-        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
+        <v>(opzionale)</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B635" t="str">
-        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
+        <v>p. es. valutare profili ICC per la calibrazione di stampa</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B636" t="str">
-        <v>Annulla</v>
+        <v>Accetto di ricevere e-mail sulle versioni di profiletool. Posso annullare l’iscrizione in qualsiasi momento.</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B637" t="str">
-        <v>Iscriviti</v>
+        <v>Annulla</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B638" t="str">
-        <v>Grazie — ti ricontatteremo.</v>
+        <v>Iscriviti</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B639" t="str">
-        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
+        <v>Grazie — ti ricontatteremo.</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B640" t="str">
-        <v>Chiudi</v>
+        <v>Una volta approvato, riceverai un’e-mail di benvenuto. In seguito, ti contatteremo solo quando uscirà una nuova versione di profiletool.</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B641" t="str">
-        <v>Informativa sulla privacy</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B642" t="str">
-        <v>Inserisci un indirizzo e-mail valido.</v>
+        <v>Informativa sulla privacy</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B643" t="str">
-        <v>Troppe richieste. Riprova più tardi.</v>
+        <v>Inserisci un indirizzo e-mail valido.</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B644" t="str">
-        <v>Controlla il modulo e riprova.</v>
+        <v>Troppe richieste. Riprova più tardi.</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B645" t="str">
-        <v>Impossibile inviare la richiesta. Riprova.</v>
+        <v>Controlla il modulo e riprova.</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B646" t="str">
-        <v>Errore di rete. Riprova.</v>
+        <v>Impossibile inviare la richiesta. Riprova.</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B647" t="str">
-        <v>Errore:</v>
+        <v>Errore di rete. Riprova.</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B648" t="str">
-        <v>Converti in XML</v>
+        <v>Errore:</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B649" t="str">
-        <v>Converti in JSON</v>
+        <v>Converti in XML</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B650" t="str">
-        <v>Converti in ICC</v>
+        <v>Converti in JSON</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B651" t="str">
-        <v>Conversione in XML…</v>
+        <v>Converti in ICC</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B652" t="str">
-        <v>Conversione in JSON…</v>
+        <v>Conversione in XML…</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B653" t="str">
-        <v>Conversione in ICC…</v>
+        <v>Conversione in JSON…</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B654" t="str">
-        <v>Carica profilo ICC</v>
+        <v>Conversione in ICC…</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B655" t="str">
-        <v>Area di rilascio per i file di profilo ICC</v>
+        <v>Carica profilo ICC</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B656" t="str">
-        <v>ID profilo</v>
+        <v>Area di rilascio per i file di profilo ICC</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B657" t="str">
-        <v>Nessun tag trovato.</v>
+        <v>ID profilo</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B658" t="str">
-        <v>Nome tag</v>
+        <v>Nessun tag trovato.</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B659" t="str">
-        <v>ID</v>
+        <v>Nome tag</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B660" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B661" t="str">
-        <v>Dimensione</v>
+        <v>Offset</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B662" t="str">
-        <v>Riempimento</v>
+        <v>Dimensione</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B663" t="str">
-        <v>Byte modificati dal caricamento</v>
+        <v>Riempimento</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B664" t="str">
-        <v>Tipo</v>
+        <v>Byte modificati dal caricamento</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B665" t="str">
-        <v>Array di {type}</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B666" t="str">
-        <v>(Nessun contenuto)</v>
+        <v>Array di {type}</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B667" t="str">
-        <v>byte</v>
+        <v>(Nessun contenuto)</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B668" t="str">
-        <v>Caricamento descrizione completa…</v>
+        <v>byte</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B669" t="str">
-        <v>Impossibile caricare la descrizione completa:</v>
+        <v>Caricamento descrizione completa…</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B670" t="str">
-        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
+        <v>Impossibile caricare la descrizione completa:</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B671" t="str">
-        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
+        <v>Impossibile analizzare completamente questo profilo, che non deve essere applicato. L’intestazione e la directory dei tag seguenti sono mostrate solo per ispezione.</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B672" t="str">
-        <v>Nessun output di convalida</v>
+        <v>Contenuto del tag non disponibile — impossibile analizzare completamente il profilo.</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B673" t="str">
-        <v>Il profilo è valido</v>
+        <v>Nessun output di convalida</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B674" t="str">
-        <v>Il profilo presenta avvisi</v>
+        <v>Il profilo è valido</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B675" t="str">
-        <v>Il profilo non è conforme</v>
+        <v>Il profilo presenta avvisi</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B676" t="str">
-        <v>Errore di convalida critico</v>
+        <v>Il profilo non è conforme</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B677" t="str">
-        <v>Stato di convalida sconosciuto</v>
+        <v>Errore di convalida critico</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B678" t="str">
-        <v>Critico — mostrato solo per ispezione</v>
+        <v>Stato di convalida sconosciuto</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B679" t="str">
-        <v>Nessun avviso o errore trovato.</v>
+        <v>Critico — mostrato solo per ispezione</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B680" t="str">
-        <v>Valido</v>
+        <v>Nessun avviso o errore trovato.</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B681" t="str">
-        <v>Avviso</v>
+        <v>Valido</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B682" t="str">
-        <v>Errore</v>
+        <v>Avviso</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B683" t="str">
-        <v>Sconosciuto</v>
+        <v>Errore</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B684" t="str">
-        <v>Superato</v>
+        <v>Sconosciuto</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B685" t="str">
-        <v>Non superato</v>
+        <v>Superato</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B686" t="str">
-        <v>Mostra nel contesto</v>
+        <v>Non superato</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B687" t="str">
-        <v>Dettaglio convalida</v>
+        <v>Mostra nel contesto</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B688" t="str">
-        <v>Attivato da</v>
+        <v>Dettaglio convalida</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B689" t="str">
-        <v>Campo</v>
+        <v>Attivato da</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B690" t="str">
-        <v>Valore attuale</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B691" t="str">
-        <v>Richiesto: 0</v>
+        <v>Valore attuale</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B692" t="str">
-        <v>Atteso: {value}</v>
+        <v>Richiesto: 0</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B693" t="str">
-        <v>Non valido</v>
+        <v>Atteso: {value}</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B694" t="str">
-        <v>Impossibile associare questo risultato a un campo specifico.</v>
+        <v>Non valido</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B695" t="str">
-        <v>Chiudi</v>
+        <v>Impossibile associare questo risultato a un campo specifico.</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B696" t="str">
-        <v>Caricamento editor XML…</v>
+        <v>Chiudi</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B697" t="str">
-        <v>Caricamento editor JSON…</v>
+        <v>Caricamento editor XML…</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B698" t="str">
-        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Caricamento editor JSON…</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B699" t="str">
-        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
+        <v>Hai modifiche XML non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B700" t="str">
-        <v>● modifiche XML non salvate</v>
+        <v>Hai modifiche JSON non salvate. Sovrascriverle con una nuova conversione dal profilo ICC?</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B701" t="str">
-        <v>● modifiche JSON non salvate</v>
+        <v>● modifiche XML non salvate</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B702" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● modifiche JSON non salvate</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B703" t="str">
-        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Fai clic su &lt;em&gt;Converti in XML&lt;/em&gt; per generare una rappresentazione XML modificabile di questo profilo. L’XML è prodotto dallo stesso percorso di codice IccLibXML usato dallo strumento &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B704" t="str">
-        <v>rientro</v>
+        <v>Fai clic su &lt;em&gt;Converti in JSON&lt;/em&gt; per generare una rappresentazione JSON modificabile di questo profilo. Il JSON è prodotto dallo stesso percorso di codice IccLibJSON usato dallo strumento &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B705" t="str">
-        <v>ordina chiavi</v>
+        <v>rientro</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B706" t="str">
+        <v>ordina chiavi</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B706" t="str">
+      <c r="B707" t="str">
         <v>Profilo scritto dalle modifiche, ma la riconvalida è fallita:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B706"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B707"/>
   </ignoredErrors>
 </worksheet>
 </file>